--- a/research/traditional_assets/database/data/norway/norway_recreation.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_recreation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ob_sats" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,31 +590,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.1172452723680497</v>
+        <v>0.01527400976668475</v>
       </c>
       <c r="H2">
-        <v>0.09201241885407846</v>
+        <v>-0.01169289202387412</v>
       </c>
       <c r="I2">
-        <v>-0.08636748518204911</v>
+        <v>0.0219750406945198</v>
       </c>
       <c r="J2">
-        <v>-0.08636748518204911</v>
+        <v>0.0219750406945198</v>
       </c>
       <c r="K2">
-        <v>-55.1</v>
+        <v>-14.9</v>
       </c>
       <c r="L2">
-        <v>-0.1555179226644087</v>
+        <v>-0.04042322300596853</v>
       </c>
       <c r="M2">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.005579922027290449</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.04156079854809437</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +626,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>2.29</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>17.2</v>
+        <v>11.5</v>
       </c>
       <c r="V2">
-        <v>0.04191033138401559</v>
+        <v>0.06339581036383682</v>
       </c>
       <c r="W2">
-        <v>-0.5092421441774492</v>
+        <v>-0.2487479131886478</v>
       </c>
       <c r="X2">
-        <v>0.1149202024591365</v>
+        <v>0.244460601345568</v>
       </c>
       <c r="Y2">
-        <v>-0.6241623466365858</v>
+        <v>-0.4932085145342158</v>
       </c>
       <c r="Z2">
-        <v>0.7290123456790124</v>
+        <v>0.7106227106227107</v>
       </c>
       <c r="AA2">
-        <v>-0.06296296296296297</v>
+        <v>0.01561596298438403</v>
       </c>
       <c r="AB2">
-        <v>0.05458063733306845</v>
+        <v>0.09062626691565857</v>
       </c>
       <c r="AC2">
-        <v>-0.1175436002960314</v>
+        <v>-0.07501030393127454</v>
       </c>
       <c r="AD2">
-        <v>755.7</v>
+        <v>584.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>755.7</v>
+        <v>584.7</v>
       </c>
       <c r="AG2">
-        <v>738.5</v>
+        <v>573.2</v>
       </c>
       <c r="AH2">
-        <v>0.6480576279907384</v>
+        <v>0.7632162903015273</v>
       </c>
       <c r="AI2">
-        <v>0.9265571358509074</v>
+        <v>0.8658374055975122</v>
       </c>
       <c r="AJ2">
-        <v>0.6427887544607885</v>
+        <v>0.759607739199576</v>
       </c>
       <c r="AK2">
-        <v>0.9249749498997997</v>
+        <v>0.8635131063573366</v>
       </c>
       <c r="AL2">
-        <v>43.9</v>
+        <v>21.2</v>
       </c>
       <c r="AM2">
-        <v>43.9</v>
+        <v>20.832</v>
       </c>
       <c r="AN2">
-        <v>-9.093862815884478</v>
+        <v>-17.71818181818182</v>
       </c>
       <c r="AO2">
-        <v>-0.6970387243735764</v>
+        <v>0.3820754716981132</v>
       </c>
       <c r="AP2">
-        <v>-8.886883273164862</v>
+        <v>-17.36969696969697</v>
       </c>
       <c r="AQ2">
-        <v>-0.6970387243735764</v>
+        <v>0.3888248847926267</v>
       </c>
     </row>
     <row r="3">
@@ -716,31 +715,31 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1172452723680497</v>
+        <v>0.01527400976668475</v>
       </c>
       <c r="H3">
-        <v>0.09201241885407846</v>
+        <v>-0.01169289202387412</v>
       </c>
       <c r="I3">
-        <v>-0.08636748518204911</v>
+        <v>0.0219750406945198</v>
       </c>
       <c r="J3">
-        <v>-0.08636748518204911</v>
+        <v>0.0219750406945198</v>
       </c>
       <c r="K3">
-        <v>-55.1</v>
+        <v>-14.9</v>
       </c>
       <c r="L3">
-        <v>-0.1555179226644087</v>
+        <v>-0.04042322300596853</v>
       </c>
       <c r="M3">
-        <v>2.29</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.005579922027290449</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.04156079854809437</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +751,8777 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>2.29</v>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>11.5</v>
+      </c>
+      <c r="V3">
+        <v>0.06339581036383682</v>
+      </c>
+      <c r="W3">
+        <v>-0.2487479131886478</v>
+      </c>
+      <c r="X3">
+        <v>0.244460601345568</v>
+      </c>
+      <c r="Y3">
+        <v>-0.4932085145342158</v>
+      </c>
+      <c r="Z3">
+        <v>0.7106227106227107</v>
+      </c>
+      <c r="AA3">
+        <v>0.01561596298438403</v>
+      </c>
+      <c r="AB3">
+        <v>0.09062626691565857</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07501030393127454</v>
+      </c>
+      <c r="AD3">
+        <v>584.7</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>584.7</v>
+      </c>
+      <c r="AG3">
+        <v>573.2</v>
+      </c>
+      <c r="AH3">
+        <v>0.7632162903015273</v>
+      </c>
+      <c r="AI3">
+        <v>0.8658374055975122</v>
+      </c>
+      <c r="AJ3">
+        <v>0.759607739199576</v>
+      </c>
+      <c r="AK3">
+        <v>0.8635131063573366</v>
+      </c>
+      <c r="AL3">
+        <v>21.2</v>
+      </c>
+      <c r="AM3">
+        <v>20.832</v>
+      </c>
+      <c r="AN3">
+        <v>-17.71818181818182</v>
+      </c>
+      <c r="AO3">
+        <v>0.3820754716981132</v>
+      </c>
+      <c r="AP3">
+        <v>-17.36969696969697</v>
+      </c>
+      <c r="AQ3">
+        <v>0.3888248847926267</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sats ASA (OB:SATS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OB:SATS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Recreation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.763216290301527</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>181.4</v>
+      </c>
+      <c r="H2">
+        <v>364.023815944302</v>
+      </c>
+      <c r="I2">
+        <v>754.6</v>
+      </c>
+      <c r="J2">
+        <v>360.184815944302</v>
+      </c>
+      <c r="K2">
+        <v>584.7</v>
+      </c>
+      <c r="L2">
+        <v>7.661</v>
+      </c>
+      <c r="M2">
+        <v>0.0906262669156586</v>
+      </c>
+      <c r="N2">
+        <v>0.147377872479232</v>
+      </c>
+      <c r="O2">
+        <v>0.0429</v>
+      </c>
+      <c r="P2">
+        <v>4.09834836183266</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.244460601345568</v>
+      </c>
+      <c r="T2">
+        <v>0.10746907965748</v>
+      </c>
+      <c r="U2">
+        <v>3.47737985833372</v>
+      </c>
+      <c r="V2">
+        <v>1.16108030866837</v>
+      </c>
+      <c r="W2">
+        <v>-73.46483100793093</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>181.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.055</v>
+      </c>
+      <c r="AD2">
+        <v>0.22</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>-33</v>
+      </c>
+      <c r="AH2">
+        <v>101.4</v>
+      </c>
+      <c r="AI2">
+        <v>29.7</v>
+      </c>
+      <c r="AJ2">
+        <v>584.7</v>
+      </c>
+      <c r="AK2">
+        <v>584.7</v>
+      </c>
+      <c r="AL2">
+        <v>21.2</v>
+      </c>
+      <c r="AM2">
+        <v>584.7</v>
+      </c>
+      <c r="AN2">
+        <v>11.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-584.7</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>11.5</v>
+      </c>
+      <c r="H2">
+        <v>181.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>-33</v>
+      </c>
+      <c r="K2">
+        <v>101.4</v>
+      </c>
+      <c r="L2">
+        <v>-134.4</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-134.4</v>
+      </c>
+      <c r="O2">
+        <v>-29.568</v>
+      </c>
+      <c r="P2">
+        <v>-104.832</v>
+      </c>
+      <c r="Q2">
+        <v>-3.432000000000002</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1473778724792316</v>
+      </c>
+      <c r="C3">
+        <v>364.0238159443022</v>
+      </c>
+      <c r="D3">
+        <v>360.1848159443022</v>
+      </c>
+      <c r="E3">
+        <v>-577.0390000000001</v>
+      </c>
+      <c r="F3">
+        <v>7.661</v>
+      </c>
+      <c r="G3">
+        <v>11.5</v>
+      </c>
+      <c r="H3">
+        <v>181.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>-33</v>
+      </c>
+      <c r="K3">
+        <v>101.4</v>
+      </c>
+      <c r="L3">
+        <v>-134.4</v>
+      </c>
+      <c r="M3">
+        <v>1.8294468</v>
+      </c>
+      <c r="N3">
+        <v>-136.2294468</v>
+      </c>
+      <c r="O3">
+        <v>-29.970478296</v>
+      </c>
+      <c r="P3">
+        <v>-106.258968504</v>
+      </c>
+      <c r="Q3">
+        <v>-4.858968504000003</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1074690796574798</v>
       </c>
       <c r="T3">
+        <v>1.161080308668366</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-16.1622628217448</v>
+      </c>
+      <c r="W3">
+        <v>4.098348361832659</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-73.46483100793093</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1493778724792316</v>
+      </c>
+      <c r="C4">
+        <v>349.8482247721499</v>
+      </c>
+      <c r="D4">
+        <v>353.6702247721499</v>
+      </c>
+      <c r="E4">
+        <v>-569.378</v>
+      </c>
+      <c r="F4">
+        <v>15.322</v>
+      </c>
+      <c r="G4">
+        <v>11.5</v>
+      </c>
+      <c r="H4">
+        <v>181.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>-33</v>
+      </c>
+      <c r="K4">
+        <v>101.4</v>
+      </c>
+      <c r="L4">
+        <v>-134.4</v>
+      </c>
+      <c r="M4">
+        <v>3.6588936</v>
+      </c>
+      <c r="N4">
+        <v>-138.0588936</v>
+      </c>
+      <c r="O4">
+        <v>-30.372956592</v>
+      </c>
+      <c r="P4">
+        <v>-107.685937008</v>
+      </c>
+      <c r="Q4">
+        <v>-6.285937008000005</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1081697845519439</v>
+      </c>
+      <c r="T4">
+        <v>1.172928066920084</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-8.0811314108724</v>
+      </c>
+      <c r="W4">
+        <v>2.168574180916329</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-36.73241550396546</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1513778724792316</v>
+      </c>
+      <c r="C5">
+        <v>335.9041032850672</v>
+      </c>
+      <c r="D5">
+        <v>347.3871032850672</v>
+      </c>
+      <c r="E5">
+        <v>-561.7170000000001</v>
+      </c>
+      <c r="F5">
+        <v>22.983</v>
+      </c>
+      <c r="G5">
+        <v>11.5</v>
+      </c>
+      <c r="H5">
+        <v>181.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>-33</v>
+      </c>
+      <c r="K5">
+        <v>101.4</v>
+      </c>
+      <c r="L5">
+        <v>-134.4</v>
+      </c>
+      <c r="M5">
+        <v>5.4883404</v>
+      </c>
+      <c r="N5">
+        <v>-139.8883404</v>
+      </c>
+      <c r="O5">
+        <v>-30.775434888</v>
+      </c>
+      <c r="P5">
+        <v>-109.112905512</v>
+      </c>
+      <c r="Q5">
+        <v>-7.712905512000006</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1088849369700052</v>
+      </c>
+      <c r="T5">
+        <v>1.185020108847095</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-5.387420940581601</v>
+      </c>
+      <c r="W5">
+        <v>1.525316120610886</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-24.48827700264364</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1533778724792316</v>
+      </c>
+      <c r="C6">
+        <v>322.1793303109612</v>
+      </c>
+      <c r="D6">
+        <v>341.3233303109612</v>
+      </c>
+      <c r="E6">
+        <v>-554.056</v>
+      </c>
+      <c r="F6">
+        <v>30.644</v>
+      </c>
+      <c r="G6">
+        <v>11.5</v>
+      </c>
+      <c r="H6">
+        <v>181.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>-33</v>
+      </c>
+      <c r="K6">
+        <v>101.4</v>
+      </c>
+      <c r="L6">
+        <v>-134.4</v>
+      </c>
+      <c r="M6">
+        <v>7.317787200000001</v>
+      </c>
+      <c r="N6">
+        <v>-141.7177872</v>
+      </c>
+      <c r="O6">
+        <v>-31.177913184</v>
+      </c>
+      <c r="P6">
+        <v>-110.539874016</v>
+      </c>
+      <c r="Q6">
+        <v>-9.139874015999993</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1096149883967761</v>
+      </c>
+      <c r="T6">
+        <v>1.197364068314252</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-4.0405657054362</v>
+      </c>
+      <c r="W6">
+        <v>1.203687090458165</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-18.36620775198273</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1553778724792316</v>
+      </c>
+      <c r="C7">
+        <v>308.6626164769013</v>
+      </c>
+      <c r="D7">
+        <v>335.4676164769013</v>
+      </c>
+      <c r="E7">
+        <v>-546.3950000000001</v>
+      </c>
+      <c r="F7">
+        <v>38.305</v>
+      </c>
+      <c r="G7">
+        <v>11.5</v>
+      </c>
+      <c r="H7">
+        <v>181.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>-33</v>
+      </c>
+      <c r="K7">
+        <v>101.4</v>
+      </c>
+      <c r="L7">
+        <v>-134.4</v>
+      </c>
+      <c r="M7">
+        <v>9.147234000000001</v>
+      </c>
+      <c r="N7">
+        <v>-143.547234</v>
+      </c>
+      <c r="O7">
+        <v>-31.58039148</v>
+      </c>
+      <c r="P7">
+        <v>-111.96684252</v>
+      </c>
+      <c r="Q7">
+        <v>-10.56684251999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1103604093272684</v>
+      </c>
+      <c r="T7">
+        <v>1.209967900612297</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-3.23245256434896</v>
+      </c>
+      <c r="W7">
+        <v>1.010709672366532</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-14.69296620158618</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1573778724792316</v>
+      </c>
+      <c r="C8">
+        <v>295.3434340611954</v>
+      </c>
+      <c r="D8">
+        <v>329.8094340611954</v>
+      </c>
+      <c r="E8">
+        <v>-538.734</v>
+      </c>
+      <c r="F8">
+        <v>45.966</v>
+      </c>
+      <c r="G8">
+        <v>11.5</v>
+      </c>
+      <c r="H8">
+        <v>181.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>-33</v>
+      </c>
+      <c r="K8">
+        <v>101.4</v>
+      </c>
+      <c r="L8">
+        <v>-134.4</v>
+      </c>
+      <c r="M8">
+        <v>10.9766808</v>
+      </c>
+      <c r="N8">
+        <v>-145.3766808</v>
+      </c>
+      <c r="O8">
+        <v>-31.982869776</v>
+      </c>
+      <c r="P8">
+        <v>-113.393811024</v>
+      </c>
+      <c r="Q8">
+        <v>-11.993811024</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1111216902775585</v>
+      </c>
+      <c r="T8">
+        <v>1.222839899554981</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-2.6937104702908</v>
+      </c>
+      <c r="W8">
+        <v>0.8820580603054432</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-12.24413850132182</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1593778724792316</v>
+      </c>
+      <c r="C9">
+        <v>282.2119538266398</v>
+      </c>
+      <c r="D9">
+        <v>324.3389538266399</v>
+      </c>
+      <c r="E9">
+        <v>-531.0730000000001</v>
+      </c>
+      <c r="F9">
+        <v>53.62700000000001</v>
+      </c>
+      <c r="G9">
+        <v>11.5</v>
+      </c>
+      <c r="H9">
+        <v>181.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>-33</v>
+      </c>
+      <c r="K9">
+        <v>101.4</v>
+      </c>
+      <c r="L9">
+        <v>-134.4</v>
+      </c>
+      <c r="M9">
+        <v>12.8061276</v>
+      </c>
+      <c r="N9">
+        <v>-147.2061276</v>
+      </c>
+      <c r="O9">
+        <v>-32.385348072</v>
+      </c>
+      <c r="P9">
+        <v>-114.820779528</v>
+      </c>
+      <c r="Q9">
+        <v>-13.420779528</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1118993428611882</v>
+      </c>
+      <c r="T9">
+        <v>1.235988715679228</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-2.308894688820685</v>
+      </c>
+      <c r="W9">
+        <v>0.7901640516903797</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-10.49497585827584</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1613778724792316</v>
+      </c>
+      <c r="C10">
+        <v>269.2589880376008</v>
+      </c>
+      <c r="D10">
+        <v>319.0469880376008</v>
+      </c>
+      <c r="E10">
+        <v>-523.412</v>
+      </c>
+      <c r="F10">
+        <v>61.288</v>
+      </c>
+      <c r="G10">
+        <v>11.5</v>
+      </c>
+      <c r="H10">
+        <v>181.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>-33</v>
+      </c>
+      <c r="K10">
+        <v>101.4</v>
+      </c>
+      <c r="L10">
+        <v>-134.4</v>
+      </c>
+      <c r="M10">
+        <v>14.6355744</v>
+      </c>
+      <c r="N10">
+        <v>-149.0355744</v>
+      </c>
+      <c r="O10">
+        <v>-32.787826368</v>
+      </c>
+      <c r="P10">
+        <v>-116.247748032</v>
+      </c>
+      <c r="Q10">
+        <v>-14.847748032</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1126939009357663</v>
+      </c>
+      <c r="T10">
+        <v>1.249423375632263</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-2.0202828527181</v>
+      </c>
+      <c r="W10">
+        <v>0.7212435452290823</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-9.183103875991364</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1633778724792316</v>
+      </c>
+      <c r="C11">
+        <v>256.4759389659923</v>
+      </c>
+      <c r="D11">
+        <v>313.9249389659923</v>
+      </c>
+      <c r="E11">
+        <v>-515.7510000000001</v>
+      </c>
+      <c r="F11">
+        <v>68.949</v>
+      </c>
+      <c r="G11">
+        <v>11.5</v>
+      </c>
+      <c r="H11">
+        <v>181.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>-33</v>
+      </c>
+      <c r="K11">
+        <v>101.4</v>
+      </c>
+      <c r="L11">
+        <v>-134.4</v>
+      </c>
+      <c r="M11">
+        <v>16.4650212</v>
+      </c>
+      <c r="N11">
+        <v>-150.8650212</v>
+      </c>
+      <c r="O11">
+        <v>-33.190304664</v>
+      </c>
+      <c r="P11">
+        <v>-117.674716536</v>
+      </c>
+      <c r="Q11">
+        <v>-16.274716536</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1135059218251703</v>
+      </c>
+      <c r="T11">
+        <v>1.263153302837013</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-1.795806980193867</v>
+      </c>
+      <c r="W11">
+        <v>0.6676387068702955</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-8.162759000881215</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1653778724792316</v>
+      </c>
+      <c r="C12">
+        <v>243.8547522790578</v>
+      </c>
+      <c r="D12">
+        <v>308.9647522790578</v>
+      </c>
+      <c r="E12">
+        <v>-508.09</v>
+      </c>
+      <c r="F12">
+        <v>76.61</v>
+      </c>
+      <c r="G12">
+        <v>11.5</v>
+      </c>
+      <c r="H12">
+        <v>181.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>-33</v>
+      </c>
+      <c r="K12">
+        <v>101.4</v>
+      </c>
+      <c r="L12">
+        <v>-134.4</v>
+      </c>
+      <c r="M12">
+        <v>18.294468</v>
+      </c>
+      <c r="N12">
+        <v>-152.694468</v>
+      </c>
+      <c r="O12">
+        <v>-33.59278295999999</v>
+      </c>
+      <c r="P12">
+        <v>-119.10168504</v>
+      </c>
+      <c r="Q12">
+        <v>-17.70168504</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1143359876232278</v>
+      </c>
+      <c r="T12">
+        <v>1.277188339535202</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-1.61622628217448</v>
+      </c>
+      <c r="W12">
+        <v>0.6247548361832659</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-7.346483100793092</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1673778724792316</v>
+      </c>
+      <c r="C13">
+        <v>231.3878747774066</v>
+      </c>
+      <c r="D13">
+        <v>304.1588747774067</v>
+      </c>
+      <c r="E13">
+        <v>-500.429</v>
+      </c>
+      <c r="F13">
+        <v>84.271</v>
+      </c>
+      <c r="G13">
+        <v>11.5</v>
+      </c>
+      <c r="H13">
+        <v>181.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>-33</v>
+      </c>
+      <c r="K13">
+        <v>101.4</v>
+      </c>
+      <c r="L13">
+        <v>-134.4</v>
+      </c>
+      <c r="M13">
+        <v>20.1239148</v>
+      </c>
+      <c r="N13">
+        <v>-154.5239148</v>
+      </c>
+      <c r="O13">
+        <v>-33.995261256</v>
+      </c>
+      <c r="P13">
+        <v>-120.528653544</v>
+      </c>
+      <c r="Q13">
+        <v>-19.128653544</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1151847065852865</v>
+      </c>
+      <c r="T13">
+        <v>1.291538770316497</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-1.469296620158618</v>
+      </c>
+      <c r="W13">
+        <v>0.589668032893878</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-6.678621000720993</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1693778724792316</v>
+      </c>
+      <c r="C14">
+        <v>219.0682160168914</v>
+      </c>
+      <c r="D14">
+        <v>299.5002160168914</v>
+      </c>
+      <c r="E14">
+        <v>-492.768</v>
+      </c>
+      <c r="F14">
+        <v>91.932</v>
+      </c>
+      <c r="G14">
+        <v>11.5</v>
+      </c>
+      <c r="H14">
+        <v>181.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>-33</v>
+      </c>
+      <c r="K14">
+        <v>101.4</v>
+      </c>
+      <c r="L14">
+        <v>-134.4</v>
+      </c>
+      <c r="M14">
+        <v>21.9533616</v>
+      </c>
+      <c r="N14">
+        <v>-156.3533616</v>
+      </c>
+      <c r="O14">
+        <v>-34.397739552</v>
+      </c>
+      <c r="P14">
+        <v>-121.955622048</v>
+      </c>
+      <c r="Q14">
+        <v>-20.555622048</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1160527146146648</v>
+      </c>
+      <c r="T14">
+        <v>1.306215347251911</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-1.3468552351454</v>
+      </c>
+      <c r="W14">
+        <v>0.5604290301527216</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-6.12206925066091</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1713778724792316</v>
+      </c>
+      <c r="C15">
+        <v>206.8891134041978</v>
+      </c>
+      <c r="D15">
+        <v>294.9821134041978</v>
+      </c>
+      <c r="E15">
+        <v>-485.107</v>
+      </c>
+      <c r="F15">
+        <v>99.593</v>
+      </c>
+      <c r="G15">
+        <v>11.5</v>
+      </c>
+      <c r="H15">
+        <v>181.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>-33</v>
+      </c>
+      <c r="K15">
+        <v>101.4</v>
+      </c>
+      <c r="L15">
+        <v>-134.4</v>
+      </c>
+      <c r="M15">
+        <v>23.7828084</v>
+      </c>
+      <c r="N15">
+        <v>-158.1828084</v>
+      </c>
+      <c r="O15">
+        <v>-34.800217848</v>
+      </c>
+      <c r="P15">
+        <v>-123.382590552</v>
+      </c>
+      <c r="Q15">
+        <v>-21.982590552</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1169406768516149</v>
+      </c>
+      <c r="T15">
+        <v>1.321229316760554</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-1.243250986288062</v>
+      </c>
+      <c r="W15">
+        <v>0.5356883355255891</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-5.651140846763917</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1733778724792316</v>
+      </c>
+      <c r="C16">
+        <v>194.8443004047803</v>
+      </c>
+      <c r="D16">
+        <v>290.5983004047803</v>
+      </c>
+      <c r="E16">
+        <v>-477.446</v>
+      </c>
+      <c r="F16">
+        <v>107.254</v>
+      </c>
+      <c r="G16">
+        <v>11.5</v>
+      </c>
+      <c r="H16">
+        <v>181.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>-33</v>
+      </c>
+      <c r="K16">
+        <v>101.4</v>
+      </c>
+      <c r="L16">
+        <v>-134.4</v>
+      </c>
+      <c r="M16">
+        <v>25.61225520000001</v>
+      </c>
+      <c r="N16">
+        <v>-160.0122552</v>
+      </c>
+      <c r="O16">
+        <v>-35.202696144</v>
+      </c>
+      <c r="P16">
+        <v>-124.809559056</v>
+      </c>
+      <c r="Q16">
+        <v>-23.40955905600002</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1178492893731453</v>
+      </c>
+      <c r="T16">
+        <v>1.336592448350793</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-1.154447344410343</v>
+      </c>
+      <c r="W16">
+        <v>0.5144820258451899</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-5.247487929137923</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1753778724792316</v>
+      </c>
+      <c r="C17">
+        <v>182.9278775441121</v>
+      </c>
+      <c r="D17">
+        <v>286.3428775441121</v>
+      </c>
+      <c r="E17">
+        <v>-469.785</v>
+      </c>
+      <c r="F17">
+        <v>114.915</v>
+      </c>
+      <c r="G17">
+        <v>11.5</v>
+      </c>
+      <c r="H17">
+        <v>181.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>-33</v>
+      </c>
+      <c r="K17">
+        <v>101.4</v>
+      </c>
+      <c r="L17">
+        <v>-134.4</v>
+      </c>
+      <c r="M17">
+        <v>27.441702</v>
+      </c>
+      <c r="N17">
+        <v>-161.841702</v>
+      </c>
+      <c r="O17">
+        <v>-35.60517443999999</v>
+      </c>
+      <c r="P17">
+        <v>-126.23652756</v>
+      </c>
+      <c r="Q17">
+        <v>-24.83652756000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1187792810128294</v>
+      </c>
+      <c r="T17">
+        <v>1.352317065390214</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-1.07748418811632</v>
+      </c>
+      <c r="W17">
+        <v>0.4961032241221772</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-4.897655400528728</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1773778724792316</v>
+      </c>
+      <c r="C18">
+        <v>171.1342859200484</v>
+      </c>
+      <c r="D18">
+        <v>282.2102859200484</v>
+      </c>
+      <c r="E18">
+        <v>-462.124</v>
+      </c>
+      <c r="F18">
+        <v>122.576</v>
+      </c>
+      <c r="G18">
+        <v>11.5</v>
+      </c>
+      <c r="H18">
+        <v>181.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>-33</v>
+      </c>
+      <c r="K18">
+        <v>101.4</v>
+      </c>
+      <c r="L18">
+        <v>-134.4</v>
+      </c>
+      <c r="M18">
+        <v>29.2711488</v>
+      </c>
+      <c r="N18">
+        <v>-163.6711488</v>
+      </c>
+      <c r="O18">
+        <v>-36.007652736</v>
+      </c>
+      <c r="P18">
+        <v>-127.663496064</v>
+      </c>
+      <c r="Q18">
+        <v>-26.26349606399999</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1197314153106012</v>
+      </c>
+      <c r="T18">
+        <v>1.368416078073431</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-1.01014142635905</v>
+      </c>
+      <c r="W18">
+        <v>0.4800217726145412</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-4.591551937995682</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1793778724792316</v>
+      </c>
+      <c r="C19">
+        <v>159.4582829762282</v>
+      </c>
+      <c r="D19">
+        <v>278.1952829762283</v>
+      </c>
+      <c r="E19">
+        <v>-454.463</v>
+      </c>
+      <c r="F19">
+        <v>130.237</v>
+      </c>
+      <c r="G19">
+        <v>11.5</v>
+      </c>
+      <c r="H19">
+        <v>181.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>-33</v>
+      </c>
+      <c r="K19">
+        <v>101.4</v>
+      </c>
+      <c r="L19">
+        <v>-134.4</v>
+      </c>
+      <c r="M19">
+        <v>31.10059560000001</v>
+      </c>
+      <c r="N19">
+        <v>-165.5005956</v>
+      </c>
+      <c r="O19">
+        <v>-36.410131032</v>
+      </c>
+      <c r="P19">
+        <v>-129.090464568</v>
+      </c>
+      <c r="Q19">
+        <v>-27.69046456800001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1207064926035</v>
+      </c>
+      <c r="T19">
+        <v>1.384903018773111</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.9507213424555765</v>
+      </c>
+      <c r="W19">
+        <v>0.4658322565783917</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-4.321460647525347</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1813778724792316</v>
+      </c>
+      <c r="C20">
+        <v>147.894920314494</v>
+      </c>
+      <c r="D20">
+        <v>274.292920314494</v>
+      </c>
+      <c r="E20">
+        <v>-446.802</v>
+      </c>
+      <c r="F20">
+        <v>137.898</v>
+      </c>
+      <c r="G20">
+        <v>11.5</v>
+      </c>
+      <c r="H20">
+        <v>181.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>-33</v>
+      </c>
+      <c r="K20">
+        <v>101.4</v>
+      </c>
+      <c r="L20">
+        <v>-134.4</v>
+      </c>
+      <c r="M20">
+        <v>32.9300424</v>
+      </c>
+      <c r="N20">
+        <v>-167.3300424</v>
+      </c>
+      <c r="O20">
+        <v>-36.81260932799999</v>
+      </c>
+      <c r="P20">
+        <v>-130.517433072</v>
+      </c>
+      <c r="Q20">
+        <v>-29.11743307200001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1217053522693964</v>
+      </c>
+      <c r="T20">
+        <v>1.401792079977661</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.8979034900969335</v>
+      </c>
+      <c r="W20">
+        <v>0.4532193534351477</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-4.081379500440607</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1833778724792316</v>
+      </c>
+      <c r="C21">
+        <v>136.4395233488878</v>
+      </c>
+      <c r="D21">
+        <v>270.4985233488878</v>
+      </c>
+      <c r="E21">
+        <v>-439.1410000000001</v>
+      </c>
+      <c r="F21">
+        <v>145.559</v>
+      </c>
+      <c r="G21">
+        <v>11.5</v>
+      </c>
+      <c r="H21">
+        <v>181.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>-33</v>
+      </c>
+      <c r="K21">
+        <v>101.4</v>
+      </c>
+      <c r="L21">
+        <v>-134.4</v>
+      </c>
+      <c r="M21">
+        <v>34.7594892</v>
+      </c>
+      <c r="N21">
+        <v>-169.1594892</v>
+      </c>
+      <c r="O21">
+        <v>-37.21508762399999</v>
+      </c>
+      <c r="P21">
+        <v>-131.944401576</v>
+      </c>
+      <c r="Q21">
+        <v>-30.54440157600001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1227288751369198</v>
+      </c>
+      <c r="T21">
+        <v>1.419098155039114</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.850645411670779</v>
+      </c>
+      <c r="W21">
+        <v>0.441934124306982</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-3.866570053048995</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1853778724792316</v>
+      </c>
+      <c r="C22">
+        <v>125.0876726253284</v>
+      </c>
+      <c r="D22">
+        <v>266.8076726253284</v>
+      </c>
+      <c r="E22">
+        <v>-431.48</v>
+      </c>
+      <c r="F22">
+        <v>153.22</v>
+      </c>
+      <c r="G22">
+        <v>11.5</v>
+      </c>
+      <c r="H22">
+        <v>181.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>-33</v>
+      </c>
+      <c r="K22">
+        <v>101.4</v>
+      </c>
+      <c r="L22">
+        <v>-134.4</v>
+      </c>
+      <c r="M22">
+        <v>36.588936</v>
+      </c>
+      <c r="N22">
+        <v>-170.988936</v>
+      </c>
+      <c r="O22">
+        <v>-37.61756592</v>
+      </c>
+      <c r="P22">
+        <v>-133.37137008</v>
+      </c>
+      <c r="Q22">
+        <v>-31.97137008000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1237779860761312</v>
+      </c>
+      <c r="T22">
+        <v>1.436836881977102</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.80811314108724</v>
+      </c>
+      <c r="W22">
+        <v>0.4317774180916329</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-3.673241550396546</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1873778724792316</v>
+      </c>
+      <c r="C23">
+        <v>113.8351866500177</v>
+      </c>
+      <c r="D23">
+        <v>263.2161866500177</v>
+      </c>
+      <c r="E23">
+        <v>-423.8190000000001</v>
+      </c>
+      <c r="F23">
+        <v>160.881</v>
+      </c>
+      <c r="G23">
+        <v>11.5</v>
+      </c>
+      <c r="H23">
+        <v>181.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>-33</v>
+      </c>
+      <c r="K23">
+        <v>101.4</v>
+      </c>
+      <c r="L23">
+        <v>-134.4</v>
+      </c>
+      <c r="M23">
+        <v>38.4183828</v>
+      </c>
+      <c r="N23">
+        <v>-172.8183828</v>
+      </c>
+      <c r="O23">
+        <v>-38.020044216</v>
+      </c>
+      <c r="P23">
+        <v>-134.798338584</v>
+      </c>
+      <c r="Q23">
+        <v>-33.39833858399999</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1248536567859557</v>
+      </c>
+      <c r="T23">
+        <v>1.455024690609724</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.7696315629402286</v>
+      </c>
+      <c r="W23">
+        <v>0.4225880172301266</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-3.498325286091948</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1893778724792316</v>
+      </c>
+      <c r="C24">
+        <v>102.6781060863039</v>
+      </c>
+      <c r="D24">
+        <v>259.7201060863039</v>
+      </c>
+      <c r="E24">
+        <v>-416.158</v>
+      </c>
+      <c r="F24">
+        <v>168.542</v>
+      </c>
+      <c r="G24">
+        <v>11.5</v>
+      </c>
+      <c r="H24">
+        <v>181.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>-33</v>
+      </c>
+      <c r="K24">
+        <v>101.4</v>
+      </c>
+      <c r="L24">
+        <v>-134.4</v>
+      </c>
+      <c r="M24">
+        <v>40.2478296</v>
+      </c>
+      <c r="N24">
+        <v>-174.6478296</v>
+      </c>
+      <c r="O24">
+        <v>-38.422522512</v>
+      </c>
+      <c r="P24">
+        <v>-136.225307088</v>
+      </c>
+      <c r="Q24">
+        <v>-34.82530708800002</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1259569087960321</v>
+      </c>
+      <c r="T24">
+        <v>1.473678853309849</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.7346483100793091</v>
+      </c>
+      <c r="W24">
+        <v>0.414234016446939</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-3.339310500360496</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1913778724792316</v>
+      </c>
+      <c r="C25">
+        <v>91.61267919443381</v>
+      </c>
+      <c r="D25">
+        <v>256.3156791944338</v>
+      </c>
+      <c r="E25">
+        <v>-408.4970000000001</v>
+      </c>
+      <c r="F25">
+        <v>176.203</v>
+      </c>
+      <c r="G25">
+        <v>11.5</v>
+      </c>
+      <c r="H25">
+        <v>181.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>-33</v>
+      </c>
+      <c r="K25">
+        <v>101.4</v>
+      </c>
+      <c r="L25">
+        <v>-134.4</v>
+      </c>
+      <c r="M25">
+        <v>42.0772764</v>
+      </c>
+      <c r="N25">
+        <v>-176.4772764</v>
+      </c>
+      <c r="O25">
+        <v>-38.82500080799999</v>
+      </c>
+      <c r="P25">
+        <v>-137.652275592</v>
+      </c>
+      <c r="Q25">
+        <v>-36.25227559199999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.127088816702474</v>
+      </c>
+      <c r="T25">
+        <v>1.49281753971647</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.7027070792062956</v>
+      </c>
+      <c r="W25">
+        <v>0.4066064505144634</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-3.194123087301344</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1933778724792316</v>
+      </c>
+      <c r="C26">
+        <v>80.63534840163075</v>
+      </c>
+      <c r="D26">
+        <v>252.9993484016307</v>
+      </c>
+      <c r="E26">
+        <v>-400.836</v>
+      </c>
+      <c r="F26">
+        <v>183.864</v>
+      </c>
+      <c r="G26">
+        <v>11.5</v>
+      </c>
+      <c r="H26">
+        <v>181.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>-33</v>
+      </c>
+      <c r="K26">
+        <v>101.4</v>
+      </c>
+      <c r="L26">
+        <v>-134.4</v>
+      </c>
+      <c r="M26">
+        <v>43.9067232</v>
+      </c>
+      <c r="N26">
+        <v>-178.3067232</v>
+      </c>
+      <c r="O26">
+        <v>-39.227479104</v>
+      </c>
+      <c r="P26">
+        <v>-139.079244096</v>
+      </c>
+      <c r="Q26">
+        <v>-37.67924409600002</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1282505116590855</v>
+      </c>
+      <c r="T26">
+        <v>1.512459875765371</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.6734276175727001</v>
+      </c>
+      <c r="W26">
+        <v>0.3996145150763608</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-3.061034625330455</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1953778724792316</v>
+      </c>
+      <c r="C27">
+        <v>69.74273790142817</v>
+      </c>
+      <c r="D27">
+        <v>249.7677379014281</v>
+      </c>
+      <c r="E27">
+        <v>-393.1750000000001</v>
+      </c>
+      <c r="F27">
+        <v>191.525</v>
+      </c>
+      <c r="G27">
+        <v>11.5</v>
+      </c>
+      <c r="H27">
+        <v>181.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>-33</v>
+      </c>
+      <c r="K27">
+        <v>101.4</v>
+      </c>
+      <c r="L27">
+        <v>-134.4</v>
+      </c>
+      <c r="M27">
+        <v>45.73617</v>
+      </c>
+      <c r="N27">
+        <v>-180.13617</v>
+      </c>
+      <c r="O27">
+        <v>-39.6299574</v>
+      </c>
+      <c r="P27">
+        <v>-140.5062126</v>
+      </c>
+      <c r="Q27">
+        <v>-39.10621259999999</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1294431851478733</v>
+      </c>
+      <c r="T27">
+        <v>1.532626007442243</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.646490512869792</v>
+      </c>
+      <c r="W27">
+        <v>0.3931819344733063</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-2.938593240317237</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1973778724792316</v>
+      </c>
+      <c r="C28">
+        <v>58.93164219139592</v>
+      </c>
+      <c r="D28">
+        <v>246.617642191396</v>
+      </c>
+      <c r="E28">
+        <v>-385.514</v>
+      </c>
+      <c r="F28">
+        <v>199.186</v>
+      </c>
+      <c r="G28">
+        <v>11.5</v>
+      </c>
+      <c r="H28">
+        <v>181.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>-33</v>
+      </c>
+      <c r="K28">
+        <v>101.4</v>
+      </c>
+      <c r="L28">
+        <v>-134.4</v>
+      </c>
+      <c r="M28">
+        <v>47.5656168</v>
+      </c>
+      <c r="N28">
+        <v>-181.9656168</v>
+      </c>
+      <c r="O28">
+        <v>-40.032435696</v>
+      </c>
+      <c r="P28">
+        <v>-141.933181104</v>
+      </c>
+      <c r="Q28">
+        <v>-40.53318110400002</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.130668093055277</v>
+      </c>
+      <c r="T28">
+        <v>1.553337169704976</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.6216254931440308</v>
+      </c>
+      <c r="W28">
+        <v>0.3872441677627946</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-2.825570423381959</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1993778724792316</v>
+      </c>
+      <c r="C29">
+        <v>48.19901546744256</v>
+      </c>
+      <c r="D29">
+        <v>243.5460154674426</v>
+      </c>
+      <c r="E29">
+        <v>-377.8530000000001</v>
+      </c>
+      <c r="F29">
+        <v>206.847</v>
+      </c>
+      <c r="G29">
+        <v>11.5</v>
+      </c>
+      <c r="H29">
+        <v>181.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>-33</v>
+      </c>
+      <c r="K29">
+        <v>101.4</v>
+      </c>
+      <c r="L29">
+        <v>-134.4</v>
+      </c>
+      <c r="M29">
+        <v>49.39506360000001</v>
+      </c>
+      <c r="N29">
+        <v>-183.7950636</v>
+      </c>
+      <c r="O29">
+        <v>-40.434913992</v>
+      </c>
+      <c r="P29">
+        <v>-143.360149608</v>
+      </c>
+      <c r="Q29">
+        <v>-41.96014960800002</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1319265600834315</v>
+      </c>
+      <c r="T29">
+        <v>1.574615761070797</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.5986023267312889</v>
+      </c>
+      <c r="W29">
+        <v>0.3817462356234318</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-2.720919666960405</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2013778724792316</v>
+      </c>
+      <c r="C30">
+        <v>37.54196180093203</v>
+      </c>
+      <c r="D30">
+        <v>240.5499618009321</v>
+      </c>
+      <c r="E30">
+        <v>-370.192</v>
+      </c>
+      <c r="F30">
+        <v>214.508</v>
+      </c>
+      <c r="G30">
+        <v>11.5</v>
+      </c>
+      <c r="H30">
+        <v>181.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>-33</v>
+      </c>
+      <c r="K30">
+        <v>101.4</v>
+      </c>
+      <c r="L30">
+        <v>-134.4</v>
+      </c>
+      <c r="M30">
+        <v>51.22451040000001</v>
+      </c>
+      <c r="N30">
+        <v>-185.6245104</v>
+      </c>
+      <c r="O30">
+        <v>-40.837392288</v>
+      </c>
+      <c r="P30">
+        <v>-144.787118112</v>
+      </c>
+      <c r="Q30">
+        <v>-43.38711811200002</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1332199845290347</v>
+      </c>
+      <c r="T30">
+        <v>1.596485424419003</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.5772236722051713</v>
+      </c>
+      <c r="W30">
+        <v>0.3766410129225949</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-2.623743964568961</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2033778724792316</v>
+      </c>
+      <c r="C31">
+        <v>26.95772603202533</v>
+      </c>
+      <c r="D31">
+        <v>237.6267260320253</v>
+      </c>
+      <c r="E31">
+        <v>-362.5310000000001</v>
+      </c>
+      <c r="F31">
+        <v>222.169</v>
+      </c>
+      <c r="G31">
+        <v>11.5</v>
+      </c>
+      <c r="H31">
+        <v>181.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>-33</v>
+      </c>
+      <c r="K31">
+        <v>101.4</v>
+      </c>
+      <c r="L31">
+        <v>-134.4</v>
+      </c>
+      <c r="M31">
+        <v>53.0539572</v>
+      </c>
+      <c r="N31">
+        <v>-187.4539572</v>
+      </c>
+      <c r="O31">
+        <v>-41.23987058399999</v>
+      </c>
+      <c r="P31">
+        <v>-146.214086616</v>
+      </c>
+      <c r="Q31">
+        <v>-44.814086616</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1345498434660634</v>
+      </c>
+      <c r="T31">
+        <v>1.618971134622087</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.5573194076463724</v>
+      </c>
+      <c r="W31">
+        <v>0.3718878745459537</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-2.533270034756239</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2053778724792316</v>
+      </c>
+      <c r="C32">
+        <v>16.44368531905002</v>
+      </c>
+      <c r="D32">
+        <v>234.77368531905</v>
+      </c>
+      <c r="E32">
+        <v>-354.87</v>
+      </c>
+      <c r="F32">
+        <v>229.83</v>
+      </c>
+      <c r="G32">
+        <v>11.5</v>
+      </c>
+      <c r="H32">
+        <v>181.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>-33</v>
+      </c>
+      <c r="K32">
+        <v>101.4</v>
+      </c>
+      <c r="L32">
+        <v>-134.4</v>
+      </c>
+      <c r="M32">
+        <v>54.88340400000001</v>
+      </c>
+      <c r="N32">
+        <v>-189.283404</v>
+      </c>
+      <c r="O32">
+        <v>-41.64234888</v>
+      </c>
+      <c r="P32">
+        <v>-147.64105512</v>
+      </c>
+      <c r="Q32">
+        <v>-46.24105512000003</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1359176983727214</v>
+      </c>
+      <c r="T32">
+        <v>1.642099293688117</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.53874209405816</v>
+      </c>
+      <c r="W32">
+        <v>0.3674516120610886</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-2.448827700264364</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2073778724792316</v>
+      </c>
+      <c r="C33">
+        <v>5.99734128941796</v>
+      </c>
+      <c r="D33">
+        <v>231.988341289418</v>
+      </c>
+      <c r="E33">
+        <v>-347.2090000000001</v>
+      </c>
+      <c r="F33">
+        <v>237.491</v>
+      </c>
+      <c r="G33">
+        <v>11.5</v>
+      </c>
+      <c r="H33">
+        <v>181.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>-33</v>
+      </c>
+      <c r="K33">
+        <v>101.4</v>
+      </c>
+      <c r="L33">
+        <v>-134.4</v>
+      </c>
+      <c r="M33">
+        <v>56.71285080000001</v>
+      </c>
+      <c r="N33">
+        <v>-191.1128508</v>
+      </c>
+      <c r="O33">
+        <v>-42.044827176</v>
+      </c>
+      <c r="P33">
+        <v>-149.068023624</v>
+      </c>
+      <c r="Q33">
+        <v>-47.66802362400003</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1373252012476884</v>
+      </c>
+      <c r="T33">
+        <v>1.665897834176351</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.5213633168304774</v>
+      </c>
+      <c r="W33">
+        <v>0.363301560059118</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-2.369833258320353</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2093778724792316</v>
+      </c>
+      <c r="C34">
+        <v>-4.383687257281906</v>
+      </c>
+      <c r="D34">
+        <v>229.2683127427181</v>
+      </c>
+      <c r="E34">
+        <v>-339.548</v>
+      </c>
+      <c r="F34">
+        <v>245.152</v>
+      </c>
+      <c r="G34">
+        <v>11.5</v>
+      </c>
+      <c r="H34">
+        <v>181.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>-33</v>
+      </c>
+      <c r="K34">
+        <v>101.4</v>
+      </c>
+      <c r="L34">
+        <v>-134.4</v>
+      </c>
+      <c r="M34">
+        <v>58.5422976</v>
+      </c>
+      <c r="N34">
+        <v>-192.9422976</v>
+      </c>
+      <c r="O34">
+        <v>-42.447305472</v>
+      </c>
+      <c r="P34">
+        <v>-150.494992128</v>
+      </c>
+      <c r="Q34">
+        <v>-49.09499212800003</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1387741012660368</v>
+      </c>
+      <c r="T34">
+        <v>1.690396331737768</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.505070713179525</v>
+      </c>
+      <c r="W34">
+        <v>0.3594108863072706</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-2.295775968997841</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2113778724792316</v>
+      </c>
+      <c r="C35">
+        <v>-14.70167113880834</v>
+      </c>
+      <c r="D35">
+        <v>226.6113288611917</v>
+      </c>
+      <c r="E35">
+        <v>-331.8870000000001</v>
+      </c>
+      <c r="F35">
+        <v>252.813</v>
+      </c>
+      <c r="G35">
+        <v>11.5</v>
+      </c>
+      <c r="H35">
+        <v>181.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>-33</v>
+      </c>
+      <c r="K35">
+        <v>101.4</v>
+      </c>
+      <c r="L35">
+        <v>-134.4</v>
+      </c>
+      <c r="M35">
+        <v>60.3717444</v>
+      </c>
+      <c r="N35">
+        <v>-194.7717444</v>
+      </c>
+      <c r="O35">
+        <v>-42.849783768</v>
+      </c>
+      <c r="P35">
+        <v>-151.921960632</v>
+      </c>
+      <c r="Q35">
+        <v>-50.521960632</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1402662520312015</v>
+      </c>
+      <c r="T35">
+        <v>1.715626127733854</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.4897655400528728</v>
+      </c>
+      <c r="W35">
+        <v>0.3557560109646261</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-2.226207000240331</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2133778724792316</v>
+      </c>
+      <c r="C36">
+        <v>-24.9587771130995</v>
+      </c>
+      <c r="D36">
+        <v>224.0152228869005</v>
+      </c>
+      <c r="E36">
+        <v>-324.226</v>
+      </c>
+      <c r="F36">
+        <v>260.474</v>
+      </c>
+      <c r="G36">
+        <v>11.5</v>
+      </c>
+      <c r="H36">
+        <v>181.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>-33</v>
+      </c>
+      <c r="K36">
+        <v>101.4</v>
+      </c>
+      <c r="L36">
+        <v>-134.4</v>
+      </c>
+      <c r="M36">
+        <v>62.20119120000001</v>
+      </c>
+      <c r="N36">
+        <v>-196.6011912</v>
+      </c>
+      <c r="O36">
+        <v>-43.252262064</v>
+      </c>
+      <c r="P36">
+        <v>-153.348929136</v>
+      </c>
+      <c r="Q36">
+        <v>-51.948929136</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1418036194862197</v>
+      </c>
+      <c r="T36">
+        <v>1.741620463002548</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.4753606712277882</v>
+      </c>
+      <c r="W36">
+        <v>0.3523161282891958</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-2.160730323762674</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2153778724792316</v>
+      </c>
+      <c r="C37">
+        <v>-35.15707377141385</v>
+      </c>
+      <c r="D37">
+        <v>221.4779262285862</v>
+      </c>
+      <c r="E37">
+        <v>-316.565</v>
+      </c>
+      <c r="F37">
+        <v>268.135</v>
+      </c>
+      <c r="G37">
+        <v>11.5</v>
+      </c>
+      <c r="H37">
+        <v>181.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>-33</v>
+      </c>
+      <c r="K37">
+        <v>101.4</v>
+      </c>
+      <c r="L37">
+        <v>-134.4</v>
+      </c>
+      <c r="M37">
+        <v>64.03063800000001</v>
+      </c>
+      <c r="N37">
+        <v>-198.430638</v>
+      </c>
+      <c r="O37">
+        <v>-43.65474036</v>
+      </c>
+      <c r="P37">
+        <v>-154.77589764</v>
+      </c>
+      <c r="Q37">
+        <v>-53.37589764000001</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1433882905552385</v>
+      </c>
+      <c r="T37">
+        <v>1.768414623971819</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.4617789377641371</v>
+      </c>
+      <c r="W37">
+        <v>0.349072810338076</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-2.098995171655169</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2173778724792316</v>
+      </c>
+      <c r="C38">
+        <v>-45.29853703546507</v>
+      </c>
+      <c r="D38">
+        <v>218.9974629645349</v>
+      </c>
+      <c r="E38">
+        <v>-308.9040000000001</v>
+      </c>
+      <c r="F38">
+        <v>275.796</v>
+      </c>
+      <c r="G38">
+        <v>11.5</v>
+      </c>
+      <c r="H38">
+        <v>181.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>-33</v>
+      </c>
+      <c r="K38">
+        <v>101.4</v>
+      </c>
+      <c r="L38">
+        <v>-134.4</v>
+      </c>
+      <c r="M38">
+        <v>65.8600848</v>
+      </c>
+      <c r="N38">
+        <v>-200.2600848</v>
+      </c>
+      <c r="O38">
+        <v>-44.057218656</v>
+      </c>
+      <c r="P38">
+        <v>-156.202866144</v>
+      </c>
+      <c r="Q38">
+        <v>-54.80286614400001</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1450224825951641</v>
+      </c>
+      <c r="T38">
+        <v>1.796046102471378</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.4489517450484667</v>
+      </c>
+      <c r="W38">
+        <v>0.3460096767175739</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-2.040689750220304</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2193778724792316</v>
+      </c>
+      <c r="C39">
+        <v>-55.38505528925583</v>
+      </c>
+      <c r="D39">
+        <v>216.5719447107442</v>
+      </c>
+      <c r="E39">
+        <v>-301.2430000000001</v>
+      </c>
+      <c r="F39">
+        <v>283.457</v>
+      </c>
+      <c r="G39">
+        <v>11.5</v>
+      </c>
+      <c r="H39">
+        <v>181.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>-33</v>
+      </c>
+      <c r="K39">
+        <v>101.4</v>
+      </c>
+      <c r="L39">
+        <v>-134.4</v>
+      </c>
+      <c r="M39">
+        <v>67.6895316</v>
+      </c>
+      <c r="N39">
+        <v>-202.0895316</v>
+      </c>
+      <c r="O39">
+        <v>-44.45969695199999</v>
+      </c>
+      <c r="P39">
+        <v>-157.629834648</v>
+      </c>
+      <c r="Q39">
+        <v>-56.22983464799998</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1467085537474683</v>
+      </c>
+      <c r="T39">
+        <v>1.824554770764575</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.4368179141012108</v>
+      </c>
+      <c r="W39">
+        <v>0.3431121178873691</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-1.985535973187322</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2213778724792316</v>
+      </c>
+      <c r="C40">
+        <v>-65.41843417361792</v>
+      </c>
+      <c r="D40">
+        <v>214.1995658263821</v>
+      </c>
+      <c r="E40">
+        <v>-293.5820000000001</v>
+      </c>
+      <c r="F40">
+        <v>291.118</v>
+      </c>
+      <c r="G40">
+        <v>11.5</v>
+      </c>
+      <c r="H40">
+        <v>181.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>-33</v>
+      </c>
+      <c r="K40">
+        <v>101.4</v>
+      </c>
+      <c r="L40">
+        <v>-134.4</v>
+      </c>
+      <c r="M40">
+        <v>69.51897840000001</v>
+      </c>
+      <c r="N40">
+        <v>-203.9189784</v>
+      </c>
+      <c r="O40">
+        <v>-44.862175248</v>
+      </c>
+      <c r="P40">
+        <v>-159.056803152</v>
+      </c>
+      <c r="Q40">
+        <v>-57.65680315200001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1484490142917823</v>
+      </c>
+      <c r="T40">
+        <v>1.853983073518842</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.4253227058353895</v>
+      </c>
+      <c r="W40">
+        <v>0.340367062153491</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-1.933285026524498</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2233778724792316</v>
+      </c>
+      <c r="C41">
+        <v>-75.40040106904559</v>
+      </c>
+      <c r="D41">
+        <v>211.8785989309544</v>
+      </c>
+      <c r="E41">
+        <v>-285.921</v>
+      </c>
+      <c r="F41">
+        <v>298.779</v>
+      </c>
+      <c r="G41">
+        <v>11.5</v>
+      </c>
+      <c r="H41">
+        <v>181.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>-33</v>
+      </c>
+      <c r="K41">
+        <v>101.4</v>
+      </c>
+      <c r="L41">
+        <v>-134.4</v>
+      </c>
+      <c r="M41">
+        <v>71.34842520000001</v>
+      </c>
+      <c r="N41">
+        <v>-205.7484252</v>
+      </c>
+      <c r="O41">
+        <v>-45.264653544</v>
+      </c>
+      <c r="P41">
+        <v>-160.483771656</v>
+      </c>
+      <c r="Q41">
+        <v>-59.08377165600001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1502465391162377</v>
+      </c>
+      <c r="T41">
+        <v>1.884376238658495</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.4144169954293538</v>
+      </c>
+      <c r="W41">
+        <v>0.3377627785085297</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-1.883713615587972</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2253778724792316</v>
+      </c>
+      <c r="C42">
+        <v>-85.33260929020852</v>
+      </c>
+      <c r="D42">
+        <v>209.6073907097915</v>
+      </c>
+      <c r="E42">
+        <v>-278.26</v>
+      </c>
+      <c r="F42">
+        <v>306.44</v>
+      </c>
+      <c r="G42">
+        <v>11.5</v>
+      </c>
+      <c r="H42">
+        <v>181.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>-33</v>
+      </c>
+      <c r="K42">
+        <v>101.4</v>
+      </c>
+      <c r="L42">
+        <v>-134.4</v>
+      </c>
+      <c r="M42">
+        <v>73.17787200000001</v>
+      </c>
+      <c r="N42">
+        <v>-207.577872</v>
+      </c>
+      <c r="O42">
+        <v>-45.66713184</v>
+      </c>
+      <c r="P42">
+        <v>-161.91074016</v>
+      </c>
+      <c r="Q42">
+        <v>-60.51074016000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1521039814348417</v>
+      </c>
+      <c r="T42">
+        <v>1.915782509302803</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.40405657054362</v>
+      </c>
+      <c r="W42">
+        <v>0.3352887090458165</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-1.836620775198273</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2273778724792316</v>
+      </c>
+      <c r="C43">
+        <v>-95.21664201355071</v>
+      </c>
+      <c r="D43">
+        <v>207.3843579864493</v>
+      </c>
+      <c r="E43">
+        <v>-270.599</v>
+      </c>
+      <c r="F43">
+        <v>314.1010000000001</v>
+      </c>
+      <c r="G43">
+        <v>11.5</v>
+      </c>
+      <c r="H43">
+        <v>181.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>-33</v>
+      </c>
+      <c r="K43">
+        <v>101.4</v>
+      </c>
+      <c r="L43">
+        <v>-134.4</v>
+      </c>
+      <c r="M43">
+        <v>75.00731880000002</v>
+      </c>
+      <c r="N43">
+        <v>-209.4073188</v>
+      </c>
+      <c r="O43">
+        <v>-46.069610136</v>
+      </c>
+      <c r="P43">
+        <v>-163.337708664</v>
+      </c>
+      <c r="Q43">
+        <v>-61.93770866400004</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.154024387899839</v>
+      </c>
+      <c r="T43">
+        <v>1.948253399290987</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.394201532237678</v>
+      </c>
+      <c r="W43">
+        <v>0.3329353258983575</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-1.7918251465349</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2293778724792316</v>
+      </c>
+      <c r="C44">
+        <v>-105.0540159575829</v>
+      </c>
+      <c r="D44">
+        <v>205.2079840424171</v>
+      </c>
+      <c r="E44">
+        <v>-262.938</v>
+      </c>
+      <c r="F44">
+        <v>321.762</v>
+      </c>
+      <c r="G44">
+        <v>11.5</v>
+      </c>
+      <c r="H44">
+        <v>181.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>-33</v>
+      </c>
+      <c r="K44">
+        <v>101.4</v>
+      </c>
+      <c r="L44">
+        <v>-134.4</v>
+      </c>
+      <c r="M44">
+        <v>76.83676560000001</v>
+      </c>
+      <c r="N44">
+        <v>-211.2367656</v>
+      </c>
+      <c r="O44">
+        <v>-46.472088432</v>
+      </c>
+      <c r="P44">
+        <v>-164.764677168</v>
+      </c>
+      <c r="Q44">
+        <v>-63.36467716800001</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1560110152774224</v>
+      </c>
+      <c r="T44">
+        <v>1.981843975140831</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.3848157814701143</v>
+      </c>
+      <c r="W44">
+        <v>0.3306940086150633</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-1.749162643045974</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2313778724792316</v>
+      </c>
+      <c r="C45">
+        <v>-114.8461848338467</v>
+      </c>
+      <c r="D45">
+        <v>203.0768151661533</v>
+      </c>
+      <c r="E45">
+        <v>-255.277</v>
+      </c>
+      <c r="F45">
+        <v>329.423</v>
+      </c>
+      <c r="G45">
+        <v>11.5</v>
+      </c>
+      <c r="H45">
+        <v>181.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>-33</v>
+      </c>
+      <c r="K45">
+        <v>101.4</v>
+      </c>
+      <c r="L45">
+        <v>-134.4</v>
+      </c>
+      <c r="M45">
+        <v>78.66621240000001</v>
+      </c>
+      <c r="N45">
+        <v>-213.0662124</v>
+      </c>
+      <c r="O45">
+        <v>-46.874566728</v>
+      </c>
+      <c r="P45">
+        <v>-166.191645672</v>
+      </c>
+      <c r="Q45">
+        <v>-64.79164567200002</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1580673488787807</v>
+      </c>
+      <c r="T45">
+        <v>2.016613167687161</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.375866577249879</v>
+      </c>
+      <c r="W45">
+        <v>0.3285569386472711</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-1.708484442044905</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2333778724792316</v>
+      </c>
+      <c r="C46">
+        <v>-124.5945425850507</v>
+      </c>
+      <c r="D46">
+        <v>200.9894574149493</v>
+      </c>
+      <c r="E46">
+        <v>-247.616</v>
+      </c>
+      <c r="F46">
+        <v>337.084</v>
+      </c>
+      <c r="G46">
+        <v>11.5</v>
+      </c>
+      <c r="H46">
+        <v>181.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>-33</v>
+      </c>
+      <c r="K46">
+        <v>101.4</v>
+      </c>
+      <c r="L46">
+        <v>-134.4</v>
+      </c>
+      <c r="M46">
+        <v>80.49565920000001</v>
+      </c>
+      <c r="N46">
+        <v>-214.8956592</v>
+      </c>
+      <c r="O46">
+        <v>-47.277045024</v>
+      </c>
+      <c r="P46">
+        <v>-167.618614176</v>
+      </c>
+      <c r="Q46">
+        <v>-66.21861417600002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1601971229659018</v>
+      </c>
+      <c r="T46">
+        <v>2.052624117110146</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.3673241550396545</v>
+      </c>
+      <c r="W46">
+        <v>0.3265170082234695</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-1.669655250180248</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2353778724792316</v>
+      </c>
+      <c r="C47">
+        <v>-134.3004264255366</v>
+      </c>
+      <c r="D47">
+        <v>198.9445735744634</v>
+      </c>
+      <c r="E47">
+        <v>-239.955</v>
+      </c>
+      <c r="F47">
+        <v>344.745</v>
+      </c>
+      <c r="G47">
+        <v>11.5</v>
+      </c>
+      <c r="H47">
+        <v>181.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>-33</v>
+      </c>
+      <c r="K47">
+        <v>101.4</v>
+      </c>
+      <c r="L47">
+        <v>-134.4</v>
+      </c>
+      <c r="M47">
+        <v>82.32510600000001</v>
+      </c>
+      <c r="N47">
+        <v>-216.725106</v>
+      </c>
+      <c r="O47">
+        <v>-47.67952331999999</v>
+      </c>
+      <c r="P47">
+        <v>-169.04558268</v>
+      </c>
+      <c r="Q47">
+        <v>-67.64558268000002</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1624043433834637</v>
+      </c>
+      <c r="T47">
+        <v>2.089944555603058</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.3591613960387733</v>
+      </c>
+      <c r="W47">
+        <v>0.3245677413740591</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-1.632551800176242</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2373778724792316</v>
+      </c>
+      <c r="C48">
+        <v>-143.9651196980111</v>
+      </c>
+      <c r="D48">
+        <v>196.9408803019889</v>
+      </c>
+      <c r="E48">
+        <v>-232.294</v>
+      </c>
+      <c r="F48">
+        <v>352.406</v>
+      </c>
+      <c r="G48">
+        <v>11.5</v>
+      </c>
+      <c r="H48">
+        <v>181.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>-33</v>
+      </c>
+      <c r="K48">
+        <v>101.4</v>
+      </c>
+      <c r="L48">
+        <v>-134.4</v>
+      </c>
+      <c r="M48">
+        <v>84.1545528</v>
+      </c>
+      <c r="N48">
+        <v>-218.5545528</v>
+      </c>
+      <c r="O48">
+        <v>-48.082001616</v>
+      </c>
+      <c r="P48">
+        <v>-170.472551184</v>
+      </c>
+      <c r="Q48">
+        <v>-69.07255118399999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1646933127053797</v>
+      </c>
+      <c r="T48">
+        <v>2.12864723255867</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.3513535396031478</v>
+      </c>
+      <c r="W48">
+        <v>0.3227032252572317</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-1.597061543650672</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2393778724792316</v>
+      </c>
+      <c r="C49">
+        <v>-153.5898545593666</v>
+      </c>
+      <c r="D49">
+        <v>194.9771454406334</v>
+      </c>
+      <c r="E49">
+        <v>-224.633</v>
+      </c>
+      <c r="F49">
+        <v>360.067</v>
+      </c>
+      <c r="G49">
+        <v>11.5</v>
+      </c>
+      <c r="H49">
+        <v>181.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>-33</v>
+      </c>
+      <c r="K49">
+        <v>101.4</v>
+      </c>
+      <c r="L49">
+        <v>-134.4</v>
+      </c>
+      <c r="M49">
+        <v>85.9839996</v>
+      </c>
+      <c r="N49">
+        <v>-220.3839996</v>
+      </c>
+      <c r="O49">
+        <v>-48.484479912</v>
+      </c>
+      <c r="P49">
+        <v>-171.899519688</v>
+      </c>
+      <c r="Q49">
+        <v>-70.49951968799999</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1670686582281226</v>
+      </c>
+      <c r="T49">
+        <v>2.168810387889966</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.3438779323775489</v>
+      </c>
+      <c r="W49">
+        <v>0.3209180502517587</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-1.563081510807041</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2413778724792316</v>
+      </c>
+      <c r="C50">
+        <v>-163.1758145074047</v>
+      </c>
+      <c r="D50">
+        <v>193.0521854925954</v>
+      </c>
+      <c r="E50">
+        <v>-216.972</v>
+      </c>
+      <c r="F50">
+        <v>367.728</v>
+      </c>
+      <c r="G50">
+        <v>11.5</v>
+      </c>
+      <c r="H50">
+        <v>181.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>-33</v>
+      </c>
+      <c r="K50">
+        <v>101.4</v>
+      </c>
+      <c r="L50">
+        <v>-134.4</v>
+      </c>
+      <c r="M50">
+        <v>87.8134464</v>
+      </c>
+      <c r="N50">
+        <v>-222.2134464</v>
+      </c>
+      <c r="O50">
+        <v>-48.886958208</v>
+      </c>
+      <c r="P50">
+        <v>-173.326488192</v>
+      </c>
+      <c r="Q50">
+        <v>-71.92648819199999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1695353631940481</v>
+      </c>
+      <c r="T50">
+        <v>2.210518279964773</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.33671380878635</v>
+      </c>
+      <c r="W50">
+        <v>0.3192072575381804</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-1.530517312665228</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2433778724792316</v>
+      </c>
+      <c r="C51">
+        <v>-172.7241367593475</v>
+      </c>
+      <c r="D51">
+        <v>191.1648632406525</v>
+      </c>
+      <c r="E51">
+        <v>-209.311</v>
+      </c>
+      <c r="F51">
+        <v>375.389</v>
+      </c>
+      <c r="G51">
+        <v>11.5</v>
+      </c>
+      <c r="H51">
+        <v>181.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>-33</v>
+      </c>
+      <c r="K51">
+        <v>101.4</v>
+      </c>
+      <c r="L51">
+        <v>-134.4</v>
+      </c>
+      <c r="M51">
+        <v>89.6428932</v>
+      </c>
+      <c r="N51">
+        <v>-224.0428932</v>
+      </c>
+      <c r="O51">
+        <v>-49.28943650399999</v>
+      </c>
+      <c r="P51">
+        <v>-174.753456696</v>
+      </c>
+      <c r="Q51">
+        <v>-73.35345669599999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.172098801688049</v>
+      </c>
+      <c r="T51">
+        <v>2.253861775650357</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.3298420984029551</v>
+      </c>
+      <c r="W51">
+        <v>0.3175662930986257</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-1.499282265467978</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2453778724792316</v>
+      </c>
+      <c r="C52">
+        <v>-182.2359144921841</v>
+      </c>
+      <c r="D52">
+        <v>189.3140855078159</v>
+      </c>
+      <c r="E52">
+        <v>-201.65</v>
+      </c>
+      <c r="F52">
+        <v>383.05</v>
+      </c>
+      <c r="G52">
+        <v>11.5</v>
+      </c>
+      <c r="H52">
+        <v>181.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>-33</v>
+      </c>
+      <c r="K52">
+        <v>101.4</v>
+      </c>
+      <c r="L52">
+        <v>-134.4</v>
+      </c>
+      <c r="M52">
+        <v>91.47234</v>
+      </c>
+      <c r="N52">
+        <v>-225.87234</v>
+      </c>
+      <c r="O52">
+        <v>-49.6919148</v>
+      </c>
+      <c r="P52">
+        <v>-176.1804252</v>
+      </c>
+      <c r="Q52">
+        <v>-74.7804252</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="U3">
-        <v>17.2</v>
-      </c>
-      <c r="V3">
-        <v>0.04191033138401559</v>
-      </c>
-      <c r="W3">
-        <v>-0.5092421441774492</v>
-      </c>
-      <c r="X3">
-        <v>0.1149202024591365</v>
-      </c>
-      <c r="Y3">
-        <v>-0.6241623466365858</v>
-      </c>
-      <c r="Z3">
-        <v>0.7290123456790124</v>
-      </c>
-      <c r="AA3">
-        <v>-0.06296296296296297</v>
-      </c>
-      <c r="AB3">
-        <v>0.05458063733306845</v>
-      </c>
-      <c r="AC3">
-        <v>-0.1175436002960314</v>
-      </c>
-      <c r="AD3">
-        <v>755.7</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>755.7</v>
-      </c>
-      <c r="AG3">
-        <v>738.5</v>
-      </c>
-      <c r="AH3">
-        <v>0.6480576279907384</v>
-      </c>
-      <c r="AI3">
-        <v>0.9265571358509074</v>
-      </c>
-      <c r="AJ3">
-        <v>0.6427887544607885</v>
-      </c>
-      <c r="AK3">
-        <v>0.9249749498997997</v>
-      </c>
-      <c r="AL3">
-        <v>43.9</v>
-      </c>
-      <c r="AM3">
-        <v>43.9</v>
-      </c>
-      <c r="AN3">
-        <v>-9.093862815884478</v>
-      </c>
-      <c r="AO3">
-        <v>-0.6970387243735764</v>
-      </c>
-      <c r="AP3">
-        <v>-8.886883273164862</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.6970387243735764</v>
+      <c r="S52">
+        <v>0.17476477772181</v>
+      </c>
+      <c r="T52">
+        <v>2.298939011163364</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.323245256434896</v>
+      </c>
+      <c r="W52">
+        <v>0.3159909672366532</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-1.469296620158619</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2473778724792316</v>
+      </c>
+      <c r="C53">
+        <v>-191.712198954122</v>
+      </c>
+      <c r="D53">
+        <v>187.498801045878</v>
+      </c>
+      <c r="E53">
+        <v>-193.989</v>
+      </c>
+      <c r="F53">
+        <v>390.711</v>
+      </c>
+      <c r="G53">
+        <v>11.5</v>
+      </c>
+      <c r="H53">
+        <v>181.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>-33</v>
+      </c>
+      <c r="K53">
+        <v>101.4</v>
+      </c>
+      <c r="L53">
+        <v>-134.4</v>
+      </c>
+      <c r="M53">
+        <v>93.3017868</v>
+      </c>
+      <c r="N53">
+        <v>-227.7017868</v>
+      </c>
+      <c r="O53">
+        <v>-50.094393096</v>
+      </c>
+      <c r="P53">
+        <v>-177.607393704</v>
+      </c>
+      <c r="Q53">
+        <v>-76.207393704</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1775395691038878</v>
+      </c>
+      <c r="T53">
+        <v>2.345856133840168</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.3169071141518588</v>
+      </c>
+      <c r="W53">
+        <v>0.3144774188594639</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-1.440486882508449</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2493778724792316</v>
+      </c>
+      <c r="C54">
+        <v>-201.1540014557179</v>
+      </c>
+      <c r="D54">
+        <v>185.7179985442821</v>
+      </c>
+      <c r="E54">
+        <v>-186.328</v>
+      </c>
+      <c r="F54">
+        <v>398.372</v>
+      </c>
+      <c r="G54">
+        <v>11.5</v>
+      </c>
+      <c r="H54">
+        <v>181.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>-33</v>
+      </c>
+      <c r="K54">
+        <v>101.4</v>
+      </c>
+      <c r="L54">
+        <v>-134.4</v>
+      </c>
+      <c r="M54">
+        <v>95.1312336</v>
+      </c>
+      <c r="N54">
+        <v>-229.5312336</v>
+      </c>
+      <c r="O54">
+        <v>-50.496871392</v>
+      </c>
+      <c r="P54">
+        <v>-179.034362208</v>
+      </c>
+      <c r="Q54">
+        <v>-77.634362208</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1804299767935521</v>
+      </c>
+      <c r="T54">
+        <v>2.394728136628504</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.3108127465720154</v>
+      </c>
+      <c r="W54">
+        <v>0.3130220838813973</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-1.412785211690979</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2513778724792316</v>
+      </c>
+      <c r="C55">
+        <v>-210.5622952486072</v>
+      </c>
+      <c r="D55">
+        <v>183.9707047513928</v>
+      </c>
+      <c r="E55">
+        <v>-178.667</v>
+      </c>
+      <c r="F55">
+        <v>406.033</v>
+      </c>
+      <c r="G55">
+        <v>11.5</v>
+      </c>
+      <c r="H55">
+        <v>181.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>-33</v>
+      </c>
+      <c r="K55">
+        <v>101.4</v>
+      </c>
+      <c r="L55">
+        <v>-134.4</v>
+      </c>
+      <c r="M55">
+        <v>96.96068040000002</v>
+      </c>
+      <c r="N55">
+        <v>-231.3606804</v>
+      </c>
+      <c r="O55">
+        <v>-50.899349688</v>
+      </c>
+      <c r="P55">
+        <v>-180.461330712</v>
+      </c>
+      <c r="Q55">
+        <v>-79.06133071200003</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1834433805551171</v>
+      </c>
+      <c r="T55">
+        <v>2.445679799109962</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.3049483551272604</v>
+      </c>
+      <c r="W55">
+        <v>0.3116216672043898</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-1.386128886942093</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2533778724792316</v>
+      </c>
+      <c r="C56">
+        <v>-219.9380172991691</v>
+      </c>
+      <c r="D56">
+        <v>182.2559827008309</v>
+      </c>
+      <c r="E56">
+        <v>-171.006</v>
+      </c>
+      <c r="F56">
+        <v>413.694</v>
+      </c>
+      <c r="G56">
+        <v>11.5</v>
+      </c>
+      <c r="H56">
+        <v>181.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>-33</v>
+      </c>
+      <c r="K56">
+        <v>101.4</v>
+      </c>
+      <c r="L56">
+        <v>-134.4</v>
+      </c>
+      <c r="M56">
+        <v>98.79012720000001</v>
+      </c>
+      <c r="N56">
+        <v>-233.1901272</v>
+      </c>
+      <c r="O56">
+        <v>-51.30182798399999</v>
+      </c>
+      <c r="P56">
+        <v>-181.888299216</v>
+      </c>
+      <c r="Q56">
+        <v>-80.488299216</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1865878018715326</v>
+      </c>
+      <c r="T56">
+        <v>2.498846751264526</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.2993011633656444</v>
+      </c>
+      <c r="W56">
+        <v>0.3102731178117159</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-1.360459833480202</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2553778724792316</v>
+      </c>
+      <c r="C57">
+        <v>-229.2820699639172</v>
+      </c>
+      <c r="D57">
+        <v>180.5729300360828</v>
+      </c>
+      <c r="E57">
+        <v>-163.345</v>
+      </c>
+      <c r="F57">
+        <v>421.355</v>
+      </c>
+      <c r="G57">
+        <v>11.5</v>
+      </c>
+      <c r="H57">
+        <v>181.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>-33</v>
+      </c>
+      <c r="K57">
+        <v>101.4</v>
+      </c>
+      <c r="L57">
+        <v>-134.4</v>
+      </c>
+      <c r="M57">
+        <v>100.619574</v>
+      </c>
+      <c r="N57">
+        <v>-235.019574</v>
+      </c>
+      <c r="O57">
+        <v>-51.70430628</v>
+      </c>
+      <c r="P57">
+        <v>-183.31526772</v>
+      </c>
+      <c r="Q57">
+        <v>-81.91526772000003</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1898719752464556</v>
+      </c>
+      <c r="T57">
+        <v>2.554376679070405</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.2938593240317236</v>
+      </c>
+      <c r="W57">
+        <v>0.3089736065787756</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-1.335724200144198</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2573778724792316</v>
+      </c>
+      <c r="C58">
+        <v>-238.5953225729113</v>
+      </c>
+      <c r="D58">
+        <v>178.9206774270888</v>
+      </c>
+      <c r="E58">
+        <v>-155.684</v>
+      </c>
+      <c r="F58">
+        <v>429.0160000000001</v>
+      </c>
+      <c r="G58">
+        <v>11.5</v>
+      </c>
+      <c r="H58">
+        <v>181.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>-33</v>
+      </c>
+      <c r="K58">
+        <v>101.4</v>
+      </c>
+      <c r="L58">
+        <v>-134.4</v>
+      </c>
+      <c r="M58">
+        <v>102.4490208</v>
+      </c>
+      <c r="N58">
+        <v>-236.8490208</v>
+      </c>
+      <c r="O58">
+        <v>-52.106784576</v>
+      </c>
+      <c r="P58">
+        <v>-184.742236224</v>
+      </c>
+      <c r="Q58">
+        <v>-83.34223622400003</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1933054292293296</v>
+      </c>
+      <c r="T58">
+        <v>2.612430694503823</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.2886118361025857</v>
+      </c>
+      <c r="W58">
+        <v>0.3077205064612975</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-1.31187198228448</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2593778724792316</v>
+      </c>
+      <c r="C59">
+        <v>-247.8786129270258</v>
+      </c>
+      <c r="D59">
+        <v>177.2983870729742</v>
+      </c>
+      <c r="E59">
+        <v>-148.023</v>
+      </c>
+      <c r="F59">
+        <v>436.6770000000001</v>
+      </c>
+      <c r="G59">
+        <v>11.5</v>
+      </c>
+      <c r="H59">
+        <v>181.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>-33</v>
+      </c>
+      <c r="K59">
+        <v>101.4</v>
+      </c>
+      <c r="L59">
+        <v>-134.4</v>
+      </c>
+      <c r="M59">
+        <v>104.2784676</v>
+      </c>
+      <c r="N59">
+        <v>-238.6784676</v>
+      </c>
+      <c r="O59">
+        <v>-52.509262872</v>
+      </c>
+      <c r="P59">
+        <v>-186.169204728</v>
+      </c>
+      <c r="Q59">
+        <v>-84.76920472800003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1968985787462907</v>
+      </c>
+      <c r="T59">
+        <v>2.673184896701586</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.2835484705569263</v>
+      </c>
+      <c r="W59">
+        <v>0.306511374768994</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-1.288856684349665</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2613778724792316</v>
+      </c>
+      <c r="C60">
+        <v>-257.1327487144973</v>
+      </c>
+      <c r="D60">
+        <v>175.7052512855026</v>
+      </c>
+      <c r="E60">
+        <v>-140.3620000000001</v>
+      </c>
+      <c r="F60">
+        <v>444.338</v>
+      </c>
+      <c r="G60">
+        <v>11.5</v>
+      </c>
+      <c r="H60">
+        <v>181.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>-33</v>
+      </c>
+      <c r="K60">
+        <v>101.4</v>
+      </c>
+      <c r="L60">
+        <v>-134.4</v>
+      </c>
+      <c r="M60">
+        <v>106.1079144</v>
+      </c>
+      <c r="N60">
+        <v>-240.5079144</v>
+      </c>
+      <c r="O60">
+        <v>-52.91174116799999</v>
+      </c>
+      <c r="P60">
+        <v>-187.596173232</v>
+      </c>
+      <c r="Q60">
+        <v>-86.19617323200001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2006628306212024</v>
+      </c>
+      <c r="T60">
+        <v>2.736832156146861</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.2786597038231862</v>
+      </c>
+      <c r="W60">
+        <v>0.3053439372729769</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-1.266635017378119</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2633778724792316</v>
+      </c>
+      <c r="C61">
+        <v>-266.3585088517789</v>
+      </c>
+      <c r="D61">
+        <v>174.140491148221</v>
+      </c>
+      <c r="E61">
+        <v>-132.7010000000001</v>
+      </c>
+      <c r="F61">
+        <v>451.999</v>
+      </c>
+      <c r="G61">
+        <v>11.5</v>
+      </c>
+      <c r="H61">
+        <v>181.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>-33</v>
+      </c>
+      <c r="K61">
+        <v>101.4</v>
+      </c>
+      <c r="L61">
+        <v>-134.4</v>
+      </c>
+      <c r="M61">
+        <v>107.9373612</v>
+      </c>
+      <c r="N61">
+        <v>-242.3373612</v>
+      </c>
+      <c r="O61">
+        <v>-53.314219464</v>
+      </c>
+      <c r="P61">
+        <v>-189.023141736</v>
+      </c>
+      <c r="Q61">
+        <v>-87.62314173600001</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2046107045387927</v>
+      </c>
+      <c r="T61">
+        <v>2.803584159955322</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.2739366579956746</v>
+      </c>
+      <c r="W61">
+        <v>0.3042160739293671</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-1.245166627253067</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2653778724792316</v>
+      </c>
+      <c r="C62">
+        <v>-275.5566447533811</v>
+      </c>
+      <c r="D62">
+        <v>172.6033552466189</v>
+      </c>
+      <c r="E62">
+        <v>-125.04</v>
+      </c>
+      <c r="F62">
+        <v>459.66</v>
+      </c>
+      <c r="G62">
+        <v>11.5</v>
+      </c>
+      <c r="H62">
+        <v>181.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>-33</v>
+      </c>
+      <c r="K62">
+        <v>101.4</v>
+      </c>
+      <c r="L62">
+        <v>-134.4</v>
+      </c>
+      <c r="M62">
+        <v>109.766808</v>
+      </c>
+      <c r="N62">
+        <v>-244.166808</v>
+      </c>
+      <c r="O62">
+        <v>-53.71669776</v>
+      </c>
+      <c r="P62">
+        <v>-190.45011024</v>
+      </c>
+      <c r="Q62">
+        <v>-89.05011024000001</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2087559721522625</v>
+      </c>
+      <c r="T62">
+        <v>2.873673763954204</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.26937104702908</v>
+      </c>
+      <c r="W62">
+        <v>0.3031258060305443</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-1.224413850132182</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2673778724792316</v>
+      </c>
+      <c r="C63">
+        <v>-284.7278815350477</v>
+      </c>
+      <c r="D63">
+        <v>171.0931184649524</v>
+      </c>
+      <c r="E63">
+        <v>-117.379</v>
+      </c>
+      <c r="F63">
+        <v>467.321</v>
+      </c>
+      <c r="G63">
+        <v>11.5</v>
+      </c>
+      <c r="H63">
+        <v>181.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>-33</v>
+      </c>
+      <c r="K63">
+        <v>101.4</v>
+      </c>
+      <c r="L63">
+        <v>-134.4</v>
+      </c>
+      <c r="M63">
+        <v>111.5962548</v>
+      </c>
+      <c r="N63">
+        <v>-245.9962548</v>
+      </c>
+      <c r="O63">
+        <v>-54.119176056</v>
+      </c>
+      <c r="P63">
+        <v>-191.877078744</v>
+      </c>
+      <c r="Q63">
+        <v>-90.47707874400001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2131138175920641</v>
+      </c>
+      <c r="T63">
+        <v>2.947357706619698</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.2649551282253246</v>
+      </c>
+      <c r="W63">
+        <v>0.3020712846202075</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-1.204341491933294</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2693778724792316</v>
+      </c>
+      <c r="C64">
+        <v>-293.8729191543155</v>
+      </c>
+      <c r="D64">
+        <v>169.6090808456846</v>
+      </c>
+      <c r="E64">
+        <v>-109.718</v>
+      </c>
+      <c r="F64">
+        <v>474.982</v>
+      </c>
+      <c r="G64">
+        <v>11.5</v>
+      </c>
+      <c r="H64">
+        <v>181.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>-33</v>
+      </c>
+      <c r="K64">
+        <v>101.4</v>
+      </c>
+      <c r="L64">
+        <v>-134.4</v>
+      </c>
+      <c r="M64">
+        <v>113.4257016</v>
+      </c>
+      <c r="N64">
+        <v>-247.8257016</v>
+      </c>
+      <c r="O64">
+        <v>-54.52165435199999</v>
+      </c>
+      <c r="P64">
+        <v>-193.304047248</v>
+      </c>
+      <c r="Q64">
+        <v>-91.90404724800001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2177010233181711</v>
+      </c>
+      <c r="T64">
+        <v>3.024919751530742</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.2606816584152387</v>
+      </c>
+      <c r="W64">
+        <v>0.301050780029559</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-1.184916629160176</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2713778724792316</v>
+      </c>
+      <c r="C65">
+        <v>-302.9924334922246</v>
+      </c>
+      <c r="D65">
+        <v>168.1505665077754</v>
+      </c>
+      <c r="E65">
+        <v>-102.057</v>
+      </c>
+      <c r="F65">
+        <v>482.643</v>
+      </c>
+      <c r="G65">
+        <v>11.5</v>
+      </c>
+      <c r="H65">
+        <v>181.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>-33</v>
+      </c>
+      <c r="K65">
+        <v>101.4</v>
+      </c>
+      <c r="L65">
+        <v>-134.4</v>
+      </c>
+      <c r="M65">
+        <v>115.2551484</v>
+      </c>
+      <c r="N65">
+        <v>-249.6551484</v>
+      </c>
+      <c r="O65">
+        <v>-54.924132648</v>
+      </c>
+      <c r="P65">
+        <v>-194.731015752</v>
+      </c>
+      <c r="Q65">
+        <v>-93.33101575200001</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2225361861105541</v>
+      </c>
+      <c r="T65">
+        <v>3.106674339409951</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.2565438543134095</v>
+      </c>
+      <c r="W65">
+        <v>0.3000626724100422</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-1.166108428697316</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2733778724792316</v>
+      </c>
+      <c r="C66">
+        <v>-312.0870773796945</v>
+      </c>
+      <c r="D66">
+        <v>166.7169226203055</v>
+      </c>
+      <c r="E66">
+        <v>-94.39600000000002</v>
+      </c>
+      <c r="F66">
+        <v>490.304</v>
+      </c>
+      <c r="G66">
+        <v>11.5</v>
+      </c>
+      <c r="H66">
+        <v>181.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>-33</v>
+      </c>
+      <c r="K66">
+        <v>101.4</v>
+      </c>
+      <c r="L66">
+        <v>-134.4</v>
+      </c>
+      <c r="M66">
+        <v>117.0845952</v>
+      </c>
+      <c r="N66">
+        <v>-251.4845952</v>
+      </c>
+      <c r="O66">
+        <v>-55.326610944</v>
+      </c>
+      <c r="P66">
+        <v>-196.157984256</v>
+      </c>
+      <c r="Q66">
+        <v>-94.75798425600001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2276399690580695</v>
+      </c>
+      <c r="T66">
+        <v>3.192970848838006</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.2525353565897625</v>
+      </c>
+      <c r="W66">
+        <v>0.2991054431536353</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-1.14788798449892</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2753778724792316</v>
+      </c>
+      <c r="C67">
+        <v>-321.157481571838</v>
+      </c>
+      <c r="D67">
+        <v>165.307518428162</v>
+      </c>
+      <c r="E67">
+        <v>-86.73500000000001</v>
+      </c>
+      <c r="F67">
+        <v>497.965</v>
+      </c>
+      <c r="G67">
+        <v>11.5</v>
+      </c>
+      <c r="H67">
+        <v>181.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>-33</v>
+      </c>
+      <c r="K67">
+        <v>101.4</v>
+      </c>
+      <c r="L67">
+        <v>-134.4</v>
+      </c>
+      <c r="M67">
+        <v>118.914042</v>
+      </c>
+      <c r="N67">
+        <v>-253.314042</v>
+      </c>
+      <c r="O67">
+        <v>-55.72908924</v>
+      </c>
+      <c r="P67">
+        <v>-197.58495276</v>
+      </c>
+      <c r="Q67">
+        <v>-96.18495276000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2330353967454429</v>
+      </c>
+      <c r="T67">
+        <v>3.284198587376234</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.2486501972576123</v>
+      </c>
+      <c r="W67">
+        <v>0.2981776671051178</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-1.130228169352784</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2773778724792316</v>
+      </c>
+      <c r="C68">
+        <v>-330.2042556732695</v>
+      </c>
+      <c r="D68">
+        <v>163.9217443267306</v>
+      </c>
+      <c r="E68">
+        <v>-79.07400000000001</v>
+      </c>
+      <c r="F68">
+        <v>505.626</v>
+      </c>
+      <c r="G68">
+        <v>11.5</v>
+      </c>
+      <c r="H68">
+        <v>181.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>-33</v>
+      </c>
+      <c r="K68">
+        <v>101.4</v>
+      </c>
+      <c r="L68">
+        <v>-134.4</v>
+      </c>
+      <c r="M68">
+        <v>120.7434888</v>
+      </c>
+      <c r="N68">
+        <v>-255.1434888</v>
+      </c>
+      <c r="O68">
+        <v>-56.13156753599999</v>
+      </c>
+      <c r="P68">
+        <v>-199.011921264</v>
+      </c>
+      <c r="Q68">
+        <v>-97.61192126400002</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2387482025320735</v>
+      </c>
+      <c r="T68">
+        <v>3.380792663475535</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.2448827700264364</v>
+      </c>
+      <c r="W68">
+        <v>0.297278005482313</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-1.113103500120165</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2793778724792316</v>
+      </c>
+      <c r="C69">
+        <v>-339.2279890172587</v>
+      </c>
+      <c r="D69">
+        <v>162.5590109827413</v>
+      </c>
+      <c r="E69">
+        <v>-71.41300000000001</v>
+      </c>
+      <c r="F69">
+        <v>513.287</v>
+      </c>
+      <c r="G69">
+        <v>11.5</v>
+      </c>
+      <c r="H69">
+        <v>181.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>-33</v>
+      </c>
+      <c r="K69">
+        <v>101.4</v>
+      </c>
+      <c r="L69">
+        <v>-134.4</v>
+      </c>
+      <c r="M69">
+        <v>122.5729356</v>
+      </c>
+      <c r="N69">
+        <v>-256.9729356</v>
+      </c>
+      <c r="O69">
+        <v>-56.534045832</v>
+      </c>
+      <c r="P69">
+        <v>-200.438889768</v>
+      </c>
+      <c r="Q69">
+        <v>-99.03888976800002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2448072389724394</v>
+      </c>
+      <c r="T69">
+        <v>3.483240926005097</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.2412278033096239</v>
+      </c>
+      <c r="W69">
+        <v>0.2964051994303382</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-1.096490015043745</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2813778724792316</v>
+      </c>
+      <c r="C70">
+        <v>-348.229251501395</v>
+      </c>
+      <c r="D70">
+        <v>161.2187484986051</v>
+      </c>
+      <c r="E70">
+        <v>-63.75199999999995</v>
+      </c>
+      <c r="F70">
+        <v>520.9480000000001</v>
+      </c>
+      <c r="G70">
+        <v>11.5</v>
+      </c>
+      <c r="H70">
+        <v>181.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>-33</v>
+      </c>
+      <c r="K70">
+        <v>101.4</v>
+      </c>
+      <c r="L70">
+        <v>-134.4</v>
+      </c>
+      <c r="M70">
+        <v>124.4023824</v>
+      </c>
+      <c r="N70">
+        <v>-258.8023824000001</v>
+      </c>
+      <c r="O70">
+        <v>-56.936524128</v>
+      </c>
+      <c r="P70">
+        <v>-201.8658582720001</v>
+      </c>
+      <c r="Q70">
+        <v>-100.465858272</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2512449651903281</v>
+      </c>
+      <c r="T70">
+        <v>3.592092204942757</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.2376803356138941</v>
+      </c>
+      <c r="W70">
+        <v>0.295558064144598</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-1.080365161881337</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2833778724792316</v>
+      </c>
+      <c r="C71">
+        <v>-357.2085943822481</v>
+      </c>
+      <c r="D71">
+        <v>159.9004056177519</v>
+      </c>
+      <c r="E71">
+        <v>-56.09100000000001</v>
+      </c>
+      <c r="F71">
+        <v>528.609</v>
+      </c>
+      <c r="G71">
+        <v>11.5</v>
+      </c>
+      <c r="H71">
+        <v>181.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>-33</v>
+      </c>
+      <c r="K71">
+        <v>101.4</v>
+      </c>
+      <c r="L71">
+        <v>-134.4</v>
+      </c>
+      <c r="M71">
+        <v>126.2318292</v>
+      </c>
+      <c r="N71">
+        <v>-260.6318292</v>
+      </c>
+      <c r="O71">
+        <v>-57.339002424</v>
+      </c>
+      <c r="P71">
+        <v>-203.292826776</v>
+      </c>
+      <c r="Q71">
+        <v>-101.892826776</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2580980285835646</v>
+      </c>
+      <c r="T71">
+        <v>3.707966147037685</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.2342356930687652</v>
+      </c>
+      <c r="W71">
+        <v>0.2947354835048211</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-1.064707695767115</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2853778724792316</v>
+      </c>
+      <c r="C72">
+        <v>-366.1665510313588</v>
+      </c>
+      <c r="D72">
+        <v>158.6034489686412</v>
+      </c>
+      <c r="E72">
+        <v>-48.42999999999995</v>
+      </c>
+      <c r="F72">
+        <v>536.2700000000001</v>
+      </c>
+      <c r="G72">
+        <v>11.5</v>
+      </c>
+      <c r="H72">
+        <v>181.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>-33</v>
+      </c>
+      <c r="K72">
+        <v>101.4</v>
+      </c>
+      <c r="L72">
+        <v>-134.4</v>
+      </c>
+      <c r="M72">
+        <v>128.061276</v>
+      </c>
+      <c r="N72">
+        <v>-262.461276</v>
+      </c>
+      <c r="O72">
+        <v>-57.74148071999999</v>
+      </c>
+      <c r="P72">
+        <v>-204.71979528</v>
+      </c>
+      <c r="Q72">
+        <v>-103.31979528</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2654079628696834</v>
+      </c>
+      <c r="T72">
+        <v>3.831565018605608</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.2308894688820686</v>
+      </c>
+      <c r="W72">
+        <v>0.293936405169038</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-1.049497585827584</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2873778724792316</v>
+      </c>
+      <c r="C73">
+        <v>-375.1036376547318</v>
+      </c>
+      <c r="D73">
+        <v>157.3273623452683</v>
+      </c>
+      <c r="E73">
+        <v>-40.76900000000001</v>
+      </c>
+      <c r="F73">
+        <v>543.931</v>
+      </c>
+      <c r="G73">
+        <v>11.5</v>
+      </c>
+      <c r="H73">
+        <v>181.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>-33</v>
+      </c>
+      <c r="K73">
+        <v>101.4</v>
+      </c>
+      <c r="L73">
+        <v>-134.4</v>
+      </c>
+      <c r="M73">
+        <v>129.8907228</v>
+      </c>
+      <c r="N73">
+        <v>-264.2907228</v>
+      </c>
+      <c r="O73">
+        <v>-58.143959016</v>
+      </c>
+      <c r="P73">
+        <v>-206.146763784</v>
+      </c>
+      <c r="Q73">
+        <v>-104.746763784</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2732220305548448</v>
+      </c>
+      <c r="T73">
+        <v>3.963687950281662</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.2276375045316169</v>
+      </c>
+      <c r="W73">
+        <v>0.2931598360821501</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-1.034715929689168</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2893778724792316</v>
+      </c>
+      <c r="C74">
+        <v>-384.0203539778745</v>
+      </c>
+      <c r="D74">
+        <v>156.0716460221255</v>
+      </c>
+      <c r="E74">
+        <v>-33.10800000000006</v>
+      </c>
+      <c r="F74">
+        <v>551.592</v>
+      </c>
+      <c r="G74">
+        <v>11.5</v>
+      </c>
+      <c r="H74">
+        <v>181.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>-33</v>
+      </c>
+      <c r="K74">
+        <v>101.4</v>
+      </c>
+      <c r="L74">
+        <v>-134.4</v>
+      </c>
+      <c r="M74">
+        <v>131.7201696</v>
+      </c>
+      <c r="N74">
+        <v>-266.1201696</v>
+      </c>
+      <c r="O74">
+        <v>-58.54643731199999</v>
+      </c>
+      <c r="P74">
+        <v>-207.573732288</v>
+      </c>
+      <c r="Q74">
+        <v>-106.173732288</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2815942459318036</v>
+      </c>
+      <c r="T74">
+        <v>4.105248234220293</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.2244758725242334</v>
+      </c>
+      <c r="W74">
+        <v>0.2924048383587869</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-1.020344875110152</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2913778724792316</v>
+      </c>
+      <c r="C75">
+        <v>-392.9171838982881</v>
+      </c>
+      <c r="D75">
+        <v>154.8358161017119</v>
+      </c>
+      <c r="E75">
+        <v>-25.447</v>
+      </c>
+      <c r="F75">
+        <v>559.253</v>
+      </c>
+      <c r="G75">
+        <v>11.5</v>
+      </c>
+      <c r="H75">
+        <v>181.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>-33</v>
+      </c>
+      <c r="K75">
+        <v>101.4</v>
+      </c>
+      <c r="L75">
+        <v>-134.4</v>
+      </c>
+      <c r="M75">
+        <v>133.5496164</v>
+      </c>
+      <c r="N75">
+        <v>-267.9496164</v>
+      </c>
+      <c r="O75">
+        <v>-58.948915608</v>
+      </c>
+      <c r="P75">
+        <v>-209.000700792</v>
+      </c>
+      <c r="Q75">
+        <v>-107.600700792</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2905866254107592</v>
+      </c>
+      <c r="T75">
+        <v>4.25729446511734</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.2214008605718465</v>
+      </c>
+      <c r="W75">
+        <v>0.291670525504557</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-1.006367548053848</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2933778724792316</v>
+      </c>
+      <c r="C76">
+        <v>-401.7945961072034</v>
+      </c>
+      <c r="D76">
+        <v>153.6194038927966</v>
+      </c>
+      <c r="E76">
+        <v>-17.78600000000006</v>
+      </c>
+      <c r="F76">
+        <v>566.914</v>
+      </c>
+      <c r="G76">
+        <v>11.5</v>
+      </c>
+      <c r="H76">
+        <v>181.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>-33</v>
+      </c>
+      <c r="K76">
+        <v>101.4</v>
+      </c>
+      <c r="L76">
+        <v>-134.4</v>
+      </c>
+      <c r="M76">
+        <v>135.3790632</v>
+      </c>
+      <c r="N76">
+        <v>-269.7790632</v>
+      </c>
+      <c r="O76">
+        <v>-59.35139390399999</v>
+      </c>
+      <c r="P76">
+        <v>-210.427669296</v>
+      </c>
+      <c r="Q76">
+        <v>-109.027669296</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3002707263880961</v>
+      </c>
+      <c r="T76">
+        <v>4.421036559929545</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.2184089570506054</v>
+      </c>
+      <c r="W76">
+        <v>0.2909560589436846</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.9927679865936612</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2953778724792316</v>
+      </c>
+      <c r="C77">
+        <v>-410.6530446822378</v>
+      </c>
+      <c r="D77">
+        <v>152.4219553177623</v>
+      </c>
+      <c r="E77">
+        <v>-10.125</v>
+      </c>
+      <c r="F77">
+        <v>574.575</v>
+      </c>
+      <c r="G77">
+        <v>11.5</v>
+      </c>
+      <c r="H77">
+        <v>181.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>-33</v>
+      </c>
+      <c r="K77">
+        <v>101.4</v>
+      </c>
+      <c r="L77">
+        <v>-134.4</v>
+      </c>
+      <c r="M77">
+        <v>137.20851</v>
+      </c>
+      <c r="N77">
+        <v>-271.60851</v>
+      </c>
+      <c r="O77">
+        <v>-59.7538722</v>
+      </c>
+      <c r="P77">
+        <v>-211.8546378</v>
+      </c>
+      <c r="Q77">
+        <v>-110.4546378</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.31072955544362</v>
+      </c>
+      <c r="T77">
+        <v>4.597878022326728</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.215496837623264</v>
+      </c>
+      <c r="W77">
+        <v>0.2902606448244355</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.9795310801057455</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2973778724792316</v>
+      </c>
+      <c r="C78">
+        <v>-419.4929696525483</v>
+      </c>
+      <c r="D78">
+        <v>151.2430303474518</v>
+      </c>
+      <c r="E78">
+        <v>-2.464000000000055</v>
+      </c>
+      <c r="F78">
+        <v>582.236</v>
+      </c>
+      <c r="G78">
+        <v>11.5</v>
+      </c>
+      <c r="H78">
+        <v>181.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>-33</v>
+      </c>
+      <c r="K78">
+        <v>101.4</v>
+      </c>
+      <c r="L78">
+        <v>-134.4</v>
+      </c>
+      <c r="M78">
+        <v>139.0379568</v>
+      </c>
+      <c r="N78">
+        <v>-273.4379568000001</v>
+      </c>
+      <c r="O78">
+        <v>-60.156350496</v>
+      </c>
+      <c r="P78">
+        <v>-213.281606304</v>
+      </c>
+      <c r="Q78">
+        <v>-111.881606304</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3220599535871042</v>
+      </c>
+      <c r="T78">
+        <v>4.789456273257009</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.2126613529176948</v>
+      </c>
+      <c r="W78">
+        <v>0.2895835310767456</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.9666425132622491</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2993778724792316</v>
+      </c>
+      <c r="C79">
+        <v>-428.314797537959</v>
+      </c>
+      <c r="D79">
+        <v>150.082202462041</v>
+      </c>
+      <c r="E79">
+        <v>5.197000000000003</v>
+      </c>
+      <c r="F79">
+        <v>589.897</v>
+      </c>
+      <c r="G79">
+        <v>11.5</v>
+      </c>
+      <c r="H79">
+        <v>181.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>-33</v>
+      </c>
+      <c r="K79">
+        <v>101.4</v>
+      </c>
+      <c r="L79">
+        <v>-134.4</v>
+      </c>
+      <c r="M79">
+        <v>140.8674036</v>
+      </c>
+      <c r="N79">
+        <v>-275.2674036</v>
+      </c>
+      <c r="O79">
+        <v>-60.558828792</v>
+      </c>
+      <c r="P79">
+        <v>-214.708574808</v>
+      </c>
+      <c r="Q79">
+        <v>-113.308574808</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3343756037430652</v>
+      </c>
+      <c r="T79">
+        <v>4.997693502529052</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.2098995171655169</v>
+      </c>
+      <c r="W79">
+        <v>0.2889240046991254</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.9540887143887131</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3013778724792316</v>
+      </c>
+      <c r="C80">
+        <v>-437.1189418634498</v>
+      </c>
+      <c r="D80">
+        <v>148.9390581365502</v>
+      </c>
+      <c r="E80">
+        <v>12.85799999999995</v>
+      </c>
+      <c r="F80">
+        <v>597.558</v>
+      </c>
+      <c r="G80">
+        <v>11.5</v>
+      </c>
+      <c r="H80">
+        <v>181.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>-33</v>
+      </c>
+      <c r="K80">
+        <v>101.4</v>
+      </c>
+      <c r="L80">
+        <v>-134.4</v>
+      </c>
+      <c r="M80">
+        <v>142.6968504</v>
+      </c>
+      <c r="N80">
+        <v>-277.0968504</v>
+      </c>
+      <c r="O80">
+        <v>-60.96130708799999</v>
+      </c>
+      <c r="P80">
+        <v>-216.135543312</v>
+      </c>
+      <c r="Q80">
+        <v>-114.735543312</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3478108584586591</v>
+      </c>
+      <c r="T80">
+        <v>5.224861389007645</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.2072084977146769</v>
+      </c>
+      <c r="W80">
+        <v>0.2882813892542648</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.941856807793986</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3033778724792316</v>
+      </c>
+      <c r="C81">
+        <v>-445.9058036503098</v>
+      </c>
+      <c r="D81">
+        <v>147.8131963496902</v>
+      </c>
+      <c r="E81">
+        <v>20.51900000000001</v>
+      </c>
+      <c r="F81">
+        <v>605.2190000000001</v>
+      </c>
+      <c r="G81">
+        <v>11.5</v>
+      </c>
+      <c r="H81">
+        <v>181.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>-33</v>
+      </c>
+      <c r="K81">
+        <v>101.4</v>
+      </c>
+      <c r="L81">
+        <v>-134.4</v>
+      </c>
+      <c r="M81">
+        <v>144.5262972</v>
+      </c>
+      <c r="N81">
+        <v>-278.9262972</v>
+      </c>
+      <c r="O81">
+        <v>-61.363785384</v>
+      </c>
+      <c r="P81">
+        <v>-217.562511816</v>
+      </c>
+      <c r="Q81">
+        <v>-116.162511816</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3625256612424049</v>
+      </c>
+      <c r="T81">
+        <v>5.473664312293725</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.2045856053385418</v>
+      </c>
+      <c r="W81">
+        <v>0.2876550425548438</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.9299345697206445</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3053778724792316</v>
+      </c>
+      <c r="C82">
+        <v>-454.6757718851824</v>
+      </c>
+      <c r="D82">
+        <v>146.7042281148176</v>
+      </c>
+      <c r="E82">
+        <v>28.17999999999995</v>
+      </c>
+      <c r="F82">
+        <v>612.88</v>
+      </c>
+      <c r="G82">
+        <v>11.5</v>
+      </c>
+      <c r="H82">
+        <v>181.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>-33</v>
+      </c>
+      <c r="K82">
+        <v>101.4</v>
+      </c>
+      <c r="L82">
+        <v>-134.4</v>
+      </c>
+      <c r="M82">
+        <v>146.355744</v>
+      </c>
+      <c r="N82">
+        <v>-280.755744</v>
+      </c>
+      <c r="O82">
+        <v>-61.76626368</v>
+      </c>
+      <c r="P82">
+        <v>-218.98948032</v>
+      </c>
+      <c r="Q82">
+        <v>-117.58948032</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.378711944304525</v>
+      </c>
+      <c r="T82">
+        <v>5.747347527908411</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.20202828527181</v>
+      </c>
+      <c r="W82">
+        <v>0.2870443545229083</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.9183103875991367</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3073778724792317</v>
+      </c>
+      <c r="C83">
+        <v>-463.4292239681527</v>
+      </c>
+      <c r="D83">
+        <v>145.6117760318474</v>
+      </c>
+      <c r="E83">
+        <v>35.84100000000001</v>
+      </c>
+      <c r="F83">
+        <v>620.5410000000001</v>
+      </c>
+      <c r="G83">
+        <v>11.5</v>
+      </c>
+      <c r="H83">
+        <v>181.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>-33</v>
+      </c>
+      <c r="K83">
+        <v>101.4</v>
+      </c>
+      <c r="L83">
+        <v>-134.4</v>
+      </c>
+      <c r="M83">
+        <v>148.1851908</v>
+      </c>
+      <c r="N83">
+        <v>-282.5851908</v>
+      </c>
+      <c r="O83">
+        <v>-62.168741976</v>
+      </c>
+      <c r="P83">
+        <v>-220.416448824</v>
+      </c>
+      <c r="Q83">
+        <v>-119.016448824</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3966020466363422</v>
+      </c>
+      <c r="T83">
+        <v>6.049839503061486</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.1995341089104296</v>
+      </c>
+      <c r="W83">
+        <v>0.2864487452078106</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.9069732223201348</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3093778724792316</v>
+      </c>
+      <c r="C84">
+        <v>-472.1665261409626</v>
+      </c>
+      <c r="D84">
+        <v>144.5354738590375</v>
+      </c>
+      <c r="E84">
+        <v>43.50200000000007</v>
+      </c>
+      <c r="F84">
+        <v>628.2020000000001</v>
+      </c>
+      <c r="G84">
+        <v>11.5</v>
+      </c>
+      <c r="H84">
+        <v>181.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>-33</v>
+      </c>
+      <c r="K84">
+        <v>101.4</v>
+      </c>
+      <c r="L84">
+        <v>-134.4</v>
+      </c>
+      <c r="M84">
+        <v>150.0146376</v>
+      </c>
+      <c r="N84">
+        <v>-284.4146376</v>
+      </c>
+      <c r="O84">
+        <v>-62.57122027200001</v>
+      </c>
+      <c r="P84">
+        <v>-221.843417328</v>
+      </c>
+      <c r="Q84">
+        <v>-120.443417328</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.416479938116139</v>
+      </c>
+      <c r="T84">
+        <v>6.385941697676013</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.197100766118839</v>
+      </c>
+      <c r="W84">
+        <v>0.2858676629491788</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.89591257326745</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3113778724792316</v>
+      </c>
+      <c r="C85">
+        <v>-480.8880338963751</v>
+      </c>
+      <c r="D85">
+        <v>143.474966103625</v>
+      </c>
+      <c r="E85">
+        <v>51.16300000000001</v>
+      </c>
+      <c r="F85">
+        <v>635.8630000000001</v>
+      </c>
+      <c r="G85">
+        <v>11.5</v>
+      </c>
+      <c r="H85">
+        <v>181.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>-33</v>
+      </c>
+      <c r="K85">
+        <v>101.4</v>
+      </c>
+      <c r="L85">
+        <v>-134.4</v>
+      </c>
+      <c r="M85">
+        <v>151.8440844</v>
+      </c>
+      <c r="N85">
+        <v>-286.2440844</v>
+      </c>
+      <c r="O85">
+        <v>-62.973698568</v>
+      </c>
+      <c r="P85">
+        <v>-223.270385832</v>
+      </c>
+      <c r="Q85">
+        <v>-121.870385832</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4386964050641472</v>
+      </c>
+      <c r="T85">
+        <v>6.761585326951073</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.1947260580933108</v>
+      </c>
+      <c r="W85">
+        <v>0.2853005826726827</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.8851184458786858</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3133778724792315</v>
+      </c>
+      <c r="C86">
+        <v>-489.5940923696464</v>
+      </c>
+      <c r="D86">
+        <v>142.4299076303536</v>
+      </c>
+      <c r="E86">
+        <v>58.82399999999996</v>
+      </c>
+      <c r="F86">
+        <v>643.524</v>
+      </c>
+      <c r="G86">
+        <v>11.5</v>
+      </c>
+      <c r="H86">
+        <v>181.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>-33</v>
+      </c>
+      <c r="K86">
+        <v>101.4</v>
+      </c>
+      <c r="L86">
+        <v>-134.4</v>
+      </c>
+      <c r="M86">
+        <v>153.6735312</v>
+      </c>
+      <c r="N86">
+        <v>-288.0735312</v>
+      </c>
+      <c r="O86">
+        <v>-63.376176864</v>
+      </c>
+      <c r="P86">
+        <v>-224.697354336</v>
+      </c>
+      <c r="Q86">
+        <v>-123.297354336</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4636899303806561</v>
+      </c>
+      <c r="T86">
+        <v>7.184184409885511</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.1924078907350572</v>
+      </c>
+      <c r="W86">
+        <v>0.2847470043075316</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.8745813215229874</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3153778724792316</v>
+      </c>
+      <c r="C87">
+        <v>-498.2850367130144</v>
+      </c>
+      <c r="D87">
+        <v>141.3999632869856</v>
+      </c>
+      <c r="E87">
+        <v>66.48500000000001</v>
+      </c>
+      <c r="F87">
+        <v>651.1850000000001</v>
+      </c>
+      <c r="G87">
+        <v>11.5</v>
+      </c>
+      <c r="H87">
+        <v>181.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>-33</v>
+      </c>
+      <c r="K87">
+        <v>101.4</v>
+      </c>
+      <c r="L87">
+        <v>-134.4</v>
+      </c>
+      <c r="M87">
+        <v>155.502978</v>
+      </c>
+      <c r="N87">
+        <v>-289.902978</v>
+      </c>
+      <c r="O87">
+        <v>-63.77865516</v>
+      </c>
+      <c r="P87">
+        <v>-226.12432284</v>
+      </c>
+      <c r="Q87">
+        <v>-124.72432284</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4920159257393666</v>
+      </c>
+      <c r="T87">
+        <v>7.663130037211212</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.1901442684911153</v>
+      </c>
+      <c r="W87">
+        <v>0.2842064513156783</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.8642921295050696</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3173778724792317</v>
+      </c>
+      <c r="C88">
+        <v>-506.9611924540542</v>
+      </c>
+      <c r="D88">
+        <v>140.3848075459458</v>
+      </c>
+      <c r="E88">
+        <v>74.14599999999996</v>
+      </c>
+      <c r="F88">
+        <v>658.846</v>
+      </c>
+      <c r="G88">
+        <v>11.5</v>
+      </c>
+      <c r="H88">
+        <v>181.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>-33</v>
+      </c>
+      <c r="K88">
+        <v>101.4</v>
+      </c>
+      <c r="L88">
+        <v>-134.4</v>
+      </c>
+      <c r="M88">
+        <v>157.3324248</v>
+      </c>
+      <c r="N88">
+        <v>-291.7324248</v>
+      </c>
+      <c r="O88">
+        <v>-64.18113345599998</v>
+      </c>
+      <c r="P88">
+        <v>-227.551291344</v>
+      </c>
+      <c r="Q88">
+        <v>-126.151291344</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5243884918636071</v>
+      </c>
+      <c r="T88">
+        <v>8.210496468440585</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.1879332886249395</v>
+      </c>
+      <c r="W88">
+        <v>0.2836784693236356</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.8542422210224523</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3193778724792317</v>
+      </c>
+      <c r="C89">
+        <v>-515.6228758387095</v>
+      </c>
+      <c r="D89">
+        <v>139.3841241612905</v>
+      </c>
+      <c r="E89">
+        <v>81.80700000000002</v>
+      </c>
+      <c r="F89">
+        <v>666.5070000000001</v>
+      </c>
+      <c r="G89">
+        <v>11.5</v>
+      </c>
+      <c r="H89">
+        <v>181.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>-33</v>
+      </c>
+      <c r="K89">
+        <v>101.4</v>
+      </c>
+      <c r="L89">
+        <v>-134.4</v>
+      </c>
+      <c r="M89">
+        <v>159.1618716</v>
+      </c>
+      <c r="N89">
+        <v>-293.5618716</v>
+      </c>
+      <c r="O89">
+        <v>-64.583611752</v>
+      </c>
+      <c r="P89">
+        <v>-228.978259848</v>
+      </c>
+      <c r="Q89">
+        <v>-127.578259848</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5617414527761924</v>
+      </c>
+      <c r="T89">
+        <v>8.842073119859093</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.1857731358821241</v>
+      </c>
+      <c r="W89">
+        <v>0.2831626248486513</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.8444233449187462</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3213778724792316</v>
+      </c>
+      <c r="C90">
+        <v>-524.2703941597542</v>
+      </c>
+      <c r="D90">
+        <v>138.3976058402458</v>
+      </c>
+      <c r="E90">
+        <v>89.46799999999996</v>
+      </c>
+      <c r="F90">
+        <v>674.168</v>
+      </c>
+      <c r="G90">
+        <v>11.5</v>
+      </c>
+      <c r="H90">
+        <v>181.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>-33</v>
+      </c>
+      <c r="K90">
+        <v>101.4</v>
+      </c>
+      <c r="L90">
+        <v>-134.4</v>
+      </c>
+      <c r="M90">
+        <v>160.9913184</v>
+      </c>
+      <c r="N90">
+        <v>-295.3913184</v>
+      </c>
+      <c r="O90">
+        <v>-64.98609004800001</v>
+      </c>
+      <c r="P90">
+        <v>-230.4052283520001</v>
+      </c>
+      <c r="Q90">
+        <v>-129.005228352</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6053199071742084</v>
+      </c>
+      <c r="T90">
+        <v>9.578912546514017</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.1836620775198273</v>
+      </c>
+      <c r="W90">
+        <v>0.2826585041117348</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.8348276250901243</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3233778724792316</v>
+      </c>
+      <c r="C91">
+        <v>-532.9040460714052</v>
+      </c>
+      <c r="D91">
+        <v>137.4249539285948</v>
+      </c>
+      <c r="E91">
+        <v>97.12900000000002</v>
+      </c>
+      <c r="F91">
+        <v>681.8290000000001</v>
+      </c>
+      <c r="G91">
+        <v>11.5</v>
+      </c>
+      <c r="H91">
+        <v>181.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>-33</v>
+      </c>
+      <c r="K91">
+        <v>101.4</v>
+      </c>
+      <c r="L91">
+        <v>-134.4</v>
+      </c>
+      <c r="M91">
+        <v>162.8207652</v>
+      </c>
+      <c r="N91">
+        <v>-297.2207652</v>
+      </c>
+      <c r="O91">
+        <v>-65.38856834399999</v>
+      </c>
+      <c r="P91">
+        <v>-231.832196856</v>
+      </c>
+      <c r="Q91">
+        <v>-130.432196856</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6568217169173183</v>
+      </c>
+      <c r="T91">
+        <v>10.44972277801529</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.1815984586712899</v>
+      </c>
+      <c r="W91">
+        <v>0.2821657119307041</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.8254475394149541</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3253778724792316</v>
+      </c>
+      <c r="C92">
+        <v>-541.5241218907607</v>
+      </c>
+      <c r="D92">
+        <v>136.4658781092393</v>
+      </c>
+      <c r="E92">
+        <v>104.79</v>
+      </c>
+      <c r="F92">
+        <v>689.49</v>
+      </c>
+      <c r="G92">
+        <v>11.5</v>
+      </c>
+      <c r="H92">
+        <v>181.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>-33</v>
+      </c>
+      <c r="K92">
+        <v>101.4</v>
+      </c>
+      <c r="L92">
+        <v>-134.4</v>
+      </c>
+      <c r="M92">
+        <v>164.650212</v>
+      </c>
+      <c r="N92">
+        <v>-299.050212</v>
+      </c>
+      <c r="O92">
+        <v>-65.79104663999999</v>
+      </c>
+      <c r="P92">
+        <v>-233.25916536</v>
+      </c>
+      <c r="Q92">
+        <v>-131.85916536</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7186238886090501</v>
+      </c>
+      <c r="T92">
+        <v>11.49469505581682</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.1795806980193867</v>
+      </c>
+      <c r="W92">
+        <v>0.2816838706870295</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.8162759000881212</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3273778724792317</v>
+      </c>
+      <c r="C93">
+        <v>-550.1309038867041</v>
+      </c>
+      <c r="D93">
+        <v>135.520096113296</v>
+      </c>
+      <c r="E93">
+        <v>112.451</v>
+      </c>
+      <c r="F93">
+        <v>697.1510000000001</v>
+      </c>
+      <c r="G93">
+        <v>11.5</v>
+      </c>
+      <c r="H93">
+        <v>181.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>-33</v>
+      </c>
+      <c r="K93">
+        <v>101.4</v>
+      </c>
+      <c r="L93">
+        <v>-134.4</v>
+      </c>
+      <c r="M93">
+        <v>166.4796588</v>
+      </c>
+      <c r="N93">
+        <v>-300.8796588</v>
+      </c>
+      <c r="O93">
+        <v>-66.19352493599999</v>
+      </c>
+      <c r="P93">
+        <v>-234.686133864</v>
+      </c>
+      <c r="Q93">
+        <v>-133.286133864</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7941598762322781</v>
+      </c>
+      <c r="T93">
+        <v>12.77188339535203</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.1776072837554373</v>
+      </c>
+      <c r="W93">
+        <v>0.2812126193607985</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.8073058352519877</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3293778724792316</v>
+      </c>
+      <c r="C94">
+        <v>-558.7246665568759</v>
+      </c>
+      <c r="D94">
+        <v>134.5873334431241</v>
+      </c>
+      <c r="E94">
+        <v>120.112</v>
+      </c>
+      <c r="F94">
+        <v>704.812</v>
+      </c>
+      <c r="G94">
+        <v>11.5</v>
+      </c>
+      <c r="H94">
+        <v>181.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>-33</v>
+      </c>
+      <c r="K94">
+        <v>101.4</v>
+      </c>
+      <c r="L94">
+        <v>-134.4</v>
+      </c>
+      <c r="M94">
+        <v>168.3091056</v>
+      </c>
+      <c r="N94">
+        <v>-302.7091056</v>
+      </c>
+      <c r="O94">
+        <v>-66.596003232</v>
+      </c>
+      <c r="P94">
+        <v>-236.1131023680001</v>
+      </c>
+      <c r="Q94">
+        <v>-134.7131023680001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8885798607613131</v>
+      </c>
+      <c r="T94">
+        <v>14.36836881977103</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.1756767698015739</v>
+      </c>
+      <c r="W94">
+        <v>0.2807516126286159</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.7985307718253363</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3313778724792316</v>
+      </c>
+      <c r="C95">
+        <v>-567.3056768932877</v>
+      </c>
+      <c r="D95">
+        <v>133.6673231067124</v>
+      </c>
+      <c r="E95">
+        <v>127.773</v>
+      </c>
+      <c r="F95">
+        <v>712.4730000000001</v>
+      </c>
+      <c r="G95">
+        <v>11.5</v>
+      </c>
+      <c r="H95">
+        <v>181.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>-33</v>
+      </c>
+      <c r="K95">
+        <v>101.4</v>
+      </c>
+      <c r="L95">
+        <v>-134.4</v>
+      </c>
+      <c r="M95">
+        <v>170.1385524</v>
+      </c>
+      <c r="N95">
+        <v>-304.5385524000001</v>
+      </c>
+      <c r="O95">
+        <v>-66.99848152800001</v>
+      </c>
+      <c r="P95">
+        <v>-237.5400708720001</v>
+      </c>
+      <c r="Q95">
+        <v>-136.1400708720001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.009976983727215</v>
+      </c>
+      <c r="T95">
+        <v>16.42099293688118</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.1737877722768258</v>
+      </c>
+      <c r="W95">
+        <v>0.280300520019706</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.7899444194401175</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3333778724792316</v>
+      </c>
+      <c r="C96">
+        <v>-575.8741946371135</v>
+      </c>
+      <c r="D96">
+        <v>132.7598053628864</v>
+      </c>
+      <c r="E96">
+        <v>135.434</v>
+      </c>
+      <c r="F96">
+        <v>720.134</v>
+      </c>
+      <c r="G96">
+        <v>11.5</v>
+      </c>
+      <c r="H96">
+        <v>181.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>-33</v>
+      </c>
+      <c r="K96">
+        <v>101.4</v>
+      </c>
+      <c r="L96">
+        <v>-134.4</v>
+      </c>
+      <c r="M96">
+        <v>171.9679992</v>
+      </c>
+      <c r="N96">
+        <v>-306.3679992</v>
+      </c>
+      <c r="O96">
+        <v>-67.40095982399998</v>
+      </c>
+      <c r="P96">
+        <v>-238.967039376</v>
+      </c>
+      <c r="Q96">
+        <v>-137.567039376</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.171839814348418</v>
+      </c>
+      <c r="T96">
+        <v>19.15782509302805</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.1719389661887745</v>
+      </c>
+      <c r="W96">
+        <v>0.2798590251258793</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.7815407554035203</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3353778724792316</v>
+      </c>
+      <c r="C97">
+        <v>-584.430472523175</v>
+      </c>
+      <c r="D97">
+        <v>131.8645274768251</v>
+      </c>
+      <c r="E97">
+        <v>143.095</v>
+      </c>
+      <c r="F97">
+        <v>727.7950000000001</v>
+      </c>
+      <c r="G97">
+        <v>11.5</v>
+      </c>
+      <c r="H97">
+        <v>181.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>-33</v>
+      </c>
+      <c r="K97">
+        <v>101.4</v>
+      </c>
+      <c r="L97">
+        <v>-134.4</v>
+      </c>
+      <c r="M97">
+        <v>173.797446</v>
+      </c>
+      <c r="N97">
+        <v>-308.197446</v>
+      </c>
+      <c r="O97">
+        <v>-67.80343812</v>
+      </c>
+      <c r="P97">
+        <v>-240.39400788</v>
+      </c>
+      <c r="Q97">
+        <v>-138.99400788</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.398447777218102</v>
+      </c>
+      <c r="T97">
+        <v>22.98939011163367</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.1701290823341558</v>
+      </c>
+      <c r="W97">
+        <v>0.2794268248613964</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.7733140106097989</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3373778724792316</v>
+      </c>
+      <c r="C98">
+        <v>-592.9747565145966</v>
+      </c>
+      <c r="D98">
+        <v>130.9812434854034</v>
+      </c>
+      <c r="E98">
+        <v>150.756</v>
+      </c>
+      <c r="F98">
+        <v>735.456</v>
+      </c>
+      <c r="G98">
+        <v>11.5</v>
+      </c>
+      <c r="H98">
+        <v>181.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>-33</v>
+      </c>
+      <c r="K98">
+        <v>101.4</v>
+      </c>
+      <c r="L98">
+        <v>-134.4</v>
+      </c>
+      <c r="M98">
+        <v>175.6268928</v>
+      </c>
+      <c r="N98">
+        <v>-310.0268928</v>
+      </c>
+      <c r="O98">
+        <v>-68.20591641599999</v>
+      </c>
+      <c r="P98">
+        <v>-241.8209763840001</v>
+      </c>
+      <c r="Q98">
+        <v>-140.4209763840001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.738359721522623</v>
+      </c>
+      <c r="T98">
+        <v>28.73673763954202</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.168356904393175</v>
+      </c>
+      <c r="W98">
+        <v>0.2790036287690902</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.765258656332614</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3393778724792316</v>
+      </c>
+      <c r="C99">
+        <v>-601.5072860280969</v>
+      </c>
+      <c r="D99">
+        <v>130.109713971903</v>
+      </c>
+      <c r="E99">
+        <v>158.4169999999999</v>
+      </c>
+      <c r="F99">
+        <v>743.117</v>
+      </c>
+      <c r="G99">
+        <v>11.5</v>
+      </c>
+      <c r="H99">
+        <v>181.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>-33</v>
+      </c>
+      <c r="K99">
+        <v>101.4</v>
+      </c>
+      <c r="L99">
+        <v>-134.4</v>
+      </c>
+      <c r="M99">
+        <v>177.4563396</v>
+      </c>
+      <c r="N99">
+        <v>-311.8563396</v>
+      </c>
+      <c r="O99">
+        <v>-68.60839471199999</v>
+      </c>
+      <c r="P99">
+        <v>-243.247944888</v>
+      </c>
+      <c r="Q99">
+        <v>-141.847944888</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.304879628696832</v>
+      </c>
+      <c r="T99">
+        <v>38.31565018605604</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.1666212662035546</v>
+      </c>
+      <c r="W99">
+        <v>0.2785891583694088</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.7573693918343394</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3413778724792316</v>
+      </c>
+      <c r="C100">
+        <v>-610.0282941503422</v>
+      </c>
+      <c r="D100">
+        <v>129.2497058496578</v>
+      </c>
+      <c r="E100">
+        <v>166.078</v>
+      </c>
+      <c r="F100">
+        <v>750.778</v>
+      </c>
+      <c r="G100">
+        <v>11.5</v>
+      </c>
+      <c r="H100">
+        <v>181.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>-33</v>
+      </c>
+      <c r="K100">
+        <v>101.4</v>
+      </c>
+      <c r="L100">
+        <v>-134.4</v>
+      </c>
+      <c r="M100">
+        <v>179.2857864</v>
+      </c>
+      <c r="N100">
+        <v>-313.6857864</v>
+      </c>
+      <c r="O100">
+        <v>-69.01087300799999</v>
+      </c>
+      <c r="P100">
+        <v>-244.674913392</v>
+      </c>
+      <c r="Q100">
+        <v>-143.274913392</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.437919443045248</v>
+      </c>
+      <c r="T100">
+        <v>57.47347527908406</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.1649210492014776</v>
+      </c>
+      <c r="W100">
+        <v>0.2781831465493129</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.7496411327339889</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3433778724792316</v>
+      </c>
+      <c r="C101">
+        <v>-618.5380078457763</v>
+      </c>
+      <c r="D101">
+        <v>128.4009921542236</v>
+      </c>
+      <c r="E101">
+        <v>173.7389999999999</v>
+      </c>
+      <c r="F101">
+        <v>758.439</v>
+      </c>
+      <c r="G101">
+        <v>11.5</v>
+      </c>
+      <c r="H101">
+        <v>181.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>-33</v>
+      </c>
+      <c r="K101">
+        <v>101.4</v>
+      </c>
+      <c r="L101">
+        <v>-134.4</v>
+      </c>
+      <c r="M101">
+        <v>181.1152332</v>
+      </c>
+      <c r="N101">
+        <v>-315.5152332</v>
+      </c>
+      <c r="O101">
+        <v>-69.41335130399999</v>
+      </c>
+      <c r="P101">
+        <v>-246.101881896</v>
+      </c>
+      <c r="Q101">
+        <v>-144.701881896</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.837038886090495</v>
+      </c>
+      <c r="T101">
+        <v>114.9469505581681</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.1632551800176243</v>
+      </c>
+      <c r="W101">
+        <v>0.2777853369882087</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.7420690000801102</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_recreation.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_recreation.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,13 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1103911750302471</v>
+      </c>
+      <c r="C2">
+        <v>559.9749874676585</v>
+      </c>
+      <c r="D2">
+        <v>540.7379874676585</v>
       </c>
       <c r="E2">
-        <v>-629.4</v>
+        <v>-618.337</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>11.063</v>
       </c>
       <c r="G2">
         <v>30.3</v>
@@ -1436,43 +1445,45 @@
         <v>-102.9875</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.6086554</v>
       </c>
       <c r="N2">
-        <v>-102.9875</v>
+        <v>-105.5961554</v>
       </c>
       <c r="O2">
-        <v>-22.65725</v>
+        <v>-23.231154188</v>
       </c>
       <c r="P2">
-        <v>-80.33024999999999</v>
+        <v>-82.365001212</v>
       </c>
       <c r="Q2">
-        <v>34.16975000000001</v>
+        <v>32.134998788</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.08843734418757074</v>
+      </c>
+      <c r="T2">
+        <v>0.9846961706136432</v>
       </c>
       <c r="U2">
-        <v>0.0503</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2358</v>
+      </c>
+      <c r="V2">
+        <v>-8.685413182592072</v>
+      </c>
+      <c r="W2">
+        <v>2.283820428455211</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-39.47915082996397</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1480,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1103911750302471</v>
+        <v>0.1122911750302471</v>
       </c>
       <c r="C3">
-        <v>559.9749874676585</v>
+        <v>533.460280143774</v>
       </c>
       <c r="D3">
-        <v>540.7379874676585</v>
+        <v>525.286280143774</v>
       </c>
       <c r="E3">
-        <v>-618.337</v>
+        <v>-607.274</v>
       </c>
       <c r="F3">
-        <v>11.063</v>
+        <v>22.126</v>
       </c>
       <c r="G3">
         <v>30.3</v>
@@ -1516,37 +1527,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M3">
-        <v>2.6086554</v>
+        <v>5.217310800000001</v>
       </c>
       <c r="N3">
-        <v>-105.5961554</v>
+        <v>-108.2048108</v>
       </c>
       <c r="O3">
-        <v>-23.231154188</v>
+        <v>-23.805058376</v>
       </c>
       <c r="P3">
-        <v>-82.365001212</v>
+        <v>-84.399752424</v>
       </c>
       <c r="Q3">
-        <v>32.134998788</v>
+        <v>30.100247576</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08843734418757074</v>
+        <v>0.08887241912826024</v>
       </c>
       <c r="T3">
-        <v>0.9846961706136432</v>
+        <v>0.9947440907219458</v>
       </c>
       <c r="U3">
         <v>0.2358</v>
       </c>
       <c r="V3">
-        <v>-8.685413182592072</v>
+        <v>-4.342706591296036</v>
       </c>
       <c r="W3">
-        <v>2.283820428455211</v>
+        <v>1.259810214227605</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1554,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-39.47915082996397</v>
+        <v>-19.73957541498199</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1562,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1122911750302471</v>
+        <v>0.1141911750302471</v>
       </c>
       <c r="C4">
-        <v>533.460280143774</v>
+        <v>507.8041117732676</v>
       </c>
       <c r="D4">
-        <v>525.286280143774</v>
+        <v>510.6931117732677</v>
       </c>
       <c r="E4">
-        <v>-607.274</v>
+        <v>-596.211</v>
       </c>
       <c r="F4">
-        <v>22.126</v>
+        <v>33.189</v>
       </c>
       <c r="G4">
         <v>30.3</v>
@@ -1598,37 +1609,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M4">
-        <v>5.217310800000001</v>
+        <v>7.825966200000001</v>
       </c>
       <c r="N4">
-        <v>-108.2048108</v>
+        <v>-110.8134662</v>
       </c>
       <c r="O4">
-        <v>-23.805058376</v>
+        <v>-24.378962564</v>
       </c>
       <c r="P4">
-        <v>-84.399752424</v>
+        <v>-86.43450363599999</v>
       </c>
       <c r="Q4">
-        <v>30.100247576</v>
+        <v>28.06549636400001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08887241912826024</v>
+        <v>0.08931646468628354</v>
       </c>
       <c r="T4">
-        <v>0.9947440907219458</v>
+        <v>1.004999184440728</v>
       </c>
       <c r="U4">
         <v>0.2358</v>
       </c>
       <c r="V4">
-        <v>-4.342706591296036</v>
+        <v>-2.895137727530691</v>
       </c>
       <c r="W4">
-        <v>1.259810214227605</v>
+        <v>0.9184734761517369</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1636,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-19.73957541498199</v>
+        <v>-13.15971694332132</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1644,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1141911750302471</v>
+        <v>0.1160911750302471</v>
       </c>
       <c r="C5">
-        <v>507.8041117732676</v>
+        <v>482.9368623500409</v>
       </c>
       <c r="D5">
-        <v>510.6931117732677</v>
+        <v>496.888862350041</v>
       </c>
       <c r="E5">
-        <v>-596.211</v>
+        <v>-585.148</v>
       </c>
       <c r="F5">
-        <v>33.189</v>
+        <v>44.252</v>
       </c>
       <c r="G5">
         <v>30.3</v>
@@ -1680,37 +1691,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M5">
-        <v>7.825966200000001</v>
+        <v>10.4346216</v>
       </c>
       <c r="N5">
-        <v>-110.8134662</v>
+        <v>-113.4221216</v>
       </c>
       <c r="O5">
-        <v>-24.378962564</v>
+        <v>-24.952866752</v>
       </c>
       <c r="P5">
-        <v>-86.43450363599999</v>
+        <v>-88.46925484799999</v>
       </c>
       <c r="Q5">
-        <v>28.06549636400001</v>
+        <v>26.03074515200001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08931646468628354</v>
+        <v>0.08976976119343233</v>
       </c>
       <c r="T5">
-        <v>1.004999184440728</v>
+        <v>1.01546792594532</v>
       </c>
       <c r="U5">
         <v>0.2358</v>
       </c>
       <c r="V5">
-        <v>-2.895137727530691</v>
+        <v>-2.171353295648018</v>
       </c>
       <c r="W5">
-        <v>0.9184734761517369</v>
+        <v>0.7478051071138027</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1718,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-13.15971694332132</v>
+        <v>-9.869787707490991</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1726,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1160911750302471</v>
+        <v>0.1179911750302471</v>
       </c>
       <c r="C6">
-        <v>482.9368623500409</v>
+        <v>458.7962411855494</v>
       </c>
       <c r="D6">
-        <v>496.888862350041</v>
+        <v>483.8112411855494</v>
       </c>
       <c r="E6">
-        <v>-585.148</v>
+        <v>-574.085</v>
       </c>
       <c r="F6">
-        <v>44.252</v>
+        <v>55.315</v>
       </c>
       <c r="G6">
         <v>30.3</v>
@@ -1762,37 +1773,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M6">
-        <v>10.4346216</v>
+        <v>13.043277</v>
       </c>
       <c r="N6">
-        <v>-113.4221216</v>
+        <v>-116.030777</v>
       </c>
       <c r="O6">
-        <v>-24.952866752</v>
+        <v>-25.52677094</v>
       </c>
       <c r="P6">
-        <v>-88.46925484799999</v>
+        <v>-90.50400605999999</v>
       </c>
       <c r="Q6">
-        <v>26.03074515200001</v>
+        <v>23.99599394000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08976976119343233</v>
+        <v>0.09023260078494214</v>
       </c>
       <c r="T6">
-        <v>1.01546792594532</v>
+        <v>1.026157062007902</v>
       </c>
       <c r="U6">
         <v>0.2358</v>
       </c>
       <c r="V6">
-        <v>-2.171353295648018</v>
+        <v>-1.737082636518415</v>
       </c>
       <c r="W6">
-        <v>0.7478051071138027</v>
+        <v>0.6454040856910422</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1800,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-9.869787707490991</v>
+        <v>-7.895830165992795</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1808,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1179911750302471</v>
+        <v>0.1198911750302471</v>
       </c>
       <c r="C7">
-        <v>458.7962411855494</v>
+        <v>435.3263471407827</v>
       </c>
       <c r="D7">
-        <v>483.8112411855494</v>
+        <v>471.4043471407826</v>
       </c>
       <c r="E7">
-        <v>-574.085</v>
+        <v>-563.0219999999999</v>
       </c>
       <c r="F7">
-        <v>55.315</v>
+        <v>66.378</v>
       </c>
       <c r="G7">
         <v>30.3</v>
@@ -1844,37 +1855,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M7">
-        <v>13.043277</v>
+        <v>15.6519324</v>
       </c>
       <c r="N7">
-        <v>-116.030777</v>
+        <v>-118.6394324</v>
       </c>
       <c r="O7">
-        <v>-25.52677094</v>
+        <v>-26.100675128</v>
       </c>
       <c r="P7">
-        <v>-90.50400605999999</v>
+        <v>-92.538757272</v>
       </c>
       <c r="Q7">
-        <v>23.99599394000001</v>
+        <v>21.961242728</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09023260078494214</v>
+        <v>0.09070528802733514</v>
       </c>
       <c r="T7">
-        <v>1.026157062007902</v>
+        <v>1.037073626497348</v>
       </c>
       <c r="U7">
         <v>0.2358</v>
       </c>
       <c r="V7">
-        <v>-1.737082636518415</v>
+        <v>-1.447568863765345</v>
       </c>
       <c r="W7">
-        <v>0.6454040856910422</v>
+        <v>0.5771367380758685</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1882,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-7.895830165992795</v>
+        <v>-6.579858471660661</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1890,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1198911750302471</v>
+        <v>0.1217911750302471</v>
       </c>
       <c r="C8">
-        <v>435.3263471407827</v>
+        <v>412.47686983982</v>
       </c>
       <c r="D8">
-        <v>471.4043471407826</v>
+        <v>459.6178698398199</v>
       </c>
       <c r="E8">
-        <v>-563.0219999999999</v>
+        <v>-551.9589999999999</v>
       </c>
       <c r="F8">
-        <v>66.378</v>
+        <v>77.44099999999999</v>
       </c>
       <c r="G8">
         <v>30.3</v>
@@ -1926,37 +1937,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M8">
-        <v>15.6519324</v>
+        <v>18.2605878</v>
       </c>
       <c r="N8">
-        <v>-118.6394324</v>
+        <v>-121.2480878</v>
       </c>
       <c r="O8">
-        <v>-26.100675128</v>
+        <v>-26.674579316</v>
       </c>
       <c r="P8">
-        <v>-92.538757272</v>
+        <v>-94.573508484</v>
       </c>
       <c r="Q8">
-        <v>21.961242728</v>
+        <v>19.926491516</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09070528802733514</v>
+        <v>0.09118814058676886</v>
       </c>
       <c r="T8">
-        <v>1.037073626497348</v>
+        <v>1.048224955814523</v>
       </c>
       <c r="U8">
         <v>0.2358</v>
       </c>
       <c r="V8">
-        <v>-1.447568863765345</v>
+        <v>-1.240773311798868</v>
       </c>
       <c r="W8">
-        <v>0.5771367380758685</v>
+        <v>0.528374346922173</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1964,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-6.579858471660661</v>
+        <v>-5.639878689994853</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1972,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1217911750302471</v>
+        <v>0.1236911750302472</v>
       </c>
       <c r="C9">
-        <v>412.47686983982</v>
+        <v>390.202407792206</v>
       </c>
       <c r="D9">
-        <v>459.6178698398199</v>
+        <v>448.406407792206</v>
       </c>
       <c r="E9">
-        <v>-551.9589999999999</v>
+        <v>-540.896</v>
       </c>
       <c r="F9">
-        <v>77.441</v>
+        <v>88.504</v>
       </c>
       <c r="G9">
         <v>30.3</v>
@@ -2008,37 +2019,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M9">
-        <v>18.2605878</v>
+        <v>20.8692432</v>
       </c>
       <c r="N9">
-        <v>-121.2480878</v>
+        <v>-123.8567432</v>
       </c>
       <c r="O9">
-        <v>-26.674579316</v>
+        <v>-27.248483504</v>
       </c>
       <c r="P9">
-        <v>-94.573508484</v>
+        <v>-96.608259696</v>
       </c>
       <c r="Q9">
-        <v>19.926491516</v>
+        <v>17.891740304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09118814058676886</v>
+        <v>0.09168148994097286</v>
       </c>
       <c r="T9">
-        <v>1.048224955814523</v>
+        <v>1.059618705334247</v>
       </c>
       <c r="U9">
         <v>0.2358</v>
       </c>
       <c r="V9">
-        <v>-1.240773311798868</v>
+        <v>-1.085676647824009</v>
       </c>
       <c r="W9">
-        <v>0.528374346922173</v>
+        <v>0.4918025535569013</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2046,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-5.639878689994853</v>
+        <v>-4.934893853745495</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2054,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1236911750302472</v>
+        <v>0.1255911750302471</v>
       </c>
       <c r="C10">
-        <v>390.202407792206</v>
+        <v>368.4618839371906</v>
       </c>
       <c r="D10">
-        <v>448.406407792206</v>
+        <v>437.7288839371906</v>
       </c>
       <c r="E10">
-        <v>-540.896</v>
+        <v>-529.833</v>
       </c>
       <c r="F10">
-        <v>88.504</v>
+        <v>99.56699999999999</v>
       </c>
       <c r="G10">
         <v>30.3</v>
@@ -2090,37 +2101,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M10">
-        <v>20.8692432</v>
+        <v>23.4778986</v>
       </c>
       <c r="N10">
-        <v>-123.8567432</v>
+        <v>-126.4653986</v>
       </c>
       <c r="O10">
-        <v>-27.248483504</v>
+        <v>-27.822387692</v>
       </c>
       <c r="P10">
-        <v>-96.608259696</v>
+        <v>-98.64301090800001</v>
       </c>
       <c r="Q10">
-        <v>17.891740304</v>
+        <v>15.85698909199999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09168148994097286</v>
+        <v>0.0921856821381264</v>
       </c>
       <c r="T10">
-        <v>1.059618705334247</v>
+        <v>1.071262866931326</v>
       </c>
       <c r="U10">
         <v>0.2358</v>
       </c>
       <c r="V10">
-        <v>-1.085676647824009</v>
+        <v>-0.9650459091768973</v>
       </c>
       <c r="W10">
-        <v>0.4918025535569013</v>
+        <v>0.4633578253839124</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2128,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-4.934893853745495</v>
+        <v>-4.386572314440442</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2136,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1255911750302471</v>
+        <v>0.1274911750302472</v>
       </c>
       <c r="C11">
-        <v>368.4618839371906</v>
+        <v>347.2180427487424</v>
       </c>
       <c r="D11">
-        <v>437.7288839371906</v>
+        <v>427.5480427487424</v>
       </c>
       <c r="E11">
-        <v>-529.833</v>
+        <v>-518.77</v>
       </c>
       <c r="F11">
-        <v>99.56699999999999</v>
+        <v>110.63</v>
       </c>
       <c r="G11">
         <v>30.3</v>
@@ -2172,37 +2183,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M11">
-        <v>23.4778986</v>
+        <v>26.086554</v>
       </c>
       <c r="N11">
-        <v>-126.4653986</v>
+        <v>-129.074054</v>
       </c>
       <c r="O11">
-        <v>-27.822387692</v>
+        <v>-28.39629188</v>
       </c>
       <c r="P11">
-        <v>-98.64301090800001</v>
+        <v>-100.67776212</v>
       </c>
       <c r="Q11">
-        <v>15.85698909199999</v>
+        <v>13.82223788</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0921856821381264</v>
+        <v>0.09270107860632781</v>
       </c>
       <c r="T11">
-        <v>1.071262866931326</v>
+        <v>1.083165787675007</v>
       </c>
       <c r="U11">
         <v>0.2358</v>
       </c>
       <c r="V11">
-        <v>-0.9650459091768973</v>
+        <v>-0.8685413182592076</v>
       </c>
       <c r="W11">
-        <v>0.4633578253839124</v>
+        <v>0.4406020428455211</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2210,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-4.386572314440442</v>
+        <v>-3.947915082996397</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2218,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1274911750302472</v>
+        <v>0.1293911750302472</v>
       </c>
       <c r="C12">
-        <v>347.2180427487424</v>
+        <v>326.4370159243955</v>
       </c>
       <c r="D12">
-        <v>427.5480427487424</v>
+        <v>417.8300159243955</v>
       </c>
       <c r="E12">
-        <v>-518.77</v>
+        <v>-507.707</v>
       </c>
       <c r="F12">
-        <v>110.63</v>
+        <v>121.693</v>
       </c>
       <c r="G12">
         <v>30.3</v>
@@ -2254,37 +2265,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M12">
-        <v>26.086554</v>
+        <v>28.6952094</v>
       </c>
       <c r="N12">
-        <v>-129.074054</v>
+        <v>-131.6827094</v>
       </c>
       <c r="O12">
-        <v>-28.39629188</v>
+        <v>-28.970196068</v>
       </c>
       <c r="P12">
-        <v>-100.67776212</v>
+        <v>-102.712513332</v>
       </c>
       <c r="Q12">
-        <v>13.82223788</v>
+        <v>11.78748666800001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09270107860632781</v>
+        <v>0.09322805701763487</v>
       </c>
       <c r="T12">
-        <v>1.083165787675007</v>
+        <v>1.095336189783715</v>
       </c>
       <c r="U12">
         <v>0.2358</v>
       </c>
       <c r="V12">
-        <v>-0.8685413182592074</v>
+        <v>-0.7895830165992794</v>
       </c>
       <c r="W12">
-        <v>0.4406020428455211</v>
+        <v>0.4219836753141101</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2292,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-3.947915082996397</v>
+        <v>-3.589013711814906</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2300,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1293911750302472</v>
+        <v>0.1312911750302471</v>
       </c>
       <c r="C13">
-        <v>326.4370159243955</v>
+        <v>306.0879459882241</v>
       </c>
       <c r="D13">
-        <v>417.8300159243955</v>
+        <v>408.5439459882241</v>
       </c>
       <c r="E13">
-        <v>-507.707</v>
+        <v>-496.644</v>
       </c>
       <c r="F13">
-        <v>121.693</v>
+        <v>132.756</v>
       </c>
       <c r="G13">
         <v>30.3</v>
@@ -2336,37 +2347,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M13">
-        <v>28.6952094</v>
+        <v>31.3038648</v>
       </c>
       <c r="N13">
-        <v>-131.6827094</v>
+        <v>-134.2913648</v>
       </c>
       <c r="O13">
-        <v>-28.970196068</v>
+        <v>-29.544100256</v>
       </c>
       <c r="P13">
-        <v>-102.712513332</v>
+        <v>-104.747264544</v>
       </c>
       <c r="Q13">
-        <v>11.78748666800001</v>
+        <v>9.752735456000011</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09322805701763487</v>
+        <v>0.09376701221101709</v>
       </c>
       <c r="T13">
-        <v>1.095336189783715</v>
+        <v>1.107783191940349</v>
       </c>
       <c r="U13">
         <v>0.2358</v>
       </c>
       <c r="V13">
-        <v>-0.7895830165992794</v>
+        <v>-0.7237844318826727</v>
       </c>
       <c r="W13">
-        <v>0.4219836753141101</v>
+        <v>0.4064683690379343</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2374,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-3.589013711814906</v>
+        <v>-3.28992923583033</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2382,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1312911750302471</v>
+        <v>0.1331911750302472</v>
       </c>
       <c r="C14">
-        <v>306.0879459882241</v>
+        <v>286.1426589940399</v>
       </c>
       <c r="D14">
-        <v>408.5439459882241</v>
+        <v>399.66165899404</v>
       </c>
       <c r="E14">
-        <v>-496.644</v>
+        <v>-485.581</v>
       </c>
       <c r="F14">
-        <v>132.756</v>
+        <v>143.819</v>
       </c>
       <c r="G14">
         <v>30.3</v>
@@ -2418,37 +2429,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M14">
-        <v>31.3038648</v>
+        <v>33.9125202</v>
       </c>
       <c r="N14">
-        <v>-134.2913648</v>
+        <v>-136.9000202</v>
       </c>
       <c r="O14">
-        <v>-29.544100256</v>
+        <v>-30.118004444</v>
       </c>
       <c r="P14">
-        <v>-104.747264544</v>
+        <v>-106.782015756</v>
       </c>
       <c r="Q14">
-        <v>9.752735456000011</v>
+        <v>7.717984244000007</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09376701221101709</v>
+        <v>0.09431835717895981</v>
       </c>
       <c r="T14">
-        <v>1.107783191940349</v>
+        <v>1.120516332077594</v>
       </c>
       <c r="U14">
         <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>-0.7237844318826727</v>
+        <v>-0.6681087063532365</v>
       </c>
       <c r="W14">
-        <v>0.4064683690379343</v>
+        <v>0.3933400329580932</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2456,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-3.28992923583033</v>
+        <v>-3.036857756151075</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2464,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1331911750302472</v>
+        <v>0.1350911750302471</v>
       </c>
       <c r="C15">
-        <v>286.1426589940399</v>
+        <v>266.5753790152914</v>
       </c>
       <c r="D15">
-        <v>399.66165899404</v>
+        <v>391.1573790152914</v>
       </c>
       <c r="E15">
-        <v>-485.581</v>
+        <v>-474.518</v>
       </c>
       <c r="F15">
-        <v>143.819</v>
+        <v>154.882</v>
       </c>
       <c r="G15">
         <v>30.3</v>
@@ -2500,37 +2511,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M15">
-        <v>33.9125202</v>
+        <v>36.5211756</v>
       </c>
       <c r="N15">
-        <v>-136.9000202</v>
+        <v>-139.5086756</v>
       </c>
       <c r="O15">
-        <v>-30.118004444</v>
+        <v>-30.691908632</v>
       </c>
       <c r="P15">
-        <v>-106.782015756</v>
+        <v>-108.816766968</v>
       </c>
       <c r="Q15">
-        <v>7.717984244000007</v>
+        <v>5.683233032000004</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09431835717895981</v>
+        <v>0.09488252412290121</v>
       </c>
       <c r="T15">
-        <v>1.120516332077594</v>
+        <v>1.133545591752915</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>-0.6681087063532365</v>
+        <v>-0.6203866558994339</v>
       </c>
       <c r="W15">
-        <v>0.3933400329580932</v>
+        <v>0.3820871734610865</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2538,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-3.036857756151075</v>
+        <v>-2.819939344997427</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2546,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1350911750302471</v>
+        <v>0.1369911750302472</v>
       </c>
       <c r="C16">
-        <v>266.5753790152914</v>
+        <v>247.362478327176</v>
       </c>
       <c r="D16">
-        <v>391.1573790152914</v>
+        <v>383.007478327176</v>
       </c>
       <c r="E16">
-        <v>-474.518</v>
+        <v>-463.4549999999999</v>
       </c>
       <c r="F16">
-        <v>154.882</v>
+        <v>165.945</v>
       </c>
       <c r="G16">
         <v>30.3</v>
@@ -2582,37 +2593,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M16">
-        <v>36.5211756</v>
+        <v>39.12983100000001</v>
       </c>
       <c r="N16">
-        <v>-139.5086756</v>
+        <v>-142.117331</v>
       </c>
       <c r="O16">
-        <v>-30.691908632</v>
+        <v>-31.26581282</v>
       </c>
       <c r="P16">
-        <v>-108.816766968</v>
+        <v>-110.85151818</v>
       </c>
       <c r="Q16">
-        <v>5.683233032000004</v>
+        <v>3.648481820000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09488252412290121</v>
+        <v>0.09545996558317063</v>
       </c>
       <c r="T16">
-        <v>1.133545591752915</v>
+        <v>1.146881422244126</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>-0.6203866558994339</v>
+        <v>-0.5790275455061381</v>
       </c>
       <c r="W16">
-        <v>0.3820871734610865</v>
+        <v>0.3723346952303473</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2620,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-2.819939344997427</v>
+        <v>-2.631943388664264</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2628,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1369911750302472</v>
+        <v>0.1388911750302471</v>
       </c>
       <c r="C17">
-        <v>247.3624783271761</v>
+        <v>228.4822581816018</v>
       </c>
       <c r="D17">
-        <v>383.007478327176</v>
+        <v>375.1902581816018</v>
       </c>
       <c r="E17">
-        <v>-463.455</v>
+        <v>-452.3919999999999</v>
       </c>
       <c r="F17">
-        <v>165.945</v>
+        <v>177.008</v>
       </c>
       <c r="G17">
         <v>30.3</v>
@@ -2664,37 +2675,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M17">
-        <v>39.129831</v>
+        <v>41.73848640000001</v>
       </c>
       <c r="N17">
-        <v>-142.117331</v>
+        <v>-144.7259864</v>
       </c>
       <c r="O17">
-        <v>-31.26581282</v>
+        <v>-31.839717008</v>
       </c>
       <c r="P17">
-        <v>-110.85151818</v>
+        <v>-112.886269392</v>
       </c>
       <c r="Q17">
-        <v>3.648481820000001</v>
+        <v>1.613730607999997</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09545996558317063</v>
+        <v>0.09605115564963694</v>
       </c>
       <c r="T17">
-        <v>1.146881422244126</v>
+        <v>1.160534772508937</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>-0.5790275455061382</v>
+        <v>-0.5428383239120045</v>
       </c>
       <c r="W17">
-        <v>0.3723346952303474</v>
+        <v>0.3638012767784507</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2702,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-2.631943388664265</v>
+        <v>-2.467446926872748</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2710,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1388911750302471</v>
+        <v>0.1407911750302472</v>
       </c>
       <c r="C18">
-        <v>228.4822581816018</v>
+        <v>209.9147558915937</v>
       </c>
       <c r="D18">
-        <v>375.1902581816018</v>
+        <v>367.6857558915937</v>
       </c>
       <c r="E18">
-        <v>-452.3919999999999</v>
+        <v>-441.329</v>
       </c>
       <c r="F18">
-        <v>177.008</v>
+        <v>188.071</v>
       </c>
       <c r="G18">
         <v>30.3</v>
@@ -2746,37 +2757,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M18">
-        <v>41.73848640000001</v>
+        <v>44.3471418</v>
       </c>
       <c r="N18">
-        <v>-144.7259864</v>
+        <v>-147.3346418</v>
       </c>
       <c r="O18">
-        <v>-31.839717008</v>
+        <v>-32.41362119599999</v>
       </c>
       <c r="P18">
-        <v>-112.886269392</v>
+        <v>-114.921020604</v>
       </c>
       <c r="Q18">
-        <v>1.613730607999997</v>
+        <v>-0.4210206039999917</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09605115564963694</v>
+        <v>0.09665659125987354</v>
       </c>
       <c r="T18">
-        <v>1.160534772508937</v>
+        <v>1.174517119165671</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>-0.5428383239120045</v>
+        <v>-0.5109066577995337</v>
       </c>
       <c r="W18">
-        <v>0.3638012767784507</v>
+        <v>0.3562717899091301</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2784,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-2.467446926872748</v>
+        <v>-2.32230298999788</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2792,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1407911750302472</v>
+        <v>0.1426911750302471</v>
       </c>
       <c r="C19">
-        <v>209.9147558915937</v>
+        <v>191.6415746137226</v>
       </c>
       <c r="D19">
-        <v>367.6857558915937</v>
+        <v>360.4755746137226</v>
       </c>
       <c r="E19">
-        <v>-441.329</v>
+        <v>-430.266</v>
       </c>
       <c r="F19">
-        <v>188.071</v>
+        <v>199.134</v>
       </c>
       <c r="G19">
         <v>30.3</v>
@@ -2828,37 +2839,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M19">
-        <v>44.3471418</v>
+        <v>46.95579720000001</v>
       </c>
       <c r="N19">
-        <v>-147.3346418</v>
+        <v>-149.9432972</v>
       </c>
       <c r="O19">
-        <v>-32.41362119599999</v>
+        <v>-32.987525384</v>
       </c>
       <c r="P19">
-        <v>-114.921020604</v>
+        <v>-116.955771816</v>
       </c>
       <c r="Q19">
-        <v>-0.4210206039999917</v>
+        <v>-2.455771816000009</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09665659125987354</v>
+        <v>0.09727679359231102</v>
       </c>
       <c r="T19">
-        <v>1.174517119165671</v>
+        <v>1.188840498667691</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>-0.5109066577995337</v>
+        <v>-0.4825229545884485</v>
       </c>
       <c r="W19">
-        <v>0.3562717899091301</v>
+        <v>0.3495789126919562</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2866,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-2.32230298999788</v>
+        <v>-2.19328615722022</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2874,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1426911750302471</v>
+        <v>0.1445911750302472</v>
       </c>
       <c r="C20">
-        <v>191.6415746137226</v>
+        <v>173.6457327727749</v>
       </c>
       <c r="D20">
-        <v>360.4755746137226</v>
+        <v>353.5427327727749</v>
       </c>
       <c r="E20">
-        <v>-430.266</v>
+        <v>-419.203</v>
       </c>
       <c r="F20">
-        <v>199.134</v>
+        <v>210.197</v>
       </c>
       <c r="G20">
         <v>30.3</v>
@@ -2910,37 +2921,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M20">
-        <v>46.9557972</v>
+        <v>49.5644526</v>
       </c>
       <c r="N20">
-        <v>-149.9432972</v>
+        <v>-152.5519526</v>
       </c>
       <c r="O20">
-        <v>-32.987525384</v>
+        <v>-33.561429572</v>
       </c>
       <c r="P20">
-        <v>-116.955771816</v>
+        <v>-118.990523028</v>
       </c>
       <c r="Q20">
-        <v>-2.455771815999981</v>
+        <v>-4.490523027999984</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09727679359231102</v>
+        <v>0.09791230956258647</v>
       </c>
       <c r="T20">
-        <v>1.188840498667691</v>
+        <v>1.203517541861119</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>-0.4825229545884486</v>
+        <v>-0.4571270096101092</v>
       </c>
       <c r="W20">
-        <v>0.3495789126919562</v>
+        <v>0.3435905488660638</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2948,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-2.19328615722022</v>
+        <v>-2.077850043682314</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2956,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1445911750302472</v>
+        <v>0.1464911750302472</v>
       </c>
       <c r="C21">
-        <v>173.6457327727749</v>
+        <v>155.9115305341826</v>
       </c>
       <c r="D21">
-        <v>353.5427327727749</v>
+        <v>346.8715305341826</v>
       </c>
       <c r="E21">
-        <v>-419.203</v>
+        <v>-408.14</v>
       </c>
       <c r="F21">
-        <v>210.197</v>
+        <v>221.26</v>
       </c>
       <c r="G21">
         <v>30.3</v>
@@ -2992,37 +3003,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M21">
-        <v>49.5644526</v>
+        <v>52.173108</v>
       </c>
       <c r="N21">
-        <v>-152.5519526</v>
+        <v>-155.160608</v>
       </c>
       <c r="O21">
-        <v>-33.561429572</v>
+        <v>-34.13533376</v>
       </c>
       <c r="P21">
-        <v>-118.990523028</v>
+        <v>-121.02527424</v>
       </c>
       <c r="Q21">
-        <v>-4.490523027999984</v>
+        <v>-6.525274239999987</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09791230956258647</v>
+        <v>0.0985637134321188</v>
       </c>
       <c r="T21">
-        <v>1.203517541861119</v>
+        <v>1.218561511134383</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>-0.4571270096101092</v>
+        <v>-0.4342706591296037</v>
       </c>
       <c r="W21">
-        <v>0.3435905488660638</v>
+        <v>0.3382010214227606</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3030,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-2.077850043682314</v>
+        <v>-1.973957541498199</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3038,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1464911750302472</v>
+        <v>0.1483911750302472</v>
       </c>
       <c r="C22">
-        <v>155.9115305341826</v>
+        <v>138.424431114124</v>
       </c>
       <c r="D22">
-        <v>346.8715305341826</v>
+        <v>340.447431114124</v>
       </c>
       <c r="E22">
-        <v>-408.14</v>
+        <v>-397.077</v>
       </c>
       <c r="F22">
-        <v>221.26</v>
+        <v>232.323</v>
       </c>
       <c r="G22">
         <v>30.3</v>
@@ -3074,37 +3085,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M22">
-        <v>52.173108</v>
+        <v>54.7817634</v>
       </c>
       <c r="N22">
-        <v>-155.160608</v>
+        <v>-157.7692634</v>
       </c>
       <c r="O22">
-        <v>-34.13533376</v>
+        <v>-34.709237948</v>
       </c>
       <c r="P22">
-        <v>-121.02527424</v>
+        <v>-123.060025452</v>
       </c>
       <c r="Q22">
-        <v>-6.525274239999987</v>
+        <v>-8.560025451999991</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0985637134321188</v>
+        <v>0.09923160853885447</v>
       </c>
       <c r="T22">
-        <v>1.218561511134383</v>
+        <v>1.233986340389249</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>-0.4342706591296037</v>
+        <v>-0.4135911039329558</v>
       </c>
       <c r="W22">
-        <v>0.3382010214227606</v>
+        <v>0.333324782307391</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3112,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-1.973957541498199</v>
+        <v>-1.879959563331618</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3120,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1483911750302471</v>
+        <v>0.1502911750302472</v>
       </c>
       <c r="C23">
-        <v>138.424431114124</v>
+        <v>121.1709550387081</v>
       </c>
       <c r="D23">
-        <v>340.447431114124</v>
+        <v>334.2569550387081</v>
       </c>
       <c r="E23">
-        <v>-397.077</v>
+        <v>-386.014</v>
       </c>
       <c r="F23">
-        <v>232.323</v>
+        <v>243.386</v>
       </c>
       <c r="G23">
         <v>30.3</v>
@@ -3156,37 +3167,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M23">
-        <v>54.7817634</v>
+        <v>57.3904188</v>
       </c>
       <c r="N23">
-        <v>-157.7692634</v>
+        <v>-160.3779188</v>
       </c>
       <c r="O23">
-        <v>-34.709237948</v>
+        <v>-35.283142136</v>
       </c>
       <c r="P23">
-        <v>-123.060025452</v>
+        <v>-125.094776664</v>
       </c>
       <c r="Q23">
-        <v>-8.560025451999991</v>
+        <v>-10.59477666399999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09923160853885447</v>
+        <v>0.09991662916114748</v>
       </c>
       <c r="T23">
-        <v>1.233986340389249</v>
+        <v>1.249806678086547</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>-0.413591103932956</v>
+        <v>-0.3947915082996397</v>
       </c>
       <c r="W23">
-        <v>0.333324782307391</v>
+        <v>0.3288918376570551</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3194,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-1.879959563331618</v>
+        <v>-1.794506855907454</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3202,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1502911750302472</v>
+        <v>0.1521911750302471</v>
       </c>
       <c r="C24">
-        <v>121.1709550387081</v>
+        <v>104.1385857334722</v>
       </c>
       <c r="D24">
-        <v>334.2569550387081</v>
+        <v>328.2875857334722</v>
       </c>
       <c r="E24">
-        <v>-386.014</v>
+        <v>-374.951</v>
       </c>
       <c r="F24">
-        <v>243.386</v>
+        <v>254.449</v>
       </c>
       <c r="G24">
         <v>30.3</v>
@@ -3238,37 +3249,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M24">
-        <v>57.3904188</v>
+        <v>59.9990742</v>
       </c>
       <c r="N24">
-        <v>-160.3779188</v>
+        <v>-162.9865742</v>
       </c>
       <c r="O24">
-        <v>-35.283142136</v>
+        <v>-35.857046324</v>
       </c>
       <c r="P24">
-        <v>-125.094776664</v>
+        <v>-127.129527876</v>
       </c>
       <c r="Q24">
-        <v>-10.59477666399999</v>
+        <v>-12.629527876</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09991662916114748</v>
+        <v>0.1006194425268767</v>
       </c>
       <c r="T24">
-        <v>1.249806678086547</v>
+        <v>1.266037933646113</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>-0.3947915082996397</v>
+        <v>-0.3776266601126989</v>
       </c>
       <c r="W24">
-        <v>0.3288918376570551</v>
+        <v>0.3248443664545744</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3276,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-1.794506855907454</v>
+        <v>-1.716484818694086</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3284,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1521911750302471</v>
+        <v>0.1540911750302472</v>
       </c>
       <c r="C25">
-        <v>104.1385857334722</v>
+        <v>87.31568505163563</v>
       </c>
       <c r="D25">
-        <v>328.2875857334722</v>
+        <v>322.5276850516356</v>
       </c>
       <c r="E25">
-        <v>-374.951</v>
+        <v>-363.888</v>
       </c>
       <c r="F25">
-        <v>254.449</v>
+        <v>265.512</v>
       </c>
       <c r="G25">
         <v>30.3</v>
@@ -3320,37 +3331,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M25">
-        <v>59.9990742</v>
+        <v>62.60772960000001</v>
       </c>
       <c r="N25">
-        <v>-162.9865742</v>
+        <v>-165.5952296</v>
       </c>
       <c r="O25">
-        <v>-35.857046324</v>
+        <v>-36.430950512</v>
       </c>
       <c r="P25">
-        <v>-127.129527876</v>
+        <v>-129.164279088</v>
       </c>
       <c r="Q25">
-        <v>-12.629527876</v>
+        <v>-14.664279088</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1006194425268767</v>
+        <v>0.1013407509811777</v>
       </c>
       <c r="T25">
-        <v>1.266037933646113</v>
+        <v>1.282696327509877</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>-0.3776266601126989</v>
+        <v>-0.3618922159413364</v>
       </c>
       <c r="W25">
-        <v>0.3248443664545744</v>
+        <v>0.3211341845189671</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3358,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-1.716484818694086</v>
+        <v>-1.644964617915166</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3366,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1540911750302472</v>
+        <v>0.1559911750302471</v>
       </c>
       <c r="C26">
-        <v>87.31568505163563</v>
+        <v>70.69141754151156</v>
       </c>
       <c r="D26">
-        <v>322.5276850516356</v>
+        <v>316.9664175415115</v>
       </c>
       <c r="E26">
-        <v>-363.888</v>
+        <v>-352.825</v>
       </c>
       <c r="F26">
-        <v>265.512</v>
+        <v>276.575</v>
       </c>
       <c r="G26">
         <v>30.3</v>
@@ -3402,37 +3413,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M26">
-        <v>62.60772960000001</v>
+        <v>65.216385</v>
       </c>
       <c r="N26">
-        <v>-165.5952296</v>
+        <v>-168.203885</v>
       </c>
       <c r="O26">
-        <v>-36.430950512</v>
+        <v>-37.0048547</v>
       </c>
       <c r="P26">
-        <v>-129.164279088</v>
+        <v>-131.1990303</v>
       </c>
       <c r="Q26">
-        <v>-14.664279088</v>
+        <v>-16.6990303</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1013407509811777</v>
+        <v>0.1020812943275934</v>
       </c>
       <c r="T26">
-        <v>1.282696327509877</v>
+        <v>1.299798945210009</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>-0.3618922159413364</v>
+        <v>-0.3474165273036829</v>
       </c>
       <c r="W26">
-        <v>0.3211341845189671</v>
+        <v>0.3177208171382084</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3440,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-1.644964617915166</v>
+        <v>-1.579166033198559</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3448,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1559911750302471</v>
+        <v>0.1578911750302472</v>
       </c>
       <c r="C27">
-        <v>70.69141754151156</v>
+        <v>54.2556824161428</v>
       </c>
       <c r="D27">
-        <v>316.9664175415115</v>
+        <v>311.5936824161428</v>
       </c>
       <c r="E27">
-        <v>-352.825</v>
+        <v>-341.762</v>
       </c>
       <c r="F27">
-        <v>276.575</v>
+        <v>287.638</v>
       </c>
       <c r="G27">
         <v>30.3</v>
@@ -3484,37 +3495,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M27">
-        <v>65.216385</v>
+        <v>67.82504039999999</v>
       </c>
       <c r="N27">
-        <v>-168.203885</v>
+        <v>-170.8125404</v>
       </c>
       <c r="O27">
-        <v>-37.0048547</v>
+        <v>-37.578758888</v>
       </c>
       <c r="P27">
-        <v>-131.1990303</v>
+        <v>-133.233781512</v>
       </c>
       <c r="Q27">
-        <v>-16.6990303</v>
+        <v>-18.73378151200001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1020812943275934</v>
+        <v>0.1028418523590474</v>
       </c>
       <c r="T27">
-        <v>1.299798945210009</v>
+        <v>1.317363795820955</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>-0.3474165273036829</v>
+        <v>-0.3340543531766182</v>
       </c>
       <c r="W27">
-        <v>0.3177208171382084</v>
+        <v>0.3145700164790466</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3522,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-1.579166033198559</v>
+        <v>-1.518428878075538</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3530,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1578911750302472</v>
+        <v>0.1597911750302471</v>
       </c>
       <c r="C28">
-        <v>54.2556824161428</v>
+        <v>37.99905232650133</v>
       </c>
       <c r="D28">
-        <v>311.5936824161428</v>
+        <v>306.4000523265013</v>
       </c>
       <c r="E28">
-        <v>-341.762</v>
+        <v>-330.699</v>
       </c>
       <c r="F28">
-        <v>287.638</v>
+        <v>298.701</v>
       </c>
       <c r="G28">
         <v>30.3</v>
@@ -3566,37 +3577,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M28">
-        <v>67.82504039999999</v>
+        <v>70.43369580000001</v>
       </c>
       <c r="N28">
-        <v>-170.8125404</v>
+        <v>-173.4211958</v>
       </c>
       <c r="O28">
-        <v>-37.578758888</v>
+        <v>-38.152663076</v>
       </c>
       <c r="P28">
-        <v>-133.233781512</v>
+        <v>-135.268532724</v>
       </c>
       <c r="Q28">
-        <v>-18.73378151200001</v>
+        <v>-20.76853272400001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1028418523590474</v>
+        <v>0.1036232475968425</v>
       </c>
       <c r="T28">
-        <v>1.317363795820955</v>
+        <v>1.335409875215763</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>-0.3340543531766182</v>
+        <v>-0.3216819697256323</v>
       </c>
       <c r="W28">
-        <v>0.3145700164790466</v>
+        <v>0.3116526084613041</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3604,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-1.518428878075538</v>
+        <v>-1.462190771480147</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3612,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1597911750302471</v>
+        <v>0.1616911750302472</v>
       </c>
       <c r="C29">
-        <v>37.99905232650133</v>
+        <v>21.91271815745517</v>
       </c>
       <c r="D29">
-        <v>306.4000523265013</v>
+        <v>301.3767181574552</v>
       </c>
       <c r="E29">
-        <v>-330.699</v>
+        <v>-319.636</v>
       </c>
       <c r="F29">
-        <v>298.701</v>
+        <v>309.764</v>
       </c>
       <c r="G29">
         <v>30.3</v>
@@ -3648,37 +3659,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M29">
-        <v>70.43369580000001</v>
+        <v>73.0423512</v>
       </c>
       <c r="N29">
-        <v>-173.4211958</v>
+        <v>-176.0298512</v>
       </c>
       <c r="O29">
-        <v>-38.152663076</v>
+        <v>-38.726567264</v>
       </c>
       <c r="P29">
-        <v>-135.268532724</v>
+        <v>-137.303283936</v>
       </c>
       <c r="Q29">
-        <v>-20.76853272400001</v>
+        <v>-22.80328393600001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1036232475968425</v>
+        <v>0.1044263482579098</v>
       </c>
       <c r="T29">
-        <v>1.335409875215763</v>
+        <v>1.353957234593759</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>-0.3216819697256323</v>
+        <v>-0.3101933279497169</v>
       </c>
       <c r="W29">
-        <v>0.3116526084613041</v>
+        <v>0.3089435867305432</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3686,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-1.462190771480147</v>
+        <v>-1.409969672498713</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3694,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1616911750302472</v>
+        <v>0.1635911750302471</v>
       </c>
       <c r="C30">
-        <v>21.91271815745517</v>
+        <v>5.988439166460125</v>
       </c>
       <c r="D30">
-        <v>301.3767181574552</v>
+        <v>296.5154391664601</v>
       </c>
       <c r="E30">
-        <v>-319.636</v>
+        <v>-308.573</v>
       </c>
       <c r="F30">
-        <v>309.764</v>
+        <v>320.827</v>
       </c>
       <c r="G30">
         <v>30.3</v>
@@ -3730,37 +3741,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M30">
-        <v>73.0423512</v>
+        <v>75.6510066</v>
       </c>
       <c r="N30">
-        <v>-176.0298512</v>
+        <v>-178.6385066</v>
       </c>
       <c r="O30">
-        <v>-38.726567264</v>
+        <v>-39.300471452</v>
       </c>
       <c r="P30">
-        <v>-137.303283936</v>
+        <v>-139.338035148</v>
       </c>
       <c r="Q30">
-        <v>-22.80328393600001</v>
+        <v>-24.83803514799999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1044263482579098</v>
+        <v>0.1052520714728099</v>
       </c>
       <c r="T30">
-        <v>1.353957234593759</v>
+        <v>1.373027054799305</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>-0.3101933279497169</v>
+        <v>-0.2994970062962784</v>
       </c>
       <c r="W30">
-        <v>0.3089435867305432</v>
+        <v>0.3064213940846625</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3768,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-1.409969672498713</v>
+        <v>-1.361350028619447</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3776,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1635911750302471</v>
+        <v>0.1654911750302471</v>
       </c>
       <c r="C31">
-        <v>5.988439166460182</v>
+        <v>-9.781502128701391</v>
       </c>
       <c r="D31">
-        <v>296.5154391664601</v>
+        <v>291.8084978712986</v>
       </c>
       <c r="E31">
-        <v>-308.573</v>
+        <v>-297.51</v>
       </c>
       <c r="F31">
-        <v>320.8269999999999</v>
+        <v>331.89</v>
       </c>
       <c r="G31">
         <v>30.3</v>
@@ -3812,37 +3823,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M31">
-        <v>75.65100659999999</v>
+        <v>78.25966200000001</v>
       </c>
       <c r="N31">
-        <v>-178.6385066</v>
+        <v>-181.247162</v>
       </c>
       <c r="O31">
-        <v>-39.300471452</v>
+        <v>-39.87437564</v>
       </c>
       <c r="P31">
-        <v>-139.338035148</v>
+        <v>-141.37278636</v>
       </c>
       <c r="Q31">
-        <v>-24.83803514799996</v>
+        <v>-26.87278635999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1052520714728099</v>
+        <v>0.1061013867795643</v>
       </c>
       <c r="T31">
-        <v>1.373027054799305</v>
+        <v>1.392641727010724</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>-0.2994970062962785</v>
+        <v>-0.2895137727530691</v>
       </c>
       <c r="W31">
-        <v>0.3064213940846625</v>
+        <v>0.3040673476151737</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3850,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-1.361350028619448</v>
+        <v>-1.315971694332132</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3858,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1654911750302471</v>
+        <v>0.1673911750302471</v>
       </c>
       <c r="C32">
-        <v>-9.781502128701391</v>
+        <v>-25.40434083260027</v>
       </c>
       <c r="D32">
-        <v>291.8084978712986</v>
+        <v>287.2486591673997</v>
       </c>
       <c r="E32">
-        <v>-297.51</v>
+        <v>-286.447</v>
       </c>
       <c r="F32">
-        <v>331.89</v>
+        <v>342.953</v>
       </c>
       <c r="G32">
         <v>30.3</v>
@@ -3894,37 +3905,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M32">
-        <v>78.25966200000001</v>
+        <v>80.8683174</v>
       </c>
       <c r="N32">
-        <v>-181.247162</v>
+        <v>-183.8558174</v>
       </c>
       <c r="O32">
-        <v>-39.87437564</v>
+        <v>-40.448279828</v>
       </c>
       <c r="P32">
-        <v>-141.37278636</v>
+        <v>-143.407537572</v>
       </c>
       <c r="Q32">
-        <v>-26.87278635999999</v>
+        <v>-28.90753757199997</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1061013867795643</v>
+        <v>0.1069753199212972</v>
       </c>
       <c r="T32">
-        <v>1.392641727010724</v>
+        <v>1.412824940445662</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>-0.2895137727530691</v>
+        <v>-0.2801746187932927</v>
       </c>
       <c r="W32">
-        <v>0.3040673476151737</v>
+        <v>0.3018651751114584</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3932,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-1.315971694332132</v>
+        <v>-1.273520994514967</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3940,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1673911750302471</v>
+        <v>0.1692911750302472</v>
       </c>
       <c r="C33">
-        <v>-25.40434083260027</v>
+        <v>-40.88686678078551</v>
       </c>
       <c r="D33">
-        <v>287.2486591673997</v>
+        <v>282.8291332192145</v>
       </c>
       <c r="E33">
-        <v>-286.447</v>
+        <v>-275.384</v>
       </c>
       <c r="F33">
-        <v>342.953</v>
+        <v>354.016</v>
       </c>
       <c r="G33">
         <v>30.3</v>
@@ -3976,37 +3987,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M33">
-        <v>80.8683174</v>
+        <v>83.47697280000001</v>
       </c>
       <c r="N33">
-        <v>-183.8558174</v>
+        <v>-186.4644728</v>
       </c>
       <c r="O33">
-        <v>-40.448279828</v>
+        <v>-41.022184016</v>
       </c>
       <c r="P33">
-        <v>-143.407537572</v>
+        <v>-145.442288784</v>
       </c>
       <c r="Q33">
-        <v>-28.90753757199997</v>
+        <v>-30.942288784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1069753199212972</v>
+        <v>0.1078749569789633</v>
       </c>
       <c r="T33">
-        <v>1.412824940445662</v>
+        <v>1.433601777805157</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>-0.2801746187932927</v>
+        <v>-0.2714191619560022</v>
       </c>
       <c r="W33">
-        <v>0.3018651751114584</v>
+        <v>0.2998006383892253</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4014,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-1.273520994514967</v>
+        <v>-1.233723463436374</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4022,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1692911750302472</v>
+        <v>0.1711911750302472</v>
       </c>
       <c r="C34">
-        <v>-40.88686678078551</v>
+        <v>-56.23545827465972</v>
       </c>
       <c r="D34">
-        <v>282.8291332192145</v>
+        <v>278.5435417253403</v>
       </c>
       <c r="E34">
-        <v>-275.384</v>
+        <v>-264.321</v>
       </c>
       <c r="F34">
-        <v>354.016</v>
+        <v>365.079</v>
       </c>
       <c r="G34">
         <v>30.3</v>
@@ -4058,37 +4069,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M34">
-        <v>83.47697280000001</v>
+        <v>86.0856282</v>
       </c>
       <c r="N34">
-        <v>-186.4644728</v>
+        <v>-189.0731282</v>
       </c>
       <c r="O34">
-        <v>-41.022184016</v>
+        <v>-41.596088204</v>
       </c>
       <c r="P34">
-        <v>-145.442288784</v>
+        <v>-147.477039996</v>
       </c>
       <c r="Q34">
-        <v>-30.942288784</v>
+        <v>-32.97703999599997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1078749569789633</v>
+        <v>0.1088014488741717</v>
       </c>
       <c r="T34">
-        <v>1.433601777805157</v>
+        <v>1.454998819264936</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>-0.2714191619560022</v>
+        <v>-0.2631943388664265</v>
       </c>
       <c r="W34">
-        <v>0.2998006383892253</v>
+        <v>0.2978612251047034</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4096,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-1.233723463436374</v>
+        <v>-1.196337903938302</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4104,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1711911750302472</v>
+        <v>0.1730911750302472</v>
       </c>
       <c r="C35">
-        <v>-56.23545827465972</v>
+        <v>-71.45611279511155</v>
       </c>
       <c r="D35">
-        <v>278.5435417253403</v>
+        <v>274.3858872048884</v>
       </c>
       <c r="E35">
-        <v>-264.321</v>
+        <v>-253.258</v>
       </c>
       <c r="F35">
-        <v>365.079</v>
+        <v>376.142</v>
       </c>
       <c r="G35">
         <v>30.3</v>
@@ -4140,37 +4151,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M35">
-        <v>86.0856282</v>
+        <v>88.69428360000001</v>
       </c>
       <c r="N35">
-        <v>-189.0731282</v>
+        <v>-191.6817836</v>
       </c>
       <c r="O35">
-        <v>-41.596088204</v>
+        <v>-42.169992392</v>
       </c>
       <c r="P35">
-        <v>-147.477039996</v>
+        <v>-149.511791208</v>
       </c>
       <c r="Q35">
-        <v>-32.97703999599997</v>
+        <v>-35.01179120800001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1088014488741717</v>
+        <v>0.1097560162813561</v>
       </c>
       <c r="T35">
-        <v>1.454998819264936</v>
+        <v>1.477044255920465</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>-0.2631943388664265</v>
+        <v>-0.2554533288997669</v>
       </c>
       <c r="W35">
-        <v>0.2978612251047034</v>
+        <v>0.2960358949545651</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4178,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-1.196337903938302</v>
+        <v>-1.16115149499894</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4186,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1730911750302472</v>
+        <v>0.1749911750302471</v>
       </c>
       <c r="C36">
-        <v>-71.45611279511155</v>
+        <v>-86.55447500593772</v>
       </c>
       <c r="D36">
-        <v>274.3858872048884</v>
+        <v>270.3505249940623</v>
       </c>
       <c r="E36">
-        <v>-253.258</v>
+        <v>-242.1949999999999</v>
       </c>
       <c r="F36">
-        <v>376.142</v>
+        <v>387.205</v>
       </c>
       <c r="G36">
         <v>30.3</v>
@@ -4222,37 +4233,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M36">
-        <v>88.69428360000001</v>
+        <v>91.30293900000001</v>
       </c>
       <c r="N36">
-        <v>-191.6817836</v>
+        <v>-194.290439</v>
       </c>
       <c r="O36">
-        <v>-42.169992392</v>
+        <v>-42.74389658</v>
       </c>
       <c r="P36">
-        <v>-149.511791208</v>
+        <v>-151.54654242</v>
       </c>
       <c r="Q36">
-        <v>-35.01179120800001</v>
+        <v>-37.04654241999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1097560162813561</v>
+        <v>0.110739954993377</v>
       </c>
       <c r="T36">
-        <v>1.477044255920465</v>
+        <v>1.499768013703857</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>-0.2554533288997669</v>
+        <v>-0.2481546623597735</v>
       </c>
       <c r="W36">
-        <v>0.2960358949545651</v>
+        <v>0.2943148693844346</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4260,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-1.16115149499894</v>
+        <v>-1.127975737998971</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4268,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1749911750302471</v>
+        <v>0.1768911750302471</v>
       </c>
       <c r="C37">
-        <v>-86.55447500593772</v>
+        <v>-101.5358623220191</v>
       </c>
       <c r="D37">
-        <v>270.3505249940623</v>
+        <v>266.4321376779809</v>
       </c>
       <c r="E37">
-        <v>-242.1949999999999</v>
+        <v>-231.1319999999999</v>
       </c>
       <c r="F37">
-        <v>387.205</v>
+        <v>398.268</v>
       </c>
       <c r="G37">
         <v>30.3</v>
@@ -4304,37 +4315,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M37">
-        <v>91.30293900000001</v>
+        <v>93.91159440000001</v>
       </c>
       <c r="N37">
-        <v>-194.290439</v>
+        <v>-196.8990944</v>
       </c>
       <c r="O37">
-        <v>-42.74389658</v>
+        <v>-43.31780076800001</v>
       </c>
       <c r="P37">
-        <v>-151.54654242</v>
+        <v>-153.581293632</v>
       </c>
       <c r="Q37">
-        <v>-37.04654241999998</v>
+        <v>-39.08129363200001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.110739954993377</v>
+        <v>0.1117546417901485</v>
       </c>
       <c r="T37">
-        <v>1.499768013703857</v>
+        <v>1.523201888917979</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>-0.2481546623597735</v>
+        <v>-0.2412614772942243</v>
       </c>
       <c r="W37">
-        <v>0.2943148693844346</v>
+        <v>0.2926894563459781</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4342,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-1.127975737998971</v>
+        <v>-1.09664307861011</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4350,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1768911750302471</v>
+        <v>0.1787911750302472</v>
       </c>
       <c r="C38">
-        <v>-101.5358623220191</v>
+        <v>-116.4052882857947</v>
       </c>
       <c r="D38">
-        <v>266.4321376779809</v>
+        <v>262.6257117142052</v>
       </c>
       <c r="E38">
-        <v>-231.132</v>
+        <v>-220.069</v>
       </c>
       <c r="F38">
-        <v>398.268</v>
+        <v>409.331</v>
       </c>
       <c r="G38">
         <v>30.3</v>
@@ -4386,37 +4397,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M38">
-        <v>93.9115944</v>
+        <v>96.52024979999999</v>
       </c>
       <c r="N38">
-        <v>-196.8990944</v>
+        <v>-199.5077498</v>
       </c>
       <c r="O38">
-        <v>-43.317800768</v>
+        <v>-43.891704956</v>
       </c>
       <c r="P38">
-        <v>-153.581293632</v>
+        <v>-155.616044844</v>
       </c>
       <c r="Q38">
-        <v>-39.08129363199998</v>
+        <v>-41.11604484399999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1117546417901485</v>
+        <v>0.1128015408661826</v>
       </c>
       <c r="T38">
-        <v>1.523201888917979</v>
+        <v>1.547379696678582</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>-0.2412614772942243</v>
+        <v>-0.2347408968268128</v>
       </c>
       <c r="W38">
-        <v>0.2926894563459781</v>
+        <v>0.2911519034717625</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4424,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-1.09664307861011</v>
+        <v>-1.067004076485513</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4432,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1787911750302472</v>
+        <v>0.1806911750302471</v>
       </c>
       <c r="C39">
-        <v>-116.4052882857947</v>
+        <v>-131.1674839681297</v>
       </c>
       <c r="D39">
-        <v>262.6257117142052</v>
+        <v>258.9265160318703</v>
       </c>
       <c r="E39">
-        <v>-220.069</v>
+        <v>-209.006</v>
       </c>
       <c r="F39">
-        <v>409.331</v>
+        <v>420.394</v>
       </c>
       <c r="G39">
         <v>30.3</v>
@@ -4468,37 +4479,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M39">
-        <v>96.52024979999999</v>
+        <v>99.12890520000001</v>
       </c>
       <c r="N39">
-        <v>-199.5077498</v>
+        <v>-202.1164052</v>
       </c>
       <c r="O39">
-        <v>-43.891704956</v>
+        <v>-44.465609144</v>
       </c>
       <c r="P39">
-        <v>-155.616044844</v>
+        <v>-157.650796056</v>
       </c>
       <c r="Q39">
-        <v>-41.11604484399999</v>
+        <v>-43.15079605599999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1128015408661826</v>
+        <v>0.1138822108801533</v>
       </c>
       <c r="T39">
-        <v>1.547379696678582</v>
+        <v>1.572337433721785</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>-0.2347408968268128</v>
+        <v>-0.2285635048050546</v>
       </c>
       <c r="W39">
-        <v>0.2911519034717625</v>
+        <v>0.2896952744330318</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4506,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-1.067004076485513</v>
+        <v>-1.038925021841157</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4514,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1806911750302471</v>
+        <v>0.1825911750302471</v>
       </c>
       <c r="C40">
-        <v>-131.1674839681297</v>
+        <v>-145.8269175856622</v>
       </c>
       <c r="D40">
-        <v>258.9265160318703</v>
+        <v>255.3300824143378</v>
       </c>
       <c r="E40">
-        <v>-209.006</v>
+        <v>-197.943</v>
       </c>
       <c r="F40">
-        <v>420.394</v>
+        <v>431.457</v>
       </c>
       <c r="G40">
         <v>30.3</v>
@@ -4550,37 +4561,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M40">
-        <v>99.12890520000001</v>
+        <v>101.7375606</v>
       </c>
       <c r="N40">
-        <v>-202.1164052</v>
+        <v>-204.7250606</v>
       </c>
       <c r="O40">
-        <v>-44.465609144</v>
+        <v>-45.039513332</v>
       </c>
       <c r="P40">
-        <v>-157.650796056</v>
+        <v>-159.685547268</v>
       </c>
       <c r="Q40">
-        <v>-43.15079605599999</v>
+        <v>-45.18554726799999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1138822108801533</v>
+        <v>0.1149983126978607</v>
       </c>
       <c r="T40">
-        <v>1.572337433721785</v>
+        <v>1.598113457225421</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>-0.2285635048050546</v>
+        <v>-0.2227029021177455</v>
       </c>
       <c r="W40">
-        <v>0.2896952744330318</v>
+        <v>0.2883133443193643</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4588,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-1.038925021841157</v>
+        <v>-1.012285918717025</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4596,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1825911750302471</v>
+        <v>0.1844911750302472</v>
       </c>
       <c r="C41">
-        <v>-145.8269175856622</v>
+        <v>-160.3878125056631</v>
       </c>
       <c r="D41">
-        <v>255.3300824143378</v>
+        <v>251.8321874943369</v>
       </c>
       <c r="E41">
-        <v>-197.943</v>
+        <v>-186.88</v>
       </c>
       <c r="F41">
-        <v>431.457</v>
+        <v>442.52</v>
       </c>
       <c r="G41">
         <v>30.3</v>
@@ -4632,37 +4643,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M41">
-        <v>101.7375606</v>
+        <v>104.346216</v>
       </c>
       <c r="N41">
-        <v>-204.7250606</v>
+        <v>-207.333716</v>
       </c>
       <c r="O41">
-        <v>-45.039513332</v>
+        <v>-45.61341752</v>
       </c>
       <c r="P41">
-        <v>-159.685547268</v>
+        <v>-161.72029848</v>
       </c>
       <c r="Q41">
-        <v>-45.18554726799999</v>
+        <v>-47.22029848</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1149983126978607</v>
+        <v>0.1161516179094917</v>
       </c>
       <c r="T41">
-        <v>1.598113457225421</v>
+        <v>1.624748681512512</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>-0.2227029021177455</v>
+        <v>-0.2171353295648019</v>
       </c>
       <c r="W41">
-        <v>0.2883133443193643</v>
+        <v>0.2870005107113803</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4670,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-1.012285918717025</v>
+        <v>-0.9869787707490991</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4678,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1844911750302472</v>
+        <v>0.1863911750302472</v>
       </c>
       <c r="C42">
-        <v>-160.3878125056631</v>
+        <v>-174.8541637909504</v>
       </c>
       <c r="D42">
-        <v>251.8321874943369</v>
+        <v>248.4288362090496</v>
       </c>
       <c r="E42">
-        <v>-186.88</v>
+        <v>-175.817</v>
       </c>
       <c r="F42">
-        <v>442.52</v>
+        <v>453.583</v>
       </c>
       <c r="G42">
         <v>30.3</v>
@@ -4714,37 +4725,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M42">
-        <v>104.346216</v>
+        <v>106.9548714</v>
       </c>
       <c r="N42">
-        <v>-207.333716</v>
+        <v>-209.9423714</v>
       </c>
       <c r="O42">
-        <v>-45.61341752</v>
+        <v>-46.18732170800001</v>
       </c>
       <c r="P42">
-        <v>-161.72029848</v>
+        <v>-163.755049692</v>
       </c>
       <c r="Q42">
-        <v>-47.22029848</v>
+        <v>-49.255049692</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1161516179094917</v>
+        <v>0.1173440182130424</v>
       </c>
       <c r="T42">
-        <v>1.624748681512512</v>
+        <v>1.652286794758486</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>-0.2171353295648019</v>
+        <v>-0.2118393459168798</v>
       </c>
       <c r="W42">
-        <v>0.2870005107113803</v>
+        <v>0.2857517177672003</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4752,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.9869787707490991</v>
+        <v>-0.9629061178039993</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4760,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1863911750302472</v>
+        <v>0.1882911750302472</v>
       </c>
       <c r="C43">
-        <v>-174.8541637909504</v>
+        <v>-189.2297534211292</v>
       </c>
       <c r="D43">
-        <v>248.4288362090496</v>
+        <v>245.1162465788708</v>
       </c>
       <c r="E43">
-        <v>-175.817</v>
+        <v>-164.754</v>
       </c>
       <c r="F43">
-        <v>453.583</v>
+        <v>464.646</v>
       </c>
       <c r="G43">
         <v>30.3</v>
@@ -4796,37 +4807,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M43">
-        <v>106.9548714</v>
+        <v>109.5635268</v>
       </c>
       <c r="N43">
-        <v>-209.9423714</v>
+        <v>-212.5510268</v>
       </c>
       <c r="O43">
-        <v>-46.18732170800001</v>
+        <v>-46.761225896</v>
       </c>
       <c r="P43">
-        <v>-163.755049692</v>
+        <v>-165.789800904</v>
       </c>
       <c r="Q43">
-        <v>-49.255049692</v>
+        <v>-51.289800904</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1173440182130424</v>
+        <v>0.1185775357684397</v>
       </c>
       <c r="T43">
-        <v>1.652286794758486</v>
+        <v>1.680774498116391</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>-0.2118393459168798</v>
+        <v>-0.2067955519664779</v>
       </c>
       <c r="W43">
-        <v>0.2857517177672003</v>
+        <v>0.2845623911536955</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4834,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.9629061178039993</v>
+        <v>-0.9399797816658086</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4842,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1882911750302472</v>
+        <v>0.1901911750302472</v>
       </c>
       <c r="C44">
-        <v>-189.2297534211291</v>
+        <v>-203.5181643120807</v>
       </c>
       <c r="D44">
-        <v>245.1162465788708</v>
+        <v>241.8908356879192</v>
       </c>
       <c r="E44">
-        <v>-164.754</v>
+        <v>-153.691</v>
       </c>
       <c r="F44">
-        <v>464.646</v>
+        <v>475.7089999999999</v>
       </c>
       <c r="G44">
         <v>30.3</v>
@@ -4878,37 +4889,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M44">
-        <v>109.5635268</v>
+        <v>112.1721822</v>
       </c>
       <c r="N44">
-        <v>-212.5510268</v>
+        <v>-215.1596822</v>
       </c>
       <c r="O44">
-        <v>-46.761225896</v>
+        <v>-47.335130084</v>
       </c>
       <c r="P44">
-        <v>-165.789800904</v>
+        <v>-167.824552116</v>
       </c>
       <c r="Q44">
-        <v>-51.289800904</v>
+        <v>-53.32455211600001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1185775357684397</v>
+        <v>0.1198543346415702</v>
       </c>
       <c r="T44">
-        <v>1.680774498116391</v>
+        <v>1.710261770013169</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>-0.206795551966478</v>
+        <v>-0.2019863530835366</v>
       </c>
       <c r="W44">
-        <v>0.2845623911536955</v>
+        <v>0.283428382057098</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4916,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.9399797816658089</v>
+        <v>-0.9181197867433482</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4924,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1901911750302472</v>
+        <v>0.1920911750302472</v>
       </c>
       <c r="C45">
-        <v>-203.5181643120807</v>
+        <v>-217.7227932429581</v>
       </c>
       <c r="D45">
-        <v>241.8908356879192</v>
+        <v>238.7492067570419</v>
       </c>
       <c r="E45">
-        <v>-153.691</v>
+        <v>-142.628</v>
       </c>
       <c r="F45">
-        <v>475.7089999999999</v>
+        <v>486.772</v>
       </c>
       <c r="G45">
         <v>30.3</v>
@@ -4960,37 +4971,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M45">
-        <v>112.1721822</v>
+        <v>114.7808376</v>
       </c>
       <c r="N45">
-        <v>-215.1596822</v>
+        <v>-217.7683376</v>
       </c>
       <c r="O45">
-        <v>-47.335130084</v>
+        <v>-47.909034272</v>
       </c>
       <c r="P45">
-        <v>-167.824552116</v>
+        <v>-169.859303328</v>
       </c>
       <c r="Q45">
-        <v>-53.32455211600001</v>
+        <v>-55.35930332800001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1198543346415702</v>
+        <v>0.1211767334744554</v>
       </c>
       <c r="T45">
-        <v>1.710261770013169</v>
+        <v>1.740802158763405</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>-0.2019863530835366</v>
+        <v>-0.1973957541498199</v>
       </c>
       <c r="W45">
-        <v>0.283428382057098</v>
+        <v>0.2823459188285276</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4998,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.9181197867433482</v>
+        <v>-0.8972534279537268</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5006,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1920911750302472</v>
+        <v>0.1939911750302472</v>
       </c>
       <c r="C46">
-        <v>-217.7227932429581</v>
+        <v>-231.8468627887375</v>
       </c>
       <c r="D46">
-        <v>238.7492067570419</v>
+        <v>235.6881372112625</v>
       </c>
       <c r="E46">
-        <v>-142.628</v>
+        <v>-131.565</v>
       </c>
       <c r="F46">
-        <v>486.772</v>
+        <v>497.835</v>
       </c>
       <c r="G46">
         <v>30.3</v>
@@ -5042,37 +5053,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M46">
-        <v>114.7808376</v>
+        <v>117.389493</v>
       </c>
       <c r="N46">
-        <v>-217.7683376</v>
+        <v>-220.376993</v>
       </c>
       <c r="O46">
-        <v>-47.909034272</v>
+        <v>-48.48293846</v>
       </c>
       <c r="P46">
-        <v>-169.859303328</v>
+        <v>-171.89405454</v>
       </c>
       <c r="Q46">
-        <v>-55.35930332800001</v>
+        <v>-57.39405454000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1211767334744554</v>
+        <v>0.1225472195376273</v>
       </c>
       <c r="T46">
-        <v>1.740802158763405</v>
+        <v>1.772453107104558</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>-0.1973957541498199</v>
+        <v>-0.1930091818353794</v>
       </c>
       <c r="W46">
-        <v>0.2823459188285276</v>
+        <v>0.2813115650767825</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5080,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.8972534279537268</v>
+        <v>-0.8773144628880882</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5088,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1939911750302472</v>
+        <v>0.1958911750302472</v>
       </c>
       <c r="C47">
-        <v>-231.8468627887375</v>
+        <v>-245.8934323464492</v>
       </c>
       <c r="D47">
-        <v>235.6881372112625</v>
+        <v>232.7045676535509</v>
       </c>
       <c r="E47">
-        <v>-131.565</v>
+        <v>-120.502</v>
       </c>
       <c r="F47">
-        <v>497.835</v>
+        <v>508.898</v>
       </c>
       <c r="G47">
         <v>30.3</v>
@@ -5124,37 +5135,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M47">
-        <v>117.389493</v>
+        <v>119.9981484</v>
       </c>
       <c r="N47">
-        <v>-220.376993</v>
+        <v>-222.9856484</v>
       </c>
       <c r="O47">
-        <v>-48.48293846</v>
+        <v>-49.056842648</v>
       </c>
       <c r="P47">
-        <v>-171.89405454</v>
+        <v>-173.928805752</v>
       </c>
       <c r="Q47">
-        <v>-57.39405454000001</v>
+        <v>-59.42880575200002</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1225472195376273</v>
+        <v>0.1239684643438797</v>
       </c>
       <c r="T47">
-        <v>1.772453107104558</v>
+        <v>1.805276312791679</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>-0.1930091818353794</v>
+        <v>-0.1888133300563494</v>
       </c>
       <c r="W47">
-        <v>0.2813115650767825</v>
+        <v>0.2803221832272872</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5162,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.8773144628880882</v>
+        <v>-0.8582424093470429</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5170,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1958911750302472</v>
+        <v>0.1977911750302472</v>
       </c>
       <c r="C48">
-        <v>-245.8934323464492</v>
+        <v>-259.8654083343889</v>
       </c>
       <c r="D48">
-        <v>232.7045676535509</v>
+        <v>229.7955916656111</v>
       </c>
       <c r="E48">
-        <v>-120.502</v>
+        <v>-109.439</v>
       </c>
       <c r="F48">
-        <v>508.898</v>
+        <v>519.961</v>
       </c>
       <c r="G48">
         <v>30.3</v>
@@ -5206,37 +5217,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M48">
-        <v>119.9981484</v>
+        <v>122.6068038</v>
       </c>
       <c r="N48">
-        <v>-222.9856484</v>
+        <v>-225.5943038</v>
       </c>
       <c r="O48">
-        <v>-49.056842648</v>
+        <v>-49.630746836</v>
       </c>
       <c r="P48">
-        <v>-173.928805752</v>
+        <v>-175.963556964</v>
       </c>
       <c r="Q48">
-        <v>-59.42880575200002</v>
+        <v>-61.46355696400002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1239684643438797</v>
+        <v>0.1254433410296133</v>
       </c>
       <c r="T48">
-        <v>1.805276312791679</v>
+        <v>1.839338130014164</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>-0.1888133300563494</v>
+        <v>-0.1847960251615335</v>
       </c>
       <c r="W48">
-        <v>0.2803221832272872</v>
+        <v>0.2793749027330896</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5244,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.8582424093470429</v>
+        <v>-0.8399819325524249</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5252,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1977911750302472</v>
+        <v>0.1996911750302471</v>
       </c>
       <c r="C49">
-        <v>-259.8654083343889</v>
+        <v>-273.7655536357932</v>
       </c>
       <c r="D49">
-        <v>229.7955916656111</v>
+        <v>226.9584463642068</v>
       </c>
       <c r="E49">
-        <v>-109.439</v>
+        <v>-98.37599999999998</v>
       </c>
       <c r="F49">
-        <v>519.961</v>
+        <v>531.024</v>
       </c>
       <c r="G49">
         <v>30.3</v>
@@ -5288,37 +5299,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M49">
-        <v>122.6068038</v>
+        <v>125.2154592</v>
       </c>
       <c r="N49">
-        <v>-225.5943038</v>
+        <v>-228.2029592</v>
       </c>
       <c r="O49">
-        <v>-49.630746836</v>
+        <v>-50.204651024</v>
       </c>
       <c r="P49">
-        <v>-175.963556964</v>
+        <v>-177.998308176</v>
       </c>
       <c r="Q49">
-        <v>-61.46355696400002</v>
+        <v>-63.49830817600002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1254433410296133</v>
+        <v>0.1269749437417212</v>
       </c>
       <c r="T49">
-        <v>1.839338130014164</v>
+        <v>1.874710017129821</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>-0.1847960251615335</v>
+        <v>-0.1809461079706682</v>
       </c>
       <c r="W49">
-        <v>0.2793749027330896</v>
+        <v>0.2784670922594836</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5326,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.8399819325524249</v>
+        <v>-0.8224823089575826</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5334,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1996911750302471</v>
+        <v>0.2015911750302471</v>
       </c>
       <c r="C50">
-        <v>-273.7655536357932</v>
+        <v>-287.5964963514719</v>
       </c>
       <c r="D50">
-        <v>226.9584463642068</v>
+        <v>224.1905036485281</v>
       </c>
       <c r="E50">
-        <v>-98.37599999999998</v>
+        <v>-87.31299999999999</v>
       </c>
       <c r="F50">
-        <v>531.024</v>
+        <v>542.087</v>
       </c>
       <c r="G50">
         <v>30.3</v>
@@ -5370,37 +5381,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M50">
-        <v>125.2154592</v>
+        <v>127.8241146</v>
       </c>
       <c r="N50">
-        <v>-228.2029592</v>
+        <v>-230.8116146</v>
       </c>
       <c r="O50">
-        <v>-50.204651024</v>
+        <v>-50.77855521199999</v>
       </c>
       <c r="P50">
-        <v>-177.998308176</v>
+        <v>-180.033059388</v>
       </c>
       <c r="Q50">
-        <v>-63.49830817600002</v>
+        <v>-65.533059388</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1269749437417212</v>
+        <v>0.1285666093052844</v>
       </c>
       <c r="T50">
-        <v>1.874710017129821</v>
+        <v>1.911469037073543</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>-0.1809461079706682</v>
+        <v>-0.1772533302569811</v>
       </c>
       <c r="W50">
-        <v>0.2784670922594836</v>
+        <v>0.2775963352745962</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5408,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.8224823089575826</v>
+        <v>-0.8056969557135503</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5416,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2015911750302471</v>
+        <v>0.2034911750302472</v>
       </c>
       <c r="C51">
-        <v>-287.5964963514719</v>
+        <v>-301.3607379196859</v>
       </c>
       <c r="D51">
-        <v>224.1905036485281</v>
+        <v>221.4892620803141</v>
       </c>
       <c r="E51">
-        <v>-87.31299999999999</v>
+        <v>-76.25</v>
       </c>
       <c r="F51">
-        <v>542.087</v>
+        <v>553.15</v>
       </c>
       <c r="G51">
         <v>30.3</v>
@@ -5452,37 +5463,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M51">
-        <v>127.8241146</v>
+        <v>130.43277</v>
       </c>
       <c r="N51">
-        <v>-230.8116146</v>
+        <v>-233.42027</v>
       </c>
       <c r="O51">
-        <v>-50.77855521199999</v>
+        <v>-51.3524594</v>
       </c>
       <c r="P51">
-        <v>-180.033059388</v>
+        <v>-182.0678106</v>
       </c>
       <c r="Q51">
-        <v>-65.533059388</v>
+        <v>-67.56781060000003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1285666093052844</v>
+        <v>0.1302219414913901</v>
       </c>
       <c r="T51">
-        <v>1.911469037073543</v>
+        <v>1.949698417815013</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>-0.1772533302569811</v>
+        <v>-0.1737082636518415</v>
       </c>
       <c r="W51">
-        <v>0.2775963352745962</v>
+        <v>0.2767604085691042</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5490,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.8056969557135503</v>
+        <v>-0.7895830165992794</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5498,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2034911750302472</v>
+        <v>0.2053911750302472</v>
       </c>
       <c r="C52">
-        <v>-301.3607379196859</v>
+        <v>-315.0606606560015</v>
       </c>
       <c r="D52">
-        <v>221.4892620803141</v>
+        <v>218.8523393439984</v>
       </c>
       <c r="E52">
-        <v>-76.25</v>
+        <v>-65.18700000000001</v>
       </c>
       <c r="F52">
-        <v>553.15</v>
+        <v>564.213</v>
       </c>
       <c r="G52">
         <v>30.3</v>
@@ -5534,37 +5545,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M52">
-        <v>130.43277</v>
+        <v>133.0414254</v>
       </c>
       <c r="N52">
-        <v>-233.42027</v>
+        <v>-236.0289254</v>
       </c>
       <c r="O52">
-        <v>-51.3524594</v>
+        <v>-51.926363588</v>
       </c>
       <c r="P52">
-        <v>-182.0678106</v>
+        <v>-184.102561812</v>
       </c>
       <c r="Q52">
-        <v>-67.56781060000003</v>
+        <v>-69.60256181199998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1302219414913901</v>
+        <v>0.1319448382565205</v>
       </c>
       <c r="T52">
-        <v>1.949698417815013</v>
+        <v>1.989488181443892</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>-0.1737082636518415</v>
+        <v>-0.1703022192665113</v>
       </c>
       <c r="W52">
-        <v>0.2767604085691042</v>
+        <v>0.2759572633030434</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5572,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.7895830165992794</v>
+        <v>-0.77410099666596</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5580,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2053911750302472</v>
+        <v>0.2072911750302471</v>
       </c>
       <c r="C53">
-        <v>-315.0606606560015</v>
+        <v>-328.6985347608912</v>
       </c>
       <c r="D53">
-        <v>218.8523393439984</v>
+        <v>216.2774652391088</v>
       </c>
       <c r="E53">
-        <v>-65.18700000000001</v>
+        <v>-54.12400000000002</v>
       </c>
       <c r="F53">
-        <v>564.213</v>
+        <v>575.276</v>
       </c>
       <c r="G53">
         <v>30.3</v>
@@ -5616,37 +5627,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M53">
-        <v>133.0414254</v>
+        <v>135.6500808</v>
       </c>
       <c r="N53">
-        <v>-236.0289254</v>
+        <v>-238.6375808</v>
       </c>
       <c r="O53">
-        <v>-51.926363588</v>
+        <v>-52.50026777599999</v>
       </c>
       <c r="P53">
-        <v>-184.102561812</v>
+        <v>-186.137313024</v>
       </c>
       <c r="Q53">
-        <v>-69.60256181199998</v>
+        <v>-71.63731302399998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1319448382565205</v>
+        <v>0.1337395223868647</v>
       </c>
       <c r="T53">
-        <v>1.989488181443892</v>
+        <v>2.030935851890639</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>-0.1703022192665113</v>
+        <v>-0.1670271765883091</v>
       </c>
       <c r="W53">
-        <v>0.2759572633030434</v>
+        <v>0.2751850082395233</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5654,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.77410099666596</v>
+        <v>-0.7592144390377686</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5662,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2072911750302471</v>
+        <v>0.2091911750302471</v>
       </c>
       <c r="C54">
-        <v>-328.6985347608912</v>
+        <v>-342.2765248384046</v>
       </c>
       <c r="D54">
-        <v>216.2774652391088</v>
+        <v>213.7624751615955</v>
       </c>
       <c r="E54">
-        <v>-54.12400000000002</v>
+        <v>-43.06099999999992</v>
       </c>
       <c r="F54">
-        <v>575.276</v>
+        <v>586.3390000000001</v>
       </c>
       <c r="G54">
         <v>30.3</v>
@@ -5698,37 +5709,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M54">
-        <v>135.6500808</v>
+        <v>138.2587362</v>
       </c>
       <c r="N54">
-        <v>-238.6375808</v>
+        <v>-241.2462362</v>
       </c>
       <c r="O54">
-        <v>-52.50026777599999</v>
+        <v>-53.074171964</v>
       </c>
       <c r="P54">
-        <v>-186.137313024</v>
+        <v>-188.172064236</v>
       </c>
       <c r="Q54">
-        <v>-71.63731302399998</v>
+        <v>-73.67206423599998</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1337395223868647</v>
+        <v>0.1356105760546703</v>
       </c>
       <c r="T54">
-        <v>2.030935851890639</v>
+        <v>2.074147252994695</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>-0.1670271765883091</v>
+        <v>-0.1638757204262655</v>
       </c>
       <c r="W54">
-        <v>0.2751850082395233</v>
+        <v>0.2744418948765134</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5736,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.7592144390377686</v>
+        <v>-0.7448896383012069</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5744,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2091911750302471</v>
+        <v>0.2110911750302472</v>
       </c>
       <c r="C55">
-        <v>-342.2765248384046</v>
+        <v>-355.7966959652522</v>
       </c>
       <c r="D55">
-        <v>213.7624751615955</v>
+        <v>211.3053040347478</v>
       </c>
       <c r="E55">
-        <v>-43.06099999999992</v>
+        <v>-31.99799999999993</v>
       </c>
       <c r="F55">
-        <v>586.3390000000001</v>
+        <v>597.402</v>
       </c>
       <c r="G55">
         <v>30.3</v>
@@ -5780,37 +5791,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M55">
-        <v>138.2587362</v>
+        <v>140.8673916</v>
       </c>
       <c r="N55">
-        <v>-241.2462362</v>
+        <v>-243.8548916</v>
       </c>
       <c r="O55">
-        <v>-53.074171964</v>
+        <v>-53.64807615200001</v>
       </c>
       <c r="P55">
-        <v>-188.172064236</v>
+        <v>-190.206815448</v>
       </c>
       <c r="Q55">
-        <v>-73.67206423599998</v>
+        <v>-75.70681544800001</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1356105760546703</v>
+        <v>0.1375629798819457</v>
       </c>
       <c r="T55">
-        <v>2.074147252994695</v>
+        <v>2.119237410668493</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>-0.1638757204262655</v>
+        <v>-0.1608409848628162</v>
       </c>
       <c r="W55">
-        <v>0.2744418948765134</v>
+        <v>0.273726304230652</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5818,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.7448896383012069</v>
+        <v>-0.7310953857400735</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5826,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2110911750302472</v>
+        <v>0.2129911750302471</v>
       </c>
       <c r="C56">
-        <v>-355.7966959652522</v>
+        <v>-369.2610193460669</v>
       </c>
       <c r="D56">
-        <v>211.3053040347478</v>
+        <v>208.9039806539332</v>
       </c>
       <c r="E56">
-        <v>-31.99799999999993</v>
+        <v>-20.93499999999995</v>
       </c>
       <c r="F56">
-        <v>597.402</v>
+        <v>608.465</v>
       </c>
       <c r="G56">
         <v>30.3</v>
@@ -5862,37 +5873,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M56">
-        <v>140.8673916</v>
+        <v>143.476047</v>
       </c>
       <c r="N56">
-        <v>-243.8548916</v>
+        <v>-246.463547</v>
       </c>
       <c r="O56">
-        <v>-53.64807615200001</v>
+        <v>-54.22198034</v>
       </c>
       <c r="P56">
-        <v>-190.206815448</v>
+        <v>-192.24156666</v>
       </c>
       <c r="Q56">
-        <v>-75.70681544800001</v>
+        <v>-77.74156665999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1375629798819457</v>
+        <v>0.1396021572126556</v>
       </c>
       <c r="T56">
-        <v>2.119237410668493</v>
+        <v>2.166331575350015</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>-0.1608409848628162</v>
+        <v>-0.1579166033198559</v>
       </c>
       <c r="W56">
-        <v>0.273726304230652</v>
+        <v>0.273036735062822</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5900,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.7310953857400735</v>
+        <v>-0.7178027423629811</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5908,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2129911750302471</v>
+        <v>0.2148911750302472</v>
       </c>
       <c r="C57">
-        <v>-369.2610193460669</v>
+        <v>-382.6713775873913</v>
       </c>
       <c r="D57">
-        <v>208.9039806539332</v>
+        <v>206.5566224126087</v>
       </c>
       <c r="E57">
-        <v>-20.93499999999995</v>
+        <v>-9.871999999999957</v>
       </c>
       <c r="F57">
-        <v>608.465</v>
+        <v>619.528</v>
       </c>
       <c r="G57">
         <v>30.3</v>
@@ -5944,37 +5955,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M57">
-        <v>143.476047</v>
+        <v>146.0847024</v>
       </c>
       <c r="N57">
-        <v>-246.463547</v>
+        <v>-249.0722024</v>
       </c>
       <c r="O57">
-        <v>-54.22198034</v>
+        <v>-54.79588452799999</v>
       </c>
       <c r="P57">
-        <v>-192.24156666</v>
+        <v>-194.276317872</v>
       </c>
       <c r="Q57">
-        <v>-77.74156665999999</v>
+        <v>-79.77631787199999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1396021572126556</v>
+        <v>0.1417340244220342</v>
       </c>
       <c r="T57">
-        <v>2.166331575350015</v>
+        <v>2.215566383880697</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>-0.1579166033198559</v>
+        <v>-0.1550966639748585</v>
       </c>
       <c r="W57">
-        <v>0.273036735062822</v>
+        <v>0.2723717933652717</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5982,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.7178027423629811</v>
+        <v>-0.7049848362493565</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5990,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2148911750302472</v>
+        <v>0.2167911750302472</v>
       </c>
       <c r="C58">
-        <v>-382.6713775873913</v>
+        <v>-396.0295696200475</v>
       </c>
       <c r="D58">
-        <v>206.5566224126087</v>
+        <v>204.2614303799525</v>
       </c>
       <c r="E58">
-        <v>-9.871999999999957</v>
+        <v>1.191000000000031</v>
       </c>
       <c r="F58">
-        <v>619.528</v>
+        <v>630.591</v>
       </c>
       <c r="G58">
         <v>30.3</v>
@@ -6026,37 +6037,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M58">
-        <v>146.0847024</v>
+        <v>148.6933578</v>
       </c>
       <c r="N58">
-        <v>-249.0722024</v>
+        <v>-251.6808578</v>
       </c>
       <c r="O58">
-        <v>-54.79588452799999</v>
+        <v>-55.369788716</v>
       </c>
       <c r="P58">
-        <v>-194.276317872</v>
+        <v>-196.311069084</v>
       </c>
       <c r="Q58">
-        <v>-79.77631787199999</v>
+        <v>-81.811069084</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1417340244220342</v>
+        <v>0.1439650482458024</v>
       </c>
       <c r="T58">
-        <v>2.215566383880697</v>
+        <v>2.26709118350583</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>-0.1550966639748585</v>
+        <v>-0.1523756698700364</v>
       </c>
       <c r="W58">
-        <v>0.2723717933652717</v>
+        <v>0.2717301829553546</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6064,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.7049848362493565</v>
+        <v>-0.6926166812274381</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6072,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2167911750302472</v>
+        <v>0.2186911750302472</v>
       </c>
       <c r="C59">
-        <v>-396.0295696200475</v>
+        <v>-409.3373152969394</v>
       </c>
       <c r="D59">
-        <v>204.2614303799525</v>
+        <v>202.0166847030606</v>
       </c>
       <c r="E59">
-        <v>1.191000000000031</v>
+        <v>12.25400000000002</v>
       </c>
       <c r="F59">
-        <v>630.591</v>
+        <v>641.654</v>
       </c>
       <c r="G59">
         <v>30.3</v>
@@ -6108,37 +6119,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M59">
-        <v>148.6933578</v>
+        <v>151.3020132</v>
       </c>
       <c r="N59">
-        <v>-251.6808578</v>
+        <v>-254.2895132</v>
       </c>
       <c r="O59">
-        <v>-55.369788716</v>
+        <v>-55.943692904</v>
       </c>
       <c r="P59">
-        <v>-196.311069084</v>
+        <v>-198.345820296</v>
       </c>
       <c r="Q59">
-        <v>-81.811069084</v>
+        <v>-83.845820296</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1439650482458024</v>
+        <v>0.1463023112992739</v>
       </c>
       <c r="T59">
-        <v>2.26709118350583</v>
+        <v>2.321069545017874</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>-0.1523756698700364</v>
+        <v>-0.1497485031481392</v>
       </c>
       <c r="W59">
-        <v>0.2717301829553546</v>
+        <v>0.2711106970423312</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6146,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.6926166812274381</v>
+        <v>-0.6806750143097235</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6154,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2186911750302471</v>
+        <v>0.2205911750302472</v>
       </c>
       <c r="C60">
-        <v>-409.3373152969392</v>
+        <v>-422.5962596909822</v>
       </c>
       <c r="D60">
-        <v>202.0166847030607</v>
+        <v>199.8207403090179</v>
       </c>
       <c r="E60">
-        <v>12.25399999999991</v>
+        <v>23.31700000000001</v>
       </c>
       <c r="F60">
-        <v>641.6539999999999</v>
+        <v>652.717</v>
       </c>
       <c r="G60">
         <v>30.3</v>
@@ -6190,37 +6201,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M60">
-        <v>151.3020132</v>
+        <v>153.9106686</v>
       </c>
       <c r="N60">
-        <v>-254.2895132</v>
+        <v>-256.8981686</v>
       </c>
       <c r="O60">
-        <v>-55.943692904</v>
+        <v>-56.517597092</v>
       </c>
       <c r="P60">
-        <v>-198.345820296</v>
+        <v>-200.380571508</v>
       </c>
       <c r="Q60">
-        <v>-83.845820296</v>
+        <v>-85.880571508</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1463023112992739</v>
+        <v>0.148753587184622</v>
       </c>
       <c r="T60">
-        <v>2.321069545017873</v>
+        <v>2.377680997335383</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>-0.1497485031481392</v>
+        <v>-0.1472103929252894</v>
       </c>
       <c r="W60">
-        <v>0.2711106970423312</v>
+        <v>0.2705122106517833</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6228,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.6806750143097238</v>
+        <v>-0.6691381496604063</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6236,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2205911750302472</v>
+        <v>0.2224911750302472</v>
       </c>
       <c r="C61">
-        <v>-422.5962596909822</v>
+        <v>-435.8079771157326</v>
       </c>
       <c r="D61">
-        <v>199.8207403090179</v>
+        <v>197.6720228842674</v>
       </c>
       <c r="E61">
-        <v>23.31700000000001</v>
+        <v>34.38</v>
       </c>
       <c r="F61">
-        <v>652.717</v>
+        <v>663.78</v>
       </c>
       <c r="G61">
         <v>30.3</v>
@@ -6272,37 +6283,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M61">
-        <v>153.9106686</v>
+        <v>156.519324</v>
       </c>
       <c r="N61">
-        <v>-256.8981686</v>
+        <v>-259.506824</v>
       </c>
       <c r="O61">
-        <v>-56.517597092</v>
+        <v>-57.09150128</v>
       </c>
       <c r="P61">
-        <v>-200.380571508</v>
+        <v>-202.41532272</v>
       </c>
       <c r="Q61">
-        <v>-85.880571508</v>
+        <v>-87.91532272000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.148753587184622</v>
+        <v>0.1513274268642376</v>
       </c>
       <c r="T61">
-        <v>2.377680997335383</v>
+        <v>2.437123022268767</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>-0.1472103929252894</v>
+        <v>-0.1447568863765346</v>
       </c>
       <c r="W61">
-        <v>0.2705122106517833</v>
+        <v>0.2699336738075869</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6310,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.6691381496604063</v>
+        <v>-0.657985847166066</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6318,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2224911750302472</v>
+        <v>0.2243911750302472</v>
       </c>
       <c r="C62">
-        <v>-435.8079771157326</v>
+        <v>-448.9739748893712</v>
       </c>
       <c r="D62">
-        <v>197.6720228842674</v>
+        <v>195.5690251106288</v>
       </c>
       <c r="E62">
-        <v>34.38</v>
+        <v>45.44299999999998</v>
       </c>
       <c r="F62">
-        <v>663.78</v>
+        <v>674.843</v>
       </c>
       <c r="G62">
         <v>30.3</v>
@@ -6354,37 +6365,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M62">
-        <v>156.519324</v>
+        <v>159.1279794</v>
       </c>
       <c r="N62">
-        <v>-259.506824</v>
+        <v>-262.1154794</v>
       </c>
       <c r="O62">
-        <v>-57.09150128</v>
+        <v>-57.665405468</v>
       </c>
       <c r="P62">
-        <v>-202.41532272</v>
+        <v>-204.450073932</v>
       </c>
       <c r="Q62">
-        <v>-87.91532272000001</v>
+        <v>-89.95007393199998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1513274268642376</v>
+        <v>0.1540332583222949</v>
       </c>
       <c r="T62">
-        <v>2.437123022268767</v>
+        <v>2.499613356173094</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>-0.1447568863765346</v>
+        <v>-0.1423838226654438</v>
       </c>
       <c r="W62">
-        <v>0.2699336738075869</v>
+        <v>0.2693741053845117</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6392,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.657985847166066</v>
+        <v>-0.6471991939338355</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6400,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2243911750302472</v>
+        <v>0.2262911750302472</v>
       </c>
       <c r="C63">
-        <v>-448.9739748893712</v>
+        <v>-462.0956968609464</v>
       </c>
       <c r="D63">
-        <v>195.5690251106288</v>
+        <v>193.5103031390536</v>
       </c>
       <c r="E63">
-        <v>45.44299999999998</v>
+        <v>56.50599999999997</v>
       </c>
       <c r="F63">
-        <v>674.843</v>
+        <v>685.9059999999999</v>
       </c>
       <c r="G63">
         <v>30.3</v>
@@ -6436,37 +6447,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M63">
-        <v>159.1279794</v>
+        <v>161.7366348</v>
       </c>
       <c r="N63">
-        <v>-262.1154794</v>
+        <v>-264.7241348</v>
       </c>
       <c r="O63">
-        <v>-57.665405468</v>
+        <v>-58.239309656</v>
       </c>
       <c r="P63">
-        <v>-204.450073932</v>
+        <v>-206.484825144</v>
       </c>
       <c r="Q63">
-        <v>-89.95007393199998</v>
+        <v>-91.98482514400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1540332583222949</v>
+        <v>0.1568815019623554</v>
       </c>
       <c r="T63">
-        <v>2.499613356173094</v>
+        <v>2.565392655019755</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>-0.1423838226654438</v>
+        <v>-0.1400873093966463</v>
       </c>
       <c r="W63">
-        <v>0.2693741053845117</v>
+        <v>0.2688325875557293</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6474,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.6471991939338355</v>
+        <v>-0.6367604972574836</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6482,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2262911750302472</v>
+        <v>0.2281911750302472</v>
       </c>
       <c r="C64">
-        <v>-462.0956968609464</v>
+        <v>-475.1745267162188</v>
       </c>
       <c r="D64">
-        <v>193.5103031390536</v>
+        <v>191.4944732837811</v>
       </c>
       <c r="E64">
-        <v>56.50599999999997</v>
+        <v>67.56899999999996</v>
       </c>
       <c r="F64">
-        <v>685.9059999999999</v>
+        <v>696.9689999999999</v>
       </c>
       <c r="G64">
         <v>30.3</v>
@@ -6518,37 +6529,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M64">
-        <v>161.7366348</v>
+        <v>164.3452902</v>
       </c>
       <c r="N64">
-        <v>-264.7241348</v>
+        <v>-267.3327902</v>
       </c>
       <c r="O64">
-        <v>-58.239309656</v>
+        <v>-58.813213844</v>
       </c>
       <c r="P64">
-        <v>-206.484825144</v>
+        <v>-208.519576356</v>
       </c>
       <c r="Q64">
-        <v>-91.98482514400001</v>
+        <v>-94.01957635599999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1568815019623554</v>
+        <v>0.1598837047180947</v>
       </c>
       <c r="T64">
-        <v>2.565392655019755</v>
+        <v>2.63472759164191</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>-0.1400873093966463</v>
+        <v>-0.1378637013109853</v>
       </c>
       <c r="W64">
-        <v>0.2688325875557293</v>
+        <v>0.2683082607691303</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6556,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.6367604972574836</v>
+        <v>-0.6266531877772059</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6564,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2281911750302472</v>
+        <v>0.2300911750302472</v>
       </c>
       <c r="C65">
-        <v>-475.1745267162188</v>
+        <v>-488.2117910790105</v>
       </c>
       <c r="D65">
-        <v>191.4944732837811</v>
+        <v>189.5202089209896</v>
       </c>
       <c r="E65">
-        <v>67.56899999999996</v>
+        <v>78.63200000000006</v>
       </c>
       <c r="F65">
-        <v>696.9689999999999</v>
+        <v>708.032</v>
       </c>
       <c r="G65">
         <v>30.3</v>
@@ -6600,37 +6611,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M65">
-        <v>164.3452902</v>
+        <v>166.9539456</v>
       </c>
       <c r="N65">
-        <v>-267.3327902</v>
+        <v>-269.9414456</v>
       </c>
       <c r="O65">
-        <v>-58.813213844</v>
+        <v>-59.387118032</v>
       </c>
       <c r="P65">
-        <v>-208.519576356</v>
+        <v>-210.554327568</v>
       </c>
       <c r="Q65">
-        <v>-94.01957635599999</v>
+        <v>-96.05432756800002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1598837047180947</v>
+        <v>0.1630526965158196</v>
       </c>
       <c r="T65">
-        <v>2.63472759164191</v>
+        <v>2.707914469187519</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>-0.1378637013109853</v>
+        <v>-0.1357095809780011</v>
       </c>
       <c r="W65">
-        <v>0.2683082607691303</v>
+        <v>0.2678003191946127</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6638,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.6266531877772059</v>
+        <v>-0.6168617317181868</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6646,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2300911750302472</v>
+        <v>0.2319911750302472</v>
       </c>
       <c r="C66">
-        <v>-488.2117910790105</v>
+        <v>-501.208762422665</v>
       </c>
       <c r="D66">
-        <v>189.5202089209896</v>
+        <v>187.586237577335</v>
       </c>
       <c r="E66">
-        <v>78.63200000000006</v>
+        <v>89.69500000000005</v>
       </c>
       <c r="F66">
-        <v>708.032</v>
+        <v>719.095</v>
       </c>
       <c r="G66">
         <v>30.3</v>
@@ -6682,37 +6693,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M66">
-        <v>166.9539456</v>
+        <v>169.562601</v>
       </c>
       <c r="N66">
-        <v>-269.9414456</v>
+        <v>-272.550101</v>
       </c>
       <c r="O66">
-        <v>-59.387118032</v>
+        <v>-59.96102222</v>
       </c>
       <c r="P66">
-        <v>-210.554327568</v>
+        <v>-212.58907878</v>
       </c>
       <c r="Q66">
-        <v>-96.05432756800002</v>
+        <v>-98.08907877999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1630526965158196</v>
+        <v>0.1664027735591287</v>
       </c>
       <c r="T66">
-        <v>2.707914469187519</v>
+        <v>2.785283454021448</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>-0.1357095809780011</v>
+        <v>-0.1336217412706473</v>
       </c>
       <c r="W66">
-        <v>0.2678003191946127</v>
+        <v>0.2673080065916186</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6720,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.6168617317181868</v>
+        <v>-0.6073715512302149</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6728,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2319911750302472</v>
+        <v>0.2338911750302471</v>
       </c>
       <c r="C67">
-        <v>-501.208762422665</v>
+        <v>-514.1666618050504</v>
       </c>
       <c r="D67">
-        <v>187.586237577335</v>
+        <v>185.6913381949497</v>
       </c>
       <c r="E67">
-        <v>89.69500000000005</v>
+        <v>100.758</v>
       </c>
       <c r="F67">
-        <v>719.095</v>
+        <v>730.158</v>
       </c>
       <c r="G67">
         <v>30.3</v>
@@ -6764,37 +6775,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M67">
-        <v>169.562601</v>
+        <v>172.1712564</v>
       </c>
       <c r="N67">
-        <v>-272.550101</v>
+        <v>-275.1587564</v>
       </c>
       <c r="O67">
-        <v>-59.96102222</v>
+        <v>-60.534926408</v>
       </c>
       <c r="P67">
-        <v>-212.58907878</v>
+        <v>-214.623829992</v>
       </c>
       <c r="Q67">
-        <v>-98.08907877999999</v>
+        <v>-100.123829992</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1664027735591287</v>
+        <v>0.1699499139579266</v>
       </c>
       <c r="T67">
-        <v>2.785283454021448</v>
+        <v>2.867203555610314</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>-0.1336217412706473</v>
+        <v>-0.1315971694332132</v>
       </c>
       <c r="W67">
-        <v>0.2673080065916186</v>
+        <v>0.2668306125523517</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6802,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.6073715512302149</v>
+        <v>-0.5981689519691511</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6810,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2338911750302471</v>
+        <v>0.2357911750302472</v>
       </c>
       <c r="C68">
-        <v>-514.1666618050504</v>
+        <v>-527.0866614394504</v>
       </c>
       <c r="D68">
-        <v>185.6913381949497</v>
+        <v>183.8343385605497</v>
       </c>
       <c r="E68">
-        <v>100.758</v>
+        <v>111.821</v>
       </c>
       <c r="F68">
-        <v>730.158</v>
+        <v>741.221</v>
       </c>
       <c r="G68">
         <v>30.3</v>
@@ -6846,37 +6857,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M68">
-        <v>172.1712564</v>
+        <v>174.7799118</v>
       </c>
       <c r="N68">
-        <v>-275.1587564</v>
+        <v>-277.7674118</v>
       </c>
       <c r="O68">
-        <v>-60.534926408</v>
+        <v>-61.108830596</v>
       </c>
       <c r="P68">
-        <v>-214.623829992</v>
+        <v>-216.658581204</v>
       </c>
       <c r="Q68">
-        <v>-100.123829992</v>
+        <v>-102.158581204</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1699499139579266</v>
+        <v>0.1737120325627123</v>
       </c>
       <c r="T68">
-        <v>2.867203555610314</v>
+        <v>2.95408851184093</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>-0.1315971694332132</v>
+        <v>-0.1296330325760011</v>
       </c>
       <c r="W68">
-        <v>0.2668306125523517</v>
+        <v>0.2663674690814211</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6884,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.5981689519691511</v>
+        <v>-0.5892410571636413</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6892,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2357911750302472</v>
+        <v>0.2376911750302471</v>
       </c>
       <c r="C69">
-        <v>-527.0866614394504</v>
+        <v>-539.9698871127257</v>
       </c>
       <c r="D69">
-        <v>183.8343385605497</v>
+        <v>182.0141128872743</v>
       </c>
       <c r="E69">
-        <v>111.821</v>
+        <v>122.884</v>
       </c>
       <c r="F69">
-        <v>741.221</v>
+        <v>752.284</v>
       </c>
       <c r="G69">
         <v>30.3</v>
@@ -6928,37 +6939,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M69">
-        <v>174.7799118</v>
+        <v>177.3885672</v>
       </c>
       <c r="N69">
-        <v>-277.7674118</v>
+        <v>-280.3760672</v>
       </c>
       <c r="O69">
-        <v>-61.108830596</v>
+        <v>-61.682734784</v>
       </c>
       <c r="P69">
-        <v>-216.658581204</v>
+        <v>-218.693332416</v>
       </c>
       <c r="Q69">
-        <v>-102.158581204</v>
+        <v>-104.193332416</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1737120325627123</v>
+        <v>0.177709283580297</v>
       </c>
       <c r="T69">
-        <v>2.95408851184093</v>
+        <v>3.046403777835959</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>-0.1296330325760011</v>
+        <v>-0.1277266644498834</v>
       </c>
       <c r="W69">
-        <v>0.2663674690814211</v>
+        <v>0.2659179474772825</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6966,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.5892410571636413</v>
+        <v>-0.5805757474994702</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6974,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2376911750302471</v>
+        <v>0.2395911750302472</v>
       </c>
       <c r="C70">
-        <v>-539.9698871127257</v>
+        <v>-552.8174204612224</v>
       </c>
       <c r="D70">
-        <v>182.0141128872743</v>
+        <v>180.2295795387776</v>
       </c>
       <c r="E70">
-        <v>122.884</v>
+        <v>133.947</v>
       </c>
       <c r="F70">
-        <v>752.284</v>
+        <v>763.347</v>
       </c>
       <c r="G70">
         <v>30.3</v>
@@ -7010,37 +7021,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M70">
-        <v>177.3885672</v>
+        <v>179.9972226</v>
       </c>
       <c r="N70">
-        <v>-280.3760672</v>
+        <v>-282.9847226</v>
       </c>
       <c r="O70">
-        <v>-61.682734784</v>
+        <v>-62.256638972</v>
       </c>
       <c r="P70">
-        <v>-218.693332416</v>
+        <v>-220.728083628</v>
       </c>
       <c r="Q70">
-        <v>-104.193332416</v>
+        <v>-106.228083628</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.177709283580297</v>
+        <v>0.1819644217603066</v>
       </c>
       <c r="T70">
-        <v>3.046403777835959</v>
+        <v>3.144674867443571</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>-0.1277266644498834</v>
+        <v>-0.1258755533708996</v>
       </c>
       <c r="W70">
-        <v>0.2659179474772825</v>
+        <v>0.2654814554848581</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7048,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.5805757474994702</v>
+        <v>-0.5721616062313617</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7056,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2395911750302472</v>
+        <v>0.2414911750302472</v>
       </c>
       <c r="C71">
-        <v>-552.8174204612224</v>
+        <v>-565.6303011140968</v>
       </c>
       <c r="D71">
-        <v>180.2295795387776</v>
+        <v>178.4796988859032</v>
       </c>
       <c r="E71">
-        <v>133.947</v>
+        <v>145.0100000000001</v>
       </c>
       <c r="F71">
-        <v>763.347</v>
+        <v>774.4100000000001</v>
       </c>
       <c r="G71">
         <v>30.3</v>
@@ -7092,37 +7103,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M71">
-        <v>179.9972226</v>
+        <v>182.605878</v>
       </c>
       <c r="N71">
-        <v>-282.9847226</v>
+        <v>-285.593378</v>
       </c>
       <c r="O71">
-        <v>-62.256638972</v>
+        <v>-62.83054316</v>
       </c>
       <c r="P71">
-        <v>-220.728083628</v>
+        <v>-222.76283484</v>
       </c>
       <c r="Q71">
-        <v>-106.228083628</v>
+        <v>-108.26283484</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1819644217603066</v>
+        <v>0.1865032358189835</v>
       </c>
       <c r="T71">
-        <v>3.144674867443571</v>
+        <v>3.249497363025023</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>-0.1258755533708996</v>
+        <v>-0.1240773311798868</v>
       </c>
       <c r="W71">
-        <v>0.2654814554848581</v>
+        <v>0.2650574346922173</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7130,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.5721616062313617</v>
+        <v>-0.5639878689994853</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7138,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2414911750302472</v>
+        <v>0.2433911750302472</v>
       </c>
       <c r="C72">
-        <v>-565.6303011140968</v>
+        <v>-578.4095287129828</v>
       </c>
       <c r="D72">
-        <v>178.4796988859032</v>
+        <v>176.7634712870172</v>
       </c>
       <c r="E72">
-        <v>145.0100000000001</v>
+        <v>156.0730000000001</v>
       </c>
       <c r="F72">
-        <v>774.4100000000001</v>
+        <v>785.4730000000001</v>
       </c>
       <c r="G72">
         <v>30.3</v>
@@ -7174,37 +7185,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M72">
-        <v>182.605878</v>
+        <v>185.2145334</v>
       </c>
       <c r="N72">
-        <v>-285.593378</v>
+        <v>-288.2020334</v>
       </c>
       <c r="O72">
-        <v>-62.83054316</v>
+        <v>-63.404447348</v>
       </c>
       <c r="P72">
-        <v>-222.76283484</v>
+        <v>-224.797586052</v>
       </c>
       <c r="Q72">
-        <v>-108.26283484</v>
+        <v>-110.297586052</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1865032358189835</v>
+        <v>0.1913550715368795</v>
       </c>
       <c r="T72">
-        <v>3.249497363025023</v>
+        <v>3.361548996232783</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>-0.1240773311798868</v>
+        <v>-0.1223297631350996</v>
       </c>
       <c r="W72">
-        <v>0.2650574346922173</v>
+        <v>0.2646453581472565</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7212,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.5639878689994853</v>
+        <v>-0.5560443778868163</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7220,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2433911750302472</v>
+        <v>0.2452911750302472</v>
       </c>
       <c r="C73">
-        <v>-578.4095287129826</v>
+        <v>-591.1560648162434</v>
       </c>
       <c r="D73">
-        <v>176.7634712870173</v>
+        <v>175.0799351837565</v>
       </c>
       <c r="E73">
-        <v>156.073</v>
+        <v>167.136</v>
       </c>
       <c r="F73">
-        <v>785.473</v>
+        <v>796.5359999999999</v>
       </c>
       <c r="G73">
         <v>30.3</v>
@@ -7256,37 +7267,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M73">
-        <v>185.2145334</v>
+        <v>187.8231888</v>
       </c>
       <c r="N73">
-        <v>-288.2020334</v>
+        <v>-290.8106888</v>
       </c>
       <c r="O73">
-        <v>-63.404447348</v>
+        <v>-63.978351536</v>
       </c>
       <c r="P73">
-        <v>-224.797586052</v>
+        <v>-226.832337264</v>
       </c>
       <c r="Q73">
-        <v>-110.297586052</v>
+        <v>-112.332337264</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1913550715368794</v>
+        <v>0.1965534669489108</v>
       </c>
       <c r="T73">
-        <v>3.361548996232782</v>
+        <v>3.48160431752681</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>-0.1223297631350996</v>
+        <v>-0.1206307386471122</v>
       </c>
       <c r="W73">
-        <v>0.2646453581472565</v>
+        <v>0.2642447281729891</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7294,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.5560443778868167</v>
+        <v>-0.5483215393050551</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7302,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2452911750302472</v>
+        <v>0.2471911750302471</v>
       </c>
       <c r="C74">
-        <v>-591.1560648162434</v>
+        <v>-603.8708346954309</v>
       </c>
       <c r="D74">
-        <v>175.0799351837565</v>
+        <v>173.4281653045691</v>
       </c>
       <c r="E74">
-        <v>167.136</v>
+        <v>178.199</v>
       </c>
       <c r="F74">
-        <v>796.5359999999999</v>
+        <v>807.5989999999999</v>
       </c>
       <c r="G74">
         <v>30.3</v>
@@ -7338,37 +7349,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M74">
-        <v>187.8231888</v>
+        <v>190.4318442</v>
       </c>
       <c r="N74">
-        <v>-290.8106888</v>
+        <v>-293.4193442</v>
       </c>
       <c r="O74">
-        <v>-63.978351536</v>
+        <v>-64.55225572400001</v>
       </c>
       <c r="P74">
-        <v>-226.832337264</v>
+        <v>-228.867088476</v>
       </c>
       <c r="Q74">
-        <v>-112.332337264</v>
+        <v>-114.367088476</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1965534669489108</v>
+        <v>0.2021369286877594</v>
       </c>
       <c r="T74">
-        <v>3.48160431752681</v>
+        <v>3.610552625583358</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>-0.1206307386471122</v>
+        <v>-0.1189782627752339</v>
       </c>
       <c r="W74">
-        <v>0.2642447281729891</v>
+        <v>0.2638550743624001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7376,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.5483215393050551</v>
+        <v>-0.5408102853419723</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7384,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2471911750302471</v>
+        <v>0.2490911750302471</v>
       </c>
       <c r="C75">
-        <v>-603.8708346954309</v>
+        <v>-616.5547290310047</v>
       </c>
       <c r="D75">
-        <v>173.4281653045691</v>
+        <v>171.8072709689952</v>
       </c>
       <c r="E75">
-        <v>178.199</v>
+        <v>189.2619999999999</v>
       </c>
       <c r="F75">
-        <v>807.5989999999999</v>
+        <v>818.6619999999999</v>
       </c>
       <c r="G75">
         <v>30.3</v>
@@ -7420,37 +7431,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M75">
-        <v>190.4318442</v>
+        <v>193.0404996</v>
       </c>
       <c r="N75">
-        <v>-293.4193442</v>
+        <v>-296.0279996</v>
       </c>
       <c r="O75">
-        <v>-64.55225572400001</v>
+        <v>-65.12615991199999</v>
       </c>
       <c r="P75">
-        <v>-228.867088476</v>
+        <v>-230.901839688</v>
       </c>
       <c r="Q75">
-        <v>-114.367088476</v>
+        <v>-116.401839688</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2021369286877594</v>
+        <v>0.2081498874834424</v>
       </c>
       <c r="T75">
-        <v>3.610552625583358</v>
+        <v>3.749420034259641</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>-0.1189782627752339</v>
+        <v>-0.1173704484134064</v>
       </c>
       <c r="W75">
-        <v>0.2638550743624001</v>
+        <v>0.2634759517358812</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7458,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.5408102853419723</v>
+        <v>-0.5335020382427564</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7466,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2490911750302471</v>
+        <v>0.2509911750302471</v>
       </c>
       <c r="C76">
-        <v>-616.5547290310047</v>
+        <v>-629.2086055138407</v>
       </c>
       <c r="D76">
-        <v>171.8072709689952</v>
+        <v>170.2163944861592</v>
       </c>
       <c r="E76">
-        <v>189.2619999999999</v>
+        <v>200.3249999999999</v>
       </c>
       <c r="F76">
-        <v>818.6619999999999</v>
+        <v>829.7249999999999</v>
       </c>
       <c r="G76">
         <v>30.3</v>
@@ -7502,37 +7513,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M76">
-        <v>193.0404996</v>
+        <v>195.649155</v>
       </c>
       <c r="N76">
-        <v>-296.0279996</v>
+        <v>-298.636655</v>
       </c>
       <c r="O76">
-        <v>-65.12615991199999</v>
+        <v>-65.70006409999999</v>
       </c>
       <c r="P76">
-        <v>-230.901839688</v>
+        <v>-232.9365909</v>
       </c>
       <c r="Q76">
-        <v>-116.401839688</v>
+        <v>-118.4365909</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2081498874834424</v>
+        <v>0.2146438829827801</v>
       </c>
       <c r="T76">
-        <v>3.749420034259641</v>
+        <v>3.899396835630027</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>-0.1173704484134064</v>
+        <v>-0.1158055091012277</v>
       </c>
       <c r="W76">
-        <v>0.2634759517358812</v>
+        <v>0.2631069390460695</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7540,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.5335020382427564</v>
+        <v>-0.526388677732853</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7548,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2509911750302471</v>
+        <v>0.2528911750302472</v>
       </c>
       <c r="C77">
-        <v>-629.2086055138407</v>
+        <v>-641.8332903585788</v>
       </c>
       <c r="D77">
-        <v>170.2163944861592</v>
+        <v>168.6547096414213</v>
       </c>
       <c r="E77">
-        <v>200.3249999999999</v>
+        <v>211.388</v>
       </c>
       <c r="F77">
-        <v>829.7249999999999</v>
+        <v>840.788</v>
       </c>
       <c r="G77">
         <v>30.3</v>
@@ -7584,37 +7595,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M77">
-        <v>195.649155</v>
+        <v>198.2578104</v>
       </c>
       <c r="N77">
-        <v>-298.636655</v>
+        <v>-301.2453104</v>
       </c>
       <c r="O77">
-        <v>-65.70006409999999</v>
+        <v>-66.27396828800001</v>
       </c>
       <c r="P77">
-        <v>-232.9365909</v>
+        <v>-234.971342112</v>
       </c>
       <c r="Q77">
-        <v>-118.4365909</v>
+        <v>-120.471342112</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2146438829827801</v>
+        <v>0.2216790447737293</v>
       </c>
       <c r="T77">
-        <v>3.899396835630027</v>
+        <v>4.061871703781279</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>-0.1158055091012277</v>
+        <v>-0.1142817524025273</v>
       </c>
       <c r="W77">
-        <v>0.2631069390460695</v>
+        <v>0.262747637216516</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7622,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.526388677732853</v>
+        <v>-0.5194625109205784</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7630,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2528911750302472</v>
+        <v>0.2547911750302472</v>
       </c>
       <c r="C78">
-        <v>-641.8332903585788</v>
+        <v>-654.4295797344211</v>
       </c>
       <c r="D78">
-        <v>168.6547096414213</v>
+        <v>167.121420265579</v>
       </c>
       <c r="E78">
-        <v>211.388</v>
+        <v>222.451</v>
       </c>
       <c r="F78">
-        <v>840.788</v>
+        <v>851.851</v>
       </c>
       <c r="G78">
         <v>30.3</v>
@@ -7666,37 +7677,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M78">
-        <v>198.2578104</v>
+        <v>200.8664658</v>
       </c>
       <c r="N78">
-        <v>-301.2453104</v>
+        <v>-303.8539658</v>
       </c>
       <c r="O78">
-        <v>-66.27396828800001</v>
+        <v>-66.84787247600001</v>
       </c>
       <c r="P78">
-        <v>-234.971342112</v>
+        <v>-237.006093324</v>
       </c>
       <c r="Q78">
-        <v>-120.471342112</v>
+        <v>-122.506093324</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2216790447737293</v>
+        <v>0.2293259597638915</v>
       </c>
       <c r="T78">
-        <v>4.061871703781279</v>
+        <v>4.238474821336986</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>-0.1142817524025273</v>
+        <v>-0.1127975737998971</v>
       </c>
       <c r="W78">
-        <v>0.262747637216516</v>
+        <v>0.2623976679020157</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7704,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.5194625109205784</v>
+        <v>-0.5127162445449867</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7712,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2547911750302472</v>
+        <v>0.2566911750302472</v>
       </c>
       <c r="C79">
-        <v>-654.4295797344211</v>
+        <v>-666.9982411185879</v>
       </c>
       <c r="D79">
-        <v>167.121420265579</v>
+        <v>165.6157588814121</v>
       </c>
       <c r="E79">
-        <v>222.451</v>
+        <v>233.514</v>
       </c>
       <c r="F79">
-        <v>851.851</v>
+        <v>862.914</v>
       </c>
       <c r="G79">
         <v>30.3</v>
@@ -7748,37 +7759,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M79">
-        <v>200.8664658</v>
+        <v>203.4751212</v>
       </c>
       <c r="N79">
-        <v>-303.8539658</v>
+        <v>-306.4626212</v>
       </c>
       <c r="O79">
-        <v>-66.84787247600001</v>
+        <v>-67.42177666400001</v>
       </c>
       <c r="P79">
-        <v>-237.006093324</v>
+        <v>-239.040844536</v>
       </c>
       <c r="Q79">
-        <v>-122.506093324</v>
+        <v>-124.540844536</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2293259597638915</v>
+        <v>0.2376680488440684</v>
       </c>
       <c r="T79">
-        <v>4.238474821336986</v>
+        <v>4.431132767761395</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>-0.1127975737998971</v>
+        <v>-0.1113514510588727</v>
       </c>
       <c r="W79">
-        <v>0.2623976679020157</v>
+        <v>0.2620566721596822</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7786,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.5127162445449867</v>
+        <v>-0.5061429593585123</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7794,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2566911750302472</v>
+        <v>0.2585911750302471</v>
       </c>
       <c r="C80">
-        <v>-666.9982411185879</v>
+        <v>-679.5400145772613</v>
       </c>
       <c r="D80">
-        <v>165.6157588814121</v>
+        <v>164.1369854227386</v>
       </c>
       <c r="E80">
-        <v>233.514</v>
+        <v>244.577</v>
       </c>
       <c r="F80">
-        <v>862.914</v>
+        <v>873.977</v>
       </c>
       <c r="G80">
         <v>30.3</v>
@@ -7830,37 +7841,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M80">
-        <v>203.4751212</v>
+        <v>206.0837766</v>
       </c>
       <c r="N80">
-        <v>-306.4626212</v>
+        <v>-309.0712766</v>
       </c>
       <c r="O80">
-        <v>-67.42177666400001</v>
+        <v>-67.99568085199999</v>
       </c>
       <c r="P80">
-        <v>-239.040844536</v>
+        <v>-241.075595748</v>
       </c>
       <c r="Q80">
-        <v>-124.540844536</v>
+        <v>-126.575595748</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2376680488440684</v>
+        <v>0.2468046225985478</v>
       </c>
       <c r="T80">
-        <v>4.431132767761395</v>
+        <v>4.642139090035747</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>-0.1113514510588727</v>
+        <v>-0.1099419390201528</v>
       </c>
       <c r="W80">
-        <v>0.2620566721596822</v>
+        <v>0.261724309220952</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7868,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.5061429593585123</v>
+        <v>-0.49973608645524</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7876,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2585911750302471</v>
+        <v>0.2604911750302472</v>
       </c>
       <c r="C81">
-        <v>-679.5400145772613</v>
+        <v>-692.0556139785142</v>
       </c>
       <c r="D81">
-        <v>164.1369854227386</v>
+        <v>162.6843860214858</v>
       </c>
       <c r="E81">
-        <v>244.577</v>
+        <v>255.64</v>
       </c>
       <c r="F81">
-        <v>873.977</v>
+        <v>885.04</v>
       </c>
       <c r="G81">
         <v>30.3</v>
@@ -7912,37 +7923,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M81">
-        <v>206.0837766</v>
+        <v>208.692432</v>
       </c>
       <c r="N81">
-        <v>-309.0712766</v>
+        <v>-311.679932</v>
       </c>
       <c r="O81">
-        <v>-67.99568085199999</v>
+        <v>-68.56958504000001</v>
       </c>
       <c r="P81">
-        <v>-241.075595748</v>
+        <v>-243.11034696</v>
       </c>
       <c r="Q81">
-        <v>-126.575595748</v>
+        <v>-128.61034696</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2468046225985478</v>
+        <v>0.2568548537284752</v>
       </c>
       <c r="T81">
-        <v>4.642139090035747</v>
+        <v>4.874246044537535</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>-0.1099419390201528</v>
+        <v>-0.1085676647824009</v>
       </c>
       <c r="W81">
-        <v>0.261724309220952</v>
+        <v>0.2614002553556902</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7950,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.49973608645524</v>
+        <v>-0.4934893853745497</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7958,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2604911750302472</v>
+        <v>0.2623911750302472</v>
       </c>
       <c r="C82">
-        <v>-692.0556139785142</v>
+        <v>-704.5457281413959</v>
       </c>
       <c r="D82">
-        <v>162.6843860214858</v>
+        <v>161.2572718586042</v>
       </c>
       <c r="E82">
-        <v>255.64</v>
+        <v>266.7030000000001</v>
       </c>
       <c r="F82">
-        <v>885.04</v>
+        <v>896.1030000000001</v>
       </c>
       <c r="G82">
         <v>30.3</v>
@@ -7994,37 +8005,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M82">
-        <v>208.692432</v>
+        <v>211.3010874</v>
       </c>
       <c r="N82">
-        <v>-311.679932</v>
+        <v>-314.2885874</v>
       </c>
       <c r="O82">
-        <v>-68.56958504000001</v>
+        <v>-69.14348922800001</v>
       </c>
       <c r="P82">
-        <v>-243.11034696</v>
+        <v>-245.145098172</v>
       </c>
       <c r="Q82">
-        <v>-128.61034696</v>
+        <v>-130.645098172</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2568548537284752</v>
+        <v>0.2679630039247107</v>
       </c>
       <c r="T82">
-        <v>4.874246044537535</v>
+        <v>5.13078531003951</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>-0.1085676647824009</v>
+        <v>-0.1072273232418774</v>
       </c>
       <c r="W82">
-        <v>0.2614002553556902</v>
+        <v>0.2610842028204347</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8032,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.4934893853745497</v>
+        <v>-0.4873969238267157</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8040,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2623911750302472</v>
+        <v>0.2642911750302472</v>
       </c>
       <c r="C83">
-        <v>-704.5457281413959</v>
+        <v>-717.0110219250643</v>
       </c>
       <c r="D83">
-        <v>161.2572718586042</v>
+        <v>159.8549780749358</v>
       </c>
       <c r="E83">
-        <v>266.7030000000001</v>
+        <v>277.7660000000001</v>
       </c>
       <c r="F83">
-        <v>896.1030000000001</v>
+        <v>907.1660000000001</v>
       </c>
       <c r="G83">
         <v>30.3</v>
@@ -8076,37 +8087,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M83">
-        <v>211.3010874</v>
+        <v>213.9097428</v>
       </c>
       <c r="N83">
-        <v>-314.2885874</v>
+        <v>-316.8972428</v>
       </c>
       <c r="O83">
-        <v>-69.14348922800001</v>
+        <v>-69.71739341600001</v>
       </c>
       <c r="P83">
-        <v>-245.145098172</v>
+        <v>-247.179849384</v>
       </c>
       <c r="Q83">
-        <v>-130.645098172</v>
+        <v>-132.679849384</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2679630039247107</v>
+        <v>0.2803053930316391</v>
       </c>
       <c r="T83">
-        <v>5.13078531003951</v>
+        <v>5.415828938375039</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>-0.1072273232418774</v>
+        <v>-0.1059196729584399</v>
       </c>
       <c r="W83">
-        <v>0.2610842028204347</v>
+        <v>0.2607758588836002</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8114,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.4873969238267157</v>
+        <v>-0.4814530589019994</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8122,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2642911750302472</v>
+        <v>0.2661911750302472</v>
       </c>
       <c r="C84">
-        <v>-717.0110219250643</v>
+        <v>-729.4521372615823</v>
       </c>
       <c r="D84">
-        <v>159.8549780749358</v>
+        <v>158.4768627384178</v>
       </c>
       <c r="E84">
-        <v>277.7660000000001</v>
+        <v>288.8290000000001</v>
       </c>
       <c r="F84">
-        <v>907.1660000000001</v>
+        <v>918.229</v>
       </c>
       <c r="G84">
         <v>30.3</v>
@@ -8158,37 +8169,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M84">
-        <v>213.9097428</v>
+        <v>216.5183982</v>
       </c>
       <c r="N84">
-        <v>-316.8972428</v>
+        <v>-319.5058982</v>
       </c>
       <c r="O84">
-        <v>-69.71739341600001</v>
+        <v>-70.29129760399999</v>
       </c>
       <c r="P84">
-        <v>-247.179849384</v>
+        <v>-249.214600596</v>
       </c>
       <c r="Q84">
-        <v>-132.679849384</v>
+        <v>-134.714600596</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2803053930316391</v>
+        <v>0.2940998279158533</v>
       </c>
       <c r="T84">
-        <v>5.415828938375039</v>
+        <v>5.734407111220631</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>-0.1059196729584399</v>
+        <v>-0.1046435323203864</v>
       </c>
       <c r="W84">
-        <v>0.2607758588836002</v>
+        <v>0.2604749449211471</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8196,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.4814530589019994</v>
+        <v>-0.47565241963812</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8204,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2661911750302472</v>
+        <v>0.2680911750302472</v>
       </c>
       <c r="C85">
-        <v>-729.4521372615823</v>
+        <v>-741.8696941357452</v>
       </c>
       <c r="D85">
-        <v>158.4768627384178</v>
+        <v>157.1223058642548</v>
       </c>
       <c r="E85">
-        <v>288.8290000000001</v>
+        <v>299.8920000000001</v>
       </c>
       <c r="F85">
-        <v>918.229</v>
+        <v>929.292</v>
       </c>
       <c r="G85">
         <v>30.3</v>
@@ -8240,37 +8251,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M85">
-        <v>216.5183982</v>
+        <v>219.1270536</v>
       </c>
       <c r="N85">
-        <v>-319.5058982</v>
+        <v>-322.1145536</v>
       </c>
       <c r="O85">
-        <v>-70.29129760399999</v>
+        <v>-70.86520179200001</v>
       </c>
       <c r="P85">
-        <v>-249.214600596</v>
+        <v>-251.249351808</v>
       </c>
       <c r="Q85">
-        <v>-134.714600596</v>
+        <v>-136.749351808</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2940998279158533</v>
+        <v>0.3096185671605941</v>
       </c>
       <c r="T85">
-        <v>5.734407111220631</v>
+        <v>6.092807555671921</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>-0.1046435323203864</v>
+        <v>-0.103397775983239</v>
       </c>
       <c r="W85">
-        <v>0.2604749449211471</v>
+        <v>0.2601811955768478</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8278,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.47565241963812</v>
+        <v>-0.4699898908329045</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8286,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2680911750302472</v>
+        <v>0.2699911750302472</v>
       </c>
       <c r="C86">
-        <v>-741.8696941357451</v>
+        <v>-754.264291515088</v>
       </c>
       <c r="D86">
-        <v>157.1223058642548</v>
+        <v>155.790708484912</v>
       </c>
       <c r="E86">
-        <v>299.8919999999999</v>
+        <v>310.9549999999999</v>
       </c>
       <c r="F86">
-        <v>929.2919999999999</v>
+        <v>940.3549999999999</v>
       </c>
       <c r="G86">
         <v>30.3</v>
@@ -8322,37 +8333,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M86">
-        <v>219.1270536</v>
+        <v>221.735709</v>
       </c>
       <c r="N86">
-        <v>-322.1145536</v>
+        <v>-324.723209</v>
       </c>
       <c r="O86">
-        <v>-70.86520179199999</v>
+        <v>-71.43910597999999</v>
       </c>
       <c r="P86">
-        <v>-251.249351808</v>
+        <v>-253.28410302</v>
       </c>
       <c r="Q86">
-        <v>-136.749351808</v>
+        <v>-138.78410302</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3096185671605939</v>
+        <v>0.3272064716379669</v>
       </c>
       <c r="T86">
-        <v>6.092807555671916</v>
+        <v>6.498994726050045</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>-0.103397775983239</v>
+        <v>-0.1021813315599068</v>
       </c>
       <c r="W86">
-        <v>0.2601811955768478</v>
+        <v>0.259894357981826</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8360,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.4699898908329043</v>
+        <v>-0.4644605979995762</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8368,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2699911750302472</v>
+        <v>0.2718911750302471</v>
       </c>
       <c r="C87">
-        <v>-754.264291515088</v>
+        <v>-766.6365082329971</v>
       </c>
       <c r="D87">
-        <v>155.790708484912</v>
+        <v>154.4814917670028</v>
       </c>
       <c r="E87">
-        <v>310.9549999999999</v>
+        <v>322.0179999999999</v>
       </c>
       <c r="F87">
-        <v>940.3549999999999</v>
+        <v>951.4179999999999</v>
       </c>
       <c r="G87">
         <v>30.3</v>
@@ -8404,37 +8415,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M87">
-        <v>221.735709</v>
+        <v>224.3443644</v>
       </c>
       <c r="N87">
-        <v>-324.723209</v>
+        <v>-327.3318644</v>
       </c>
       <c r="O87">
-        <v>-71.43910597999999</v>
+        <v>-72.01301016799999</v>
       </c>
       <c r="P87">
-        <v>-253.28410302</v>
+        <v>-255.318854232</v>
       </c>
       <c r="Q87">
-        <v>-138.78410302</v>
+        <v>-140.818854232</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3272064716379669</v>
+        <v>0.3473069338978217</v>
       </c>
       <c r="T87">
-        <v>6.498994726050045</v>
+        <v>6.963208635053619</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>-0.1021813315599068</v>
+        <v>-0.1009931765417683</v>
       </c>
       <c r="W87">
-        <v>0.259894357981826</v>
+        <v>0.2596141910285489</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8442,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.4644605979995762</v>
+        <v>-0.4590598933716741</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8450,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2718911750302471</v>
+        <v>0.2737911750302472</v>
       </c>
       <c r="C88">
-        <v>-766.6365082329971</v>
+        <v>-778.9869038276661</v>
       </c>
       <c r="D88">
-        <v>154.4814917670028</v>
+        <v>153.194096172334</v>
       </c>
       <c r="E88">
-        <v>322.0179999999999</v>
+        <v>333.081</v>
       </c>
       <c r="F88">
-        <v>951.4179999999999</v>
+        <v>962.481</v>
       </c>
       <c r="G88">
         <v>30.3</v>
@@ -8486,37 +8497,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M88">
-        <v>224.3443644</v>
+        <v>226.9530198</v>
       </c>
       <c r="N88">
-        <v>-327.3318644</v>
+        <v>-329.9405198</v>
       </c>
       <c r="O88">
-        <v>-72.01301016799999</v>
+        <v>-72.58691435600001</v>
       </c>
       <c r="P88">
-        <v>-255.318854232</v>
+        <v>-257.353605444</v>
       </c>
       <c r="Q88">
-        <v>-140.818854232</v>
+        <v>-142.853605444</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3473069338978217</v>
+        <v>0.3704997749668849</v>
       </c>
       <c r="T88">
-        <v>6.963208635053619</v>
+        <v>7.498840068519283</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>-0.1009931765417683</v>
+        <v>-0.0998323354320928</v>
       </c>
       <c r="W88">
-        <v>0.2596141910285489</v>
+        <v>0.2593404646948875</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8524,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.4590598933716741</v>
+        <v>-0.453783342873149</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8532,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2737911750302472</v>
+        <v>0.2756911750302471</v>
       </c>
       <c r="C89">
-        <v>-778.9869038276661</v>
+        <v>-791.3160193394474</v>
       </c>
       <c r="D89">
-        <v>153.194096172334</v>
+        <v>151.9279806605526</v>
       </c>
       <c r="E89">
-        <v>333.081</v>
+        <v>344.144</v>
       </c>
       <c r="F89">
-        <v>962.481</v>
+        <v>973.544</v>
       </c>
       <c r="G89">
         <v>30.3</v>
@@ -8568,37 +8579,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M89">
-        <v>226.9530198</v>
+        <v>229.5616752</v>
       </c>
       <c r="N89">
-        <v>-329.9405198</v>
+        <v>-332.5491752</v>
       </c>
       <c r="O89">
-        <v>-72.58691435600001</v>
+        <v>-73.16081854399999</v>
       </c>
       <c r="P89">
-        <v>-257.353605444</v>
+        <v>-259.388356656</v>
       </c>
       <c r="Q89">
-        <v>-142.853605444</v>
+        <v>-144.888356656</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3704997749668849</v>
+        <v>0.3975580895474586</v>
       </c>
       <c r="T89">
-        <v>7.498840068519283</v>
+        <v>8.123743407562557</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>-0.0998323354320928</v>
+        <v>-0.09869787707490993</v>
       </c>
       <c r="W89">
-        <v>0.2593404646948875</v>
+        <v>0.2590729594142637</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8606,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.453783342873149</v>
+        <v>-0.4486267139768632</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8614,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2756911750302471</v>
+        <v>0.2775911750302472</v>
       </c>
       <c r="C90">
-        <v>-791.3160193394474</v>
+        <v>-803.6243780689908</v>
       </c>
       <c r="D90">
-        <v>151.9279806605526</v>
+        <v>150.6826219310091</v>
       </c>
       <c r="E90">
-        <v>344.144</v>
+        <v>355.207</v>
       </c>
       <c r="F90">
-        <v>973.544</v>
+        <v>984.607</v>
       </c>
       <c r="G90">
         <v>30.3</v>
@@ -8650,37 +8661,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M90">
-        <v>229.5616752</v>
+        <v>232.1703306</v>
       </c>
       <c r="N90">
-        <v>-332.5491752</v>
+        <v>-335.1578306</v>
       </c>
       <c r="O90">
-        <v>-73.16081854399999</v>
+        <v>-73.73472273200001</v>
       </c>
       <c r="P90">
-        <v>-259.388356656</v>
+        <v>-261.423107868</v>
       </c>
       <c r="Q90">
-        <v>-144.888356656</v>
+        <v>-146.923107868</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3975580895474586</v>
+        <v>0.4295360976881368</v>
       </c>
       <c r="T90">
-        <v>8.123743407562557</v>
+        <v>8.862265535522791</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>-0.09869787707490993</v>
+        <v>-0.09758891216395589</v>
       </c>
       <c r="W90">
-        <v>0.2590729594142637</v>
+        <v>0.2588114654882608</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8688,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.4486267139768632</v>
+        <v>-0.4435859643816178</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8696,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2775911750302472</v>
+        <v>0.2794911750302472</v>
       </c>
       <c r="C91">
-        <v>-803.6243780689908</v>
+        <v>-815.9124862983959</v>
       </c>
       <c r="D91">
-        <v>150.6826219310091</v>
+        <v>149.457513701604</v>
       </c>
       <c r="E91">
-        <v>355.207</v>
+        <v>366.27</v>
       </c>
       <c r="F91">
-        <v>984.607</v>
+        <v>995.67</v>
       </c>
       <c r="G91">
         <v>30.3</v>
@@ -8732,37 +8743,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M91">
-        <v>232.1703306</v>
+        <v>234.778986</v>
       </c>
       <c r="N91">
-        <v>-335.1578306</v>
+        <v>-337.766486</v>
       </c>
       <c r="O91">
-        <v>-73.73472273200001</v>
+        <v>-74.30862691999999</v>
       </c>
       <c r="P91">
-        <v>-261.423107868</v>
+        <v>-263.45785908</v>
       </c>
       <c r="Q91">
-        <v>-146.923107868</v>
+        <v>-148.95785908</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4295360976881368</v>
+        <v>0.4679097074569504</v>
       </c>
       <c r="T91">
-        <v>8.862265535522791</v>
+        <v>9.74849208907507</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>-0.09758891216395589</v>
+        <v>-0.0965045909176897</v>
       </c>
       <c r="W91">
-        <v>0.2588114654882608</v>
+        <v>0.2585557825383913</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8770,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.4435859643816178</v>
+        <v>-0.438657231444044</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8778,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2794911750302472</v>
+        <v>0.2813911750302472</v>
       </c>
       <c r="C92">
-        <v>-815.9124862983959</v>
+        <v>-828.18083397747</v>
       </c>
       <c r="D92">
-        <v>149.457513701604</v>
+        <v>148.2521660225299</v>
       </c>
       <c r="E92">
-        <v>366.27</v>
+        <v>377.333</v>
       </c>
       <c r="F92">
-        <v>995.67</v>
+        <v>1006.733</v>
       </c>
       <c r="G92">
         <v>30.3</v>
@@ -8814,37 +8825,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M92">
-        <v>234.778986</v>
+        <v>237.3876414</v>
       </c>
       <c r="N92">
-        <v>-337.766486</v>
+        <v>-340.3751414</v>
       </c>
       <c r="O92">
-        <v>-74.30862691999999</v>
+        <v>-74.88253110800001</v>
       </c>
       <c r="P92">
-        <v>-263.45785908</v>
+        <v>-265.492610292</v>
       </c>
       <c r="Q92">
-        <v>-148.95785908</v>
+        <v>-150.992610292</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4679097074569504</v>
+        <v>0.5148107860632782</v>
       </c>
       <c r="T92">
-        <v>9.74849208907507</v>
+        <v>10.83165787675008</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>-0.0965045909176897</v>
+        <v>-0.0954441009076052</v>
       </c>
       <c r="W92">
-        <v>0.2585557825383913</v>
+        <v>0.2583057189940133</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8852,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.438657231444044</v>
+        <v>-0.4338368223072964</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8860,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2813911750302472</v>
+        <v>0.2832911750302471</v>
       </c>
       <c r="C93">
-        <v>-828.18083397747</v>
+        <v>-840.429895377044</v>
       </c>
       <c r="D93">
-        <v>148.2521660225299</v>
+        <v>147.0661046229561</v>
       </c>
       <c r="E93">
-        <v>377.333</v>
+        <v>388.3960000000001</v>
       </c>
       <c r="F93">
-        <v>1006.733</v>
+        <v>1017.796</v>
       </c>
       <c r="G93">
         <v>30.3</v>
@@ -8896,37 +8907,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M93">
-        <v>237.3876414</v>
+        <v>239.9962968</v>
       </c>
       <c r="N93">
-        <v>-340.3751414</v>
+        <v>-342.9837968</v>
       </c>
       <c r="O93">
-        <v>-74.88253110800001</v>
+        <v>-75.456435296</v>
       </c>
       <c r="P93">
-        <v>-265.492610292</v>
+        <v>-267.527361504</v>
       </c>
       <c r="Q93">
-        <v>-150.992610292</v>
+        <v>-153.027361504</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5148107860632782</v>
+        <v>0.5734371343211883</v>
       </c>
       <c r="T93">
-        <v>10.83165787675008</v>
+        <v>12.18561511134384</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>-0.0954441009076052</v>
+        <v>-0.09440666502817471</v>
       </c>
       <c r="W93">
-        <v>0.2583057189940133</v>
+        <v>0.2580610916136436</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8934,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.4338368223072964</v>
+        <v>-0.4291212046735213</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8942,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2832911750302471</v>
+        <v>0.2851911750302472</v>
       </c>
       <c r="C94">
-        <v>-840.429895377044</v>
+        <v>-852.6601297111763</v>
       </c>
       <c r="D94">
-        <v>147.0661046229561</v>
+        <v>145.8988702888237</v>
       </c>
       <c r="E94">
-        <v>388.3960000000001</v>
+        <v>399.4589999999999</v>
       </c>
       <c r="F94">
-        <v>1017.796</v>
+        <v>1028.859</v>
       </c>
       <c r="G94">
         <v>30.3</v>
@@ -8978,37 +8989,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M94">
-        <v>239.9962968</v>
+        <v>242.6049522</v>
       </c>
       <c r="N94">
-        <v>-342.9837968</v>
+        <v>-345.5924522</v>
       </c>
       <c r="O94">
-        <v>-75.456435296</v>
+        <v>-76.030339484</v>
       </c>
       <c r="P94">
-        <v>-267.527361504</v>
+        <v>-269.562112716</v>
       </c>
       <c r="Q94">
-        <v>-153.027361504</v>
+        <v>-155.062112716</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5734371343211883</v>
+        <v>0.6488138677956438</v>
       </c>
       <c r="T94">
-        <v>12.18561511134384</v>
+        <v>13.92641727010725</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>-0.09440666502817471</v>
+        <v>-0.09339153959776425</v>
       </c>
       <c r="W94">
-        <v>0.2580610916136436</v>
+        <v>0.2578217250371528</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9016,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.4291212046735213</v>
+        <v>-0.4245069981716556</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9024,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2851911750302472</v>
+        <v>0.2870911750302472</v>
       </c>
       <c r="C95">
-        <v>-852.6601297111763</v>
+        <v>-864.8719817299625</v>
       </c>
       <c r="D95">
-        <v>145.8988702888237</v>
+        <v>144.7500182700376</v>
       </c>
       <c r="E95">
-        <v>399.4589999999999</v>
+        <v>410.522</v>
       </c>
       <c r="F95">
-        <v>1028.859</v>
+        <v>1039.922</v>
       </c>
       <c r="G95">
         <v>30.3</v>
@@ -9060,37 +9071,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M95">
-        <v>242.6049522</v>
+        <v>245.2136076</v>
       </c>
       <c r="N95">
-        <v>-345.5924522</v>
+        <v>-348.2011076</v>
       </c>
       <c r="O95">
-        <v>-76.030339484</v>
+        <v>-76.604243672</v>
       </c>
       <c r="P95">
-        <v>-269.562112716</v>
+        <v>-271.596863928</v>
       </c>
       <c r="Q95">
-        <v>-155.062112716</v>
+        <v>-157.096863928</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6488138677956438</v>
+        <v>0.7493161790949179</v>
       </c>
       <c r="T95">
-        <v>13.92641727010725</v>
+        <v>16.24748681512513</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>-0.09339153959776425</v>
+        <v>-0.09239801258076674</v>
       </c>
       <c r="W95">
-        <v>0.2578217250371528</v>
+        <v>0.2575874513665448</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9098,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.4245069981716556</v>
+        <v>-0.4199909662762125</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9106,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2870911750302472</v>
+        <v>0.2889911750302471</v>
       </c>
       <c r="C96">
-        <v>-864.8719817299625</v>
+        <v>-877.0658822845525</v>
       </c>
       <c r="D96">
-        <v>144.7500182700376</v>
+        <v>143.6191177154477</v>
       </c>
       <c r="E96">
-        <v>410.522</v>
+        <v>421.5850000000002</v>
       </c>
       <c r="F96">
-        <v>1039.922</v>
+        <v>1050.985</v>
       </c>
       <c r="G96">
         <v>30.3</v>
@@ -9142,37 +9153,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M96">
-        <v>245.2136076</v>
+        <v>247.822263</v>
       </c>
       <c r="N96">
-        <v>-348.2011076</v>
+        <v>-350.809763</v>
       </c>
       <c r="O96">
-        <v>-76.604243672</v>
+        <v>-77.17814786000001</v>
       </c>
       <c r="P96">
-        <v>-271.596863928</v>
+        <v>-273.63161514</v>
       </c>
       <c r="Q96">
-        <v>-157.096863928</v>
+        <v>-159.13161514</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7493161790949179</v>
+        <v>0.8900194149139017</v>
       </c>
       <c r="T96">
-        <v>16.24748681512513</v>
+        <v>19.49698417815016</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>-0.09239801258076674</v>
+        <v>-0.09142540192202181</v>
       </c>
       <c r="W96">
-        <v>0.2575874513665448</v>
+        <v>0.2573581097732127</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9180,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.4199909662762125</v>
+        <v>-0.4155700087364627</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9188,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2889911750302471</v>
+        <v>0.2908911750302471</v>
       </c>
       <c r="C97">
-        <v>-877.0658822845525</v>
+        <v>-889.2422488658895</v>
       </c>
       <c r="D97">
-        <v>143.6191177154477</v>
+        <v>142.5057511341105</v>
       </c>
       <c r="E97">
-        <v>421.5850000000002</v>
+        <v>432.648</v>
       </c>
       <c r="F97">
-        <v>1050.985</v>
+        <v>1062.048</v>
       </c>
       <c r="G97">
         <v>30.3</v>
@@ -9224,37 +9235,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M97">
-        <v>247.822263</v>
+        <v>250.4309184</v>
       </c>
       <c r="N97">
-        <v>-350.809763</v>
+        <v>-353.4184184</v>
       </c>
       <c r="O97">
-        <v>-77.17814786000001</v>
+        <v>-77.752052048</v>
       </c>
       <c r="P97">
-        <v>-273.63161514</v>
+        <v>-275.666366352</v>
       </c>
       <c r="Q97">
-        <v>-159.13161514</v>
+        <v>-161.166366352</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8900194149139017</v>
+        <v>1.101074268642378</v>
       </c>
       <c r="T97">
-        <v>19.49698417815016</v>
+        <v>24.37123022268771</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>-0.09142540192202181</v>
+        <v>-0.09047305398533409</v>
       </c>
       <c r="W97">
-        <v>0.2573581097732127</v>
+        <v>0.2571335461297418</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9262,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.4155700087364627</v>
+        <v>-0.4112411544787913</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9270,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2908911750302471</v>
+        <v>0.2927911750302472</v>
       </c>
       <c r="C98">
-        <v>-889.2422488658895</v>
+        <v>-901.4014861185833</v>
       </c>
       <c r="D98">
-        <v>142.5057511341105</v>
+        <v>141.4095138814165</v>
       </c>
       <c r="E98">
-        <v>432.648</v>
+        <v>443.7109999999999</v>
       </c>
       <c r="F98">
-        <v>1062.048</v>
+        <v>1073.111</v>
       </c>
       <c r="G98">
         <v>30.3</v>
@@ -9306,37 +9317,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M98">
-        <v>250.4309184</v>
+        <v>253.0395738</v>
       </c>
       <c r="N98">
-        <v>-353.4184184</v>
+        <v>-356.0270738</v>
       </c>
       <c r="O98">
-        <v>-77.752052048</v>
+        <v>-78.325956236</v>
       </c>
       <c r="P98">
-        <v>-275.666366352</v>
+        <v>-277.701117564</v>
       </c>
       <c r="Q98">
-        <v>-161.166366352</v>
+        <v>-163.201117564</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.101074268642375</v>
+        <v>1.452832358189833</v>
       </c>
       <c r="T98">
-        <v>24.37123022268765</v>
+        <v>32.4949736302502</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>-0.09047305398533409</v>
+        <v>-0.08954034208857808</v>
       </c>
       <c r="W98">
-        <v>0.2571335461297418</v>
+        <v>0.2569136126644867</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9344,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.4112411544787913</v>
+        <v>-0.4070015549480823</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9352,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2927911750302472</v>
+        <v>0.2946911750302472</v>
       </c>
       <c r="C99">
-        <v>-901.4014861185833</v>
+        <v>-913.5439863312448</v>
       </c>
       <c r="D99">
-        <v>141.4095138814165</v>
+        <v>140.3300136687551</v>
       </c>
       <c r="E99">
-        <v>443.7109999999999</v>
+        <v>454.774</v>
       </c>
       <c r="F99">
-        <v>1073.111</v>
+        <v>1084.174</v>
       </c>
       <c r="G99">
         <v>30.3</v>
@@ -9388,37 +9399,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M99">
-        <v>253.0395738</v>
+        <v>255.6482292</v>
       </c>
       <c r="N99">
-        <v>-356.0270738</v>
+        <v>-358.6357292</v>
       </c>
       <c r="O99">
-        <v>-78.325956236</v>
+        <v>-78.89986042400001</v>
       </c>
       <c r="P99">
-        <v>-277.701117564</v>
+        <v>-279.735868776</v>
       </c>
       <c r="Q99">
-        <v>-163.201117564</v>
+        <v>-165.235868776</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.452832358189833</v>
+        <v>2.15634853728475</v>
       </c>
       <c r="T99">
-        <v>32.4949736302502</v>
+        <v>48.7424604453753</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>-0.08954034208857808</v>
+        <v>-0.08862666512849056</v>
       </c>
       <c r="W99">
-        <v>0.2569136126644867</v>
+        <v>0.2566981676372981</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9426,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.4070015549480823</v>
+        <v>-0.4028484778567754</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9434,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2946911750302472</v>
+        <v>0.2965911750302472</v>
       </c>
       <c r="C100">
-        <v>-913.5439863312448</v>
+        <v>-925.6701299045322</v>
       </c>
       <c r="D100">
-        <v>140.3300136687551</v>
+        <v>139.2668700954676</v>
       </c>
       <c r="E100">
-        <v>454.774</v>
+        <v>465.8369999999999</v>
       </c>
       <c r="F100">
-        <v>1084.174</v>
+        <v>1095.237</v>
       </c>
       <c r="G100">
         <v>30.3</v>
@@ -9470,37 +9481,37 @@
         <v>-102.9875</v>
       </c>
       <c r="M100">
-        <v>255.6482292</v>
+        <v>258.2568846</v>
       </c>
       <c r="N100">
-        <v>-358.6357292</v>
+        <v>-361.2443846</v>
       </c>
       <c r="O100">
-        <v>-78.89986042400001</v>
+        <v>-79.473764612</v>
       </c>
       <c r="P100">
-        <v>-279.735868776</v>
+        <v>-281.770619988</v>
       </c>
       <c r="Q100">
-        <v>-165.235868776</v>
+        <v>-167.270619988</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.15634853728475</v>
+        <v>4.266897074569499</v>
       </c>
       <c r="T100">
-        <v>48.7424604453753</v>
+        <v>97.48492089075059</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>-0.08862666512849056</v>
+        <v>-0.08773144628880884</v>
       </c>
       <c r="W100">
-        <v>0.2566981676372981</v>
+        <v>0.2564870750349011</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9508,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.4028484778567754</v>
+        <v>-0.3987793013127674</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2965911750302472</v>
-      </c>
-      <c r="C101">
-        <v>-925.6701299045322</v>
-      </c>
-      <c r="D101">
-        <v>139.2668700954676</v>
-      </c>
-      <c r="E101">
-        <v>465.8369999999999</v>
-      </c>
-      <c r="F101">
-        <v>1095.237</v>
-      </c>
-      <c r="G101">
-        <v>30.3</v>
-      </c>
-      <c r="H101">
-        <v>476.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>11.5125</v>
-      </c>
-      <c r="K101">
-        <v>114.5</v>
-      </c>
-      <c r="L101">
-        <v>-102.9875</v>
-      </c>
-      <c r="M101">
-        <v>258.2568846</v>
-      </c>
-      <c r="N101">
-        <v>-361.2443846</v>
-      </c>
-      <c r="O101">
-        <v>-79.473764612</v>
-      </c>
-      <c r="P101">
-        <v>-281.770619988</v>
-      </c>
-      <c r="Q101">
-        <v>-167.270619988</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.266897074569499</v>
-      </c>
-      <c r="T101">
-        <v>97.48492089075059</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>-0.08773144628880884</v>
-      </c>
-      <c r="W101">
-        <v>0.2564870750349011</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.3987793013127674</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
